--- a/reports/devops-jobs-israel-2026-W32.xlsx
+++ b/reports/devops-jobs-israel-2026-W32.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="475">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="490">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-03T10:01:46</t>
+    <t xml:space="preserve">2026-08-04T08:50:11</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Junior %</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1%</t>
+    <t xml:space="preserve">1.0%</t>
   </si>
   <si>
     <t xml:space="preserve">Salary disclosure rate %</t>
@@ -399,6 +399,21 @@
     <t xml:space="preserve">2026-06-12</t>
   </si>
   <si>
+    <t xml:space="preserve">Senior DevEx/DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Axonius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, GCP, Terraform, Ansible, Docker, CI/CD, Linux, Python, Security, Observability, FinOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7824320003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-04</t>
+  </si>
+  <si>
     <t xml:space="preserve">Data Science &amp; ML-Ops Team Lead</t>
   </si>
   <si>
@@ -417,6 +432,15 @@
     <t xml:space="preserve">2026-06-07</t>
   </si>
   <si>
+    <t xml:space="preserve">QA Automation Engineer (Temporary Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8542303002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-27</t>
+  </si>
+  <si>
     <t xml:space="preserve">Senior Devops Engineer</t>
   </si>
   <si>
@@ -492,928 +516,949 @@
     <t xml:space="preserve">2026-08-02</t>
   </si>
   <si>
+    <t xml:space="preserve">Checkmarx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-checkmarx-4439196775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medulla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-medulla-4448331135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Point Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-check-point-software-4446179787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wiliot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiliot-4446820849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dialog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-dialog-4446200013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4445878493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure DevOps Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/azure-devops-administrator-at-one-systems-4440105641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevSecOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Playtika</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-at-playtika-4417616851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-abra-4447643479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D-Fend Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-devops-engineer-at-d-fend-solutions-4447057704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps / Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blast Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-platform-engineer-at-blast-security-4445844401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cato-networks-4430441382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personetics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-personetics-4428829912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WalkMe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-walkme-4380911237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SecuriThings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-securithings-4446720959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Earnix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-earnix-4437761619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer – AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UR Tech Jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-%E2%80%93-aws-at-ur-tech-jobs-4447639616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bridgify</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-bridgify-4441525178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yad2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-yad2-4439486812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assured Allies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-assured-allies-4447671142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pagaya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-pagaya-4316888825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Infrastructure &amp; Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moon Active</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-cloud-engineer-at-moon-active-4447031167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oasis Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-oasis-security-4431605535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader - Infra and DevEx</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kaltura</t>
   </si>
   <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-kaltura-4445905827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check Point Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-check-point-software-4446179787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wiliot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiliot-4446820849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dialog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-dialog-4446200013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maytronics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yizra'el, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-engineer-at-maytronics-4437388572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-10</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-infra-and-devex-at-kaltura-4442712745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZOLL Medical Corporation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-zoll-medical-corporation-4399156755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aidoc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-aidoc-4437791495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-gotfriends-4445872562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps / Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lendbuzz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-site-reliability-engineer-sre-at-lendbuzz-4437323317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Linux Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weizmann Institute of Science</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-linux-administrator-at-weizmann-institute-of-science-4444102865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps SRE Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Axon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-sre-engineer-at-axon-4440000142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior\Lead DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-lead-devops-engineer-at-elbit-systems-israel-4375574113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-checkmarx-4446765835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. SRE AI Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Navan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-sre-ai-engineer-at-navan-4437742346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. Principal, DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parallel Wireless</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-principal-devops-at-parallel-wireless-4437772282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-moon-active-4447023421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teads</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-at-teads-4436613100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4429844723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SciPlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-sciplay-4391151881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viz.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-viz-ai-4437383686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4410866558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-mobileye-4436210389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-platform-engineer-at-nvidia-4434371817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Security - AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-security-ai-platform-engineer-at-cato-networks-4416844175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps / Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tipuli Tech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-engineer-at-tipuli-tech-4447115888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akeyless Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-akeyless-security-4445763841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harmonic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-harmonic-4360460066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ThetaRay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-thetaray-4446919831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YouCC Technologies Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashkelon, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ot-infrastructure-engineer-at-youcc-technologies-ltd-4448836015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
   </si>
   <si>
     <t xml:space="preserve">Paragon</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4445878493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moon Active</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-moon-active-4447023421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Infra Engineer / DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-infrastructure-engineer-at-nebius-4437660611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Infrastructure Engineer (Modiin)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-infrastructure-engineer-modiin-at-nebius-4437655743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Technology Infrastructure Engineer - 24262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-infrastructure-engineer-24262-at-comblack-4448306072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior SRE &amp; Linux Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-linux-infrastructure-engineer-at-mobileye-4439143553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computer System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camtek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Engineer (10272)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bynet Data Communications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-10272-at-bynet-data-communications-4446207580</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allpha Innovation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-allpha-innovation-4448822755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GE HealthCare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-ge-healthcare-4448609363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‫System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JobsSeek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%E2%80%ABsystem-engineer-at-jobsseek-4427766128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unilink Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-unilink-ltd-4446581282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Network Infrastructure Engineer - 20690</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-infrastructure-engineer-20690-at-comblack-4448189250</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-gotfriends-4445849138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE Technical Lead, DevOps Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BigPanda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-technical-lead-devops-group-at-bigpanda-4447980511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group Leader - Cloud Platform &amp; SRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/group-leader-cloud-platform-sre-at-confidential-4434818632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bagira</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-bagira-4368663100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KMS Lighthouse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-kms-lighthouse-4447696634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Automation Engineer - Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-automation-engineer-networking-at-cato-networks-4378169465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior SRE (IT Infrastructure)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-it-infrastructure-at-palo-alto-networks-4387086808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior AI SRE Developer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helfy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Full Stack Developer - Data Loss Prevention Cloud Service</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-full-stack-developer-data-loss-prevention-cloud-service-at-check-point-software-4446847161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator - Linux, Windows #1350</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-linux-windows-%231350-at-rad-4443763825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calanit by one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Virtualization, Active Directory, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-calanit-by-one-4448158765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waterfall Security Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-position-at-waterfall-security-solutions-4444878648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer – Test Environments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Monitoring, Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-%E2%80%93-test-environments-at-comblack-4446757352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Technical Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4442889333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior QA Engineer - Student Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fives</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-qa-engineer-student-position-at-fives-4436801163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation student- Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-jerusalem-at-radware-4440152008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-at-radware-4437695096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud &amp; AI Security Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4932015101?gh_jid=4932015101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
   </si>
   <si>
     <t xml:space="preserve">Haifa District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infra-engineer-devops-engineer-at-elbit-systems-israel-4442854342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arad Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-arad-technologies-4445126362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harmonic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-harmonic-4360460066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobileye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-mobileye-4436210389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akeyless Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-akeyless-security-4445763841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Personetics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-personetics-4428829912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cato-networks-4430441382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OFFROAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-offroad-4448139496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ThetaRay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-thetaray-4446919831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WalkMe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-walkme-4380911237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SecuriThings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-securithings-4446720959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevSecOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Playtika</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-at-playtika-4417616851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Earnix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-earnix-4437761619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer – AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UR Tech Jobs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-%E2%80%93-aws-at-ur-tech-jobs-4447639616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Specialist - 20705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-specialist-20705-at-comblack-4447008409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bridgify</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-bridgify-4441525178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assured Allies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-assured-allies-4447671142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D-Fend Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-devops-engineer-at-d-fend-solutions-4447057704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Infrastructure &amp; Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-cloud-engineer-at-moon-active-4447031167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader - Infra and DevEx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-infra-and-devex-at-kaltura-4442712745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZOLL Medical Corporation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-zoll-medical-corporation-4399156755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aidoc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-aidoc-4437791495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-gotfriends-4445872562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps / Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lendbuzz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-site-reliability-engineer-sre-at-lendbuzz-4437323317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Linux Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weizmann Institute of Science</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-linux-administrator-at-weizmann-institute-of-science-4444102865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior\Lead DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-lead-devops-engineer-at-elbit-systems-israel-4375574113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Service Reliability Engineer MI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stratacom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-reliability-engineer-mi-at-stratacom-4446130177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. SRE AI Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-sre-ai-engineer-at-navan-4437742346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-team-leader-at-radware-4442833696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior SRE (IT Infrastructure)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-it-infrastructure-at-palo-alto-networks-4387086808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4410866558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teads</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-at-teads-4436613100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SciPlay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-sciplay-4391151881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viz.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-viz-ai-4437383686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior AI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-platform-engineer-at-nvidia-4434371817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps / Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tipuli Tech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-engineer-at-tipuli-tech-4447115888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps / Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blast Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-platform-engineer-at-blast-security-4445844401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-sela-4443226746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">‫DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JobsSeek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%E2%80%ABdevops-engineer-at-jobsseek-4445184888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-abra-4447643479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4429844723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer – Test Environments</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-%E2%80%93-test-environments-at-comblack-4446757352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prisma Photonics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-prisma-photonics-4432235322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-infrastructure-engineer-at-nebius-4437660618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Snke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-snke-4445005467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Infrastructure Engineer (Modiin)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-infrastructure-engineer-modiin-at-nebius-4437655743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">‫System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%E2%80%ABsystem-engineer-at-jobsseek-4427766128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calanit by one</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-calanit-by-one-4448157690</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashdod, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4445838320</t>
-  </si>
-  <si>
-    <t xml:space="preserve">‫Satellite System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%E2%80%ABsatellite-system-engineer-at-jobsseek-4445198084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Korentec Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-yael-korentec-technologies-4447880470</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator (36620 )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-36620-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4446723677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-student-at-elbit-systems-israel-4435662496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-elbit-systems-israel-4375558561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KMS Lighthouse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-kms-lighthouse-4446064508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.6%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.3%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Axonius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, CI/CD, Git, Terraform/IaC, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-operations-engineer-at-axonius-4444135962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior AI SRE Developer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helfy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Full Stack Developer - Data Loss Prevention Cloud Service</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-full-stack-developer-data-loss-prevention-cloud-service-at-check-point-software-4446847161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior IT DevOps Engineer - Temporary Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-devops-engineer-temporary-position-at-mobileye-4417802849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Autobrains Technologies</t>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414157765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IOT student tester</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Motorola Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/iot-student-tester-at-motorola-solutions-4434451222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator &amp; IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inManage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-4428415454</t>
   </si>
   <si>
     <t xml:space="preserve">Help Desk / IT Support</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4440209390</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-gotfriends-4445849138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud &amp; AI Security Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4932015101?gh_jid=4932015101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">etoro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-etoro-4434952696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist – MENTEE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-%E2%80%93-mentee-at-mobileye-4445729205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations &amp; Helpdesk Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claroty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-helpdesk-engineer-at-claroty-4412805136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global Service Desk Representative</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Monitoring, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/global-service-desk-representative-at-radware-4442335619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Droxi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-operations-engineer-at-droxi-4426788584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Align Technology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-at-align-technology-4441786255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Help Desk (student position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LiveU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-student-position-at-liveu-4434277505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seemplicity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-at-seemplicity-4445609263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spinomenal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-spinomenal-4431228721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-24</t>
-  </si>
-  <si>
     <t xml:space="preserve">Roles requiring it</t>
   </si>
   <si>
     <t xml:space="preserve">Troubleshooting</t>
   </si>
   <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
     <t xml:space="preserve">Active Directory</t>
   </si>
   <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring</t>
+    <t xml:space="preserve">Git</t>
   </si>
   <si>
     <t xml:space="preserve">Virtualization</t>
@@ -1568,7 +1613,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7">
@@ -1576,7 +1621,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -1584,7 +1629,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9">
@@ -1592,7 +1637,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>1184</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="10">
@@ -1664,7 +1709,7 @@
         <v>23</v>
       </c>
       <c r="B19" s="3">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="20">
@@ -1672,7 +1717,7 @@
         <v>24</v>
       </c>
       <c r="B20" s="3">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -1691,47 +1736,39 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>370</v>
+        <v>390</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>401</v>
+        <v>471</v>
       </c>
       <c r="B2" s="3">
-        <v>44</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>379</v>
+        <v>408</v>
       </c>
       <c r="B3" s="3">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>396</v>
+        <v>420</v>
       </c>
       <c r="B4" s="3">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>384</v>
+        <v>399</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="B6" s="3">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1747,87 +1784,87 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>354</v>
+        <v>376</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>458</v>
+        <v>472</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>459</v>
+        <v>473</v>
       </c>
       <c r="B2" s="3">
-        <v>42</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="B3" s="3">
-        <v>37</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>460</v>
+        <v>474</v>
       </c>
       <c r="B4" s="3">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>461</v>
+        <v>371</v>
       </c>
       <c r="B5" s="3">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>462</v>
+        <v>254</v>
       </c>
       <c r="B6" s="3">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>463</v>
+        <v>475</v>
       </c>
       <c r="B7" s="3">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>359</v>
+        <v>476</v>
       </c>
       <c r="B8" s="3">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>360</v>
+        <v>477</v>
       </c>
       <c r="B9" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>464</v>
+        <v>478</v>
       </c>
       <c r="B10" s="3">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>260</v>
+        <v>378</v>
       </c>
       <c r="B11" s="3">
         <v>13</v>
@@ -1835,42 +1872,42 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>356</v>
+        <v>479</v>
       </c>
       <c r="B12" s="3">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>228</v>
+        <v>380</v>
       </c>
       <c r="B13" s="3">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>358</v>
+        <v>216</v>
       </c>
       <c r="B14" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>465</v>
+        <v>185</v>
       </c>
       <c r="B15" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>357</v>
+        <v>480</v>
       </c>
       <c r="B16" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1895,13 +1932,13 @@
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>466</v>
+        <v>481</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>467</v>
+        <v>482</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>468</v>
+        <v>483</v>
       </c>
     </row>
     <row r="2">
@@ -1909,13 +1946,13 @@
         <v>24</v>
       </c>
       <c r="B2" s="3">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C2" s="3">
-        <v>12.8</v>
+        <v>13.2</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>469</v>
+        <v>484</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -1924,88 +1961,88 @@
         <v>23</v>
       </c>
       <c r="B3" s="3">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C3" s="3">
-        <v>31.7</v>
+        <v>35.0</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>469</v>
+        <v>484</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>470</v>
+        <v>485</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>7.9</v>
+        <v>8.0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>469</v>
+        <v>484</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>471</v>
+        <v>486</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>469</v>
+        <v>484</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>472</v>
+        <v>487</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>35.6</v>
+        <v>37.6</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>469</v>
+        <v>484</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>473</v>
+        <v>488</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>469</v>
+        <v>484</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>474</v>
+        <v>489</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>405.7</v>
+        <v>28.4</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>469</v>
+        <v>484</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2017,7 +2054,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="35" customWidth="1"/>
+    <col min="2" max="2" width="31" customWidth="1"/>
     <col min="3" max="3" width="47" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -2089,7 +2126,7 @@
         <v>41</v>
       </c>
       <c r="J2" s="3">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3">
@@ -2121,7 +2158,7 @@
         <v>46</v>
       </c>
       <c r="J3" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -2153,7 +2190,7 @@
         <v>52</v>
       </c>
       <c r="J4" s="3">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5">
@@ -2185,7 +2222,7 @@
         <v>41</v>
       </c>
       <c r="J5" s="3">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6">
@@ -2217,7 +2254,7 @@
         <v>41</v>
       </c>
       <c r="J6" s="3">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7">
@@ -2249,7 +2286,7 @@
         <v>63</v>
       </c>
       <c r="J7" s="3">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8">
@@ -2281,7 +2318,7 @@
         <v>41</v>
       </c>
       <c r="J8" s="3">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9">
@@ -2313,7 +2350,7 @@
         <v>73</v>
       </c>
       <c r="J9" s="3">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10">
@@ -2345,7 +2382,7 @@
         <v>77</v>
       </c>
       <c r="J10" s="3">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11">
@@ -2377,7 +2414,7 @@
         <v>73</v>
       </c>
       <c r="J11" s="3">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12">
@@ -2409,7 +2446,7 @@
         <v>84</v>
       </c>
       <c r="J12" s="3">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13">
@@ -2441,7 +2478,7 @@
         <v>90</v>
       </c>
       <c r="J13" s="3">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14">
@@ -2473,7 +2510,7 @@
         <v>95</v>
       </c>
       <c r="J14" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
@@ -2505,7 +2542,7 @@
         <v>46</v>
       </c>
       <c r="J15" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -2537,7 +2574,7 @@
         <v>102</v>
       </c>
       <c r="J16" s="3">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17">
@@ -2569,7 +2606,7 @@
         <v>77</v>
       </c>
       <c r="J17" s="3">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18">
@@ -2601,7 +2638,7 @@
         <v>109</v>
       </c>
       <c r="J18" s="3">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="19">
@@ -2633,7 +2670,7 @@
         <v>115</v>
       </c>
       <c r="J19" s="3">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20">
@@ -2665,7 +2702,7 @@
         <v>41</v>
       </c>
       <c r="J20" s="3">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21">
@@ -2697,7 +2734,7 @@
         <v>125</v>
       </c>
       <c r="J21" s="3">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22">
@@ -2708,7 +2745,7 @@
         <v>127</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>128</v>
+        <v>87</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>49</v>
@@ -2717,30 +2754,30 @@
         <v>38</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H22" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>131</v>
-      </c>
       <c r="J22" s="3">
-        <v>57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>127</v>
-      </c>
       <c r="C23" s="3" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>49</v>
@@ -2749,36 +2786,36 @@
         <v>38</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>41</v>
+        <v>136</v>
       </c>
       <c r="J23" s="3">
-        <v>83</v>
+        <v>58</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>137</v>
+        <v>49</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="3" t="s">
@@ -2791,7 +2828,7 @@
         <v>139</v>
       </c>
       <c r="J24" s="3">
-        <v>60</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25">
@@ -2799,10 +2836,10 @@
         <v>140</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>49</v>
+        <v>133</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>49</v>
@@ -2811,24 +2848,24 @@
         <v>38</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>77</v>
+        <v>41</v>
       </c>
       <c r="J25" s="3">
-        <v>67</v>
+        <v>84</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>116</v>
+        <v>143</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>144</v>
@@ -2837,14 +2874,14 @@
         <v>145</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>49</v>
+        <v>145</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>146</v>
@@ -2853,37 +2890,39 @@
         <v>147</v>
       </c>
       <c r="J26" s="3">
-        <v>49</v>
+        <v>61</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>116</v>
+        <v>148</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>149</v>
+        <v>49</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F27" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>150</v>
+      </c>
       <c r="G27" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>151</v>
+        <v>77</v>
       </c>
       <c r="J27" s="3">
-        <v>0</v>
+        <v>68</v>
       </c>
     </row>
     <row r="28">
@@ -2897,7 +2936,7 @@
         <v>153</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>154</v>
+        <v>49</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>43</v>
@@ -2907,13 +2946,13 @@
         <v>23</v>
       </c>
       <c r="H28" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="I28" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="I28" s="3" t="s">
-        <v>156</v>
-      </c>
       <c r="J28" s="3">
-        <v>1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29">
@@ -2921,13 +2960,13 @@
         <v>116</v>
       </c>
       <c r="B29" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="C29" s="3" t="s">
-        <v>158</v>
-      </c>
       <c r="D29" s="3" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>43</v>
@@ -2937,13 +2976,13 @@
         <v>23</v>
       </c>
       <c r="H29" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="I29" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="I29" s="3" t="s">
-        <v>95</v>
-      </c>
       <c r="J29" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2954,10 +2993,10 @@
         <v>160</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>49</v>
+        <v>162</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>43</v>
@@ -2967,13 +3006,13 @@
         <v>23</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="J30" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2981,10 +3020,10 @@
         <v>116</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>49</v>
@@ -2997,13 +3036,13 @@
         <v>23</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="J31" s="3">
-        <v>4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32">
@@ -3011,13 +3050,13 @@
         <v>116</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>43</v>
@@ -3027,10 +3066,10 @@
         <v>23</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>151</v>
+        <v>130</v>
       </c>
       <c r="J32" s="3">
         <v>0</v>
@@ -3038,16 +3077,16 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>169</v>
+        <v>116</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>43</v>
@@ -3057,13 +3096,13 @@
         <v>23</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="J33" s="3">
-        <v>24</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34">
@@ -3071,10 +3110,10 @@
         <v>116</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>49</v>
@@ -3087,13 +3126,13 @@
         <v>23</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J34" s="3">
-        <v>70</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35">
@@ -3101,10 +3140,10 @@
         <v>116</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>122</v>
@@ -3117,13 +3156,13 @@
         <v>23</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="J35" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -3131,13 +3170,13 @@
         <v>116</v>
       </c>
       <c r="B36" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C36" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="C36" s="3" t="s">
-        <v>145</v>
-      </c>
       <c r="D36" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>43</v>
@@ -3147,87 +3186,91 @@
         <v>23</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>181</v>
+        <v>159</v>
       </c>
       <c r="J36" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>154</v>
+        <v>49</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F37" s="3"/>
+      <c r="F37" s="3" t="s">
+        <v>185</v>
+      </c>
       <c r="G37" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>95</v>
+        <v>130</v>
       </c>
       <c r="J37" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>116</v>
+        <v>187</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>187</v>
+        <v>60</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F38" s="3"/>
+      <c r="F38" s="3" t="s">
+        <v>189</v>
+      </c>
       <c r="G38" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="J38" s="3">
-        <v>6</v>
+        <v>68</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>189</v>
+        <v>53</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>154</v>
+        <v>122</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>38</v>
@@ -3240,24 +3283,24 @@
         <v>192</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>193</v>
+        <v>164</v>
       </c>
       <c r="J39" s="3">
-        <v>68</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B40" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="B40" s="3" t="s">
-        <v>195</v>
-      </c>
       <c r="C40" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>43</v>
@@ -3267,30 +3310,30 @@
         <v>23</v>
       </c>
       <c r="H40" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="I40" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="I40" s="3" t="s">
-        <v>197</v>
-      </c>
       <c r="J40" s="3">
-        <v>27</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>116</v>
+        <v>197</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>198</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
@@ -3300,10 +3343,10 @@
         <v>199</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="J41" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -3314,7 +3357,7 @@
         <v>200</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>201</v>
+        <v>170</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>49</v>
@@ -3327,13 +3370,13 @@
         <v>23</v>
       </c>
       <c r="H42" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="I42" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="I42" s="3" t="s">
-        <v>147</v>
-      </c>
       <c r="J42" s="3">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="43">
@@ -3360,70 +3403,72 @@
         <v>205</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>206</v>
+        <v>155</v>
       </c>
       <c r="J43" s="3">
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B44" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H44" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="C44" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F44" s="3"/>
-      <c r="G44" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H44" s="3" t="s">
+      <c r="I44" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>151</v>
-      </c>
       <c r="J44" s="3">
-        <v>0</v>
+        <v>65</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>116</v>
+        <v>53</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>209</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>210</v>
+        <v>166</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="J45" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46">
@@ -3431,10 +3476,10 @@
         <v>53</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>49</v>
@@ -3447,45 +3492,45 @@
         <v>23</v>
       </c>
       <c r="H46" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="I46" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>84</v>
-      </c>
       <c r="J46" s="3">
-        <v>80</v>
+        <v>26</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>47</v>
+        <v>214</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>145</v>
+        <v>179</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>43</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>217</v>
+        <v>164</v>
       </c>
       <c r="J47" s="3">
-        <v>64</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -3496,7 +3541,7 @@
         <v>218</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>49</v>
@@ -3512,10 +3557,10 @@
         <v>219</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="J48" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3526,28 +3571,26 @@
         <v>221</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>60</v>
+        <v>222</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>49</v>
+        <v>223</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>215</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>77</v>
+        <v>225</v>
       </c>
       <c r="J49" s="3">
-        <v>67</v>
+        <v>20</v>
       </c>
     </row>
     <row r="50">
@@ -3555,10 +3598,10 @@
         <v>53</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>49</v>
@@ -3571,34 +3614,32 @@
         <v>23</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>225</v>
+        <v>159</v>
       </c>
       <c r="J50" s="3">
-        <v>25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>226</v>
+        <v>53</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>228</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
         <v>23</v>
       </c>
@@ -3606,24 +3647,24 @@
         <v>229</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>156</v>
+        <v>230</v>
       </c>
       <c r="J51" s="3">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>232</v>
+        <v>153</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>43</v>
@@ -3636,10 +3677,10 @@
         <v>233</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="J52" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53">
@@ -3650,7 +3691,7 @@
         <v>234</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>49</v>
@@ -3666,54 +3707,54 @@
         <v>235</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>151</v>
+        <v>236</v>
       </c>
       <c r="J53" s="3">
-        <v>0</v>
+        <v>42</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>53</v>
+        <v>237</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>151</v>
+        <v>240</v>
       </c>
       <c r="J54" s="3">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>149</v>
+        <v>60</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>43</v>
@@ -3723,144 +3764,146 @@
         <v>23</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>181</v>
+        <v>139</v>
       </c>
       <c r="J55" s="3">
-        <v>3</v>
+        <v>69</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>241</v>
+        <v>53</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>179</v>
+        <v>244</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F56" s="3"/>
       <c r="G56" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>181</v>
+        <v>246</v>
       </c>
       <c r="J56" s="3">
-        <v>3</v>
+        <v>27</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>243</v>
+        <v>220</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>157</v>
+        <v>181</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>245</v>
+        <v>159</v>
       </c>
       <c r="J57" s="3">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>60</v>
+        <v>153</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>193</v>
+        <v>213</v>
       </c>
       <c r="J58" s="3">
-        <v>68</v>
+        <v>26</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>53</v>
+        <v>251</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>145</v>
+        <v>253</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F59" s="3"/>
+        <v>43</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>254</v>
+      </c>
       <c r="G59" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>251</v>
+        <v>196</v>
       </c>
       <c r="J59" s="3">
-        <v>26</v>
+        <v>4</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>177</v>
+        <v>257</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>204</v>
+        <v>153</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>49</v>
@@ -3873,27 +3916,27 @@
         <v>23</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>151</v>
+        <v>168</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>145</v>
+        <v>261</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>49</v>
+        <v>262</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>38</v>
@@ -3903,59 +3946,57 @@
         <v>23</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>225</v>
+        <v>264</v>
       </c>
       <c r="J61" s="3">
-        <v>25</v>
+        <v>72</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>258</v>
+        <v>165</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>259</v>
+        <v>166</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F62" s="3" t="s">
-        <v>260</v>
-      </c>
+      <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="J62" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>183</v>
+        <v>268</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>263</v>
+        <v>153</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>264</v>
+        <v>49</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>38</v>
@@ -3965,87 +4006,87 @@
         <v>23</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="J63" s="3">
-        <v>71</v>
+        <v>28</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>165</v>
+        <v>246</v>
       </c>
       <c r="J64" s="3">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>271</v>
+        <v>116</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>272</v>
+        <v>232</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J65" s="3">
-        <v>27</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>145</v>
+        <v>261</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>49</v>
+        <v>262</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>43</v>
@@ -4055,24 +4096,24 @@
         <v>23</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>95</v>
+        <v>279</v>
       </c>
       <c r="J66" s="3">
-        <v>6</v>
+        <v>23</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>277</v>
+        <v>53</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>49</v>
@@ -4085,27 +4126,27 @@
         <v>23</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>77</v>
+        <v>282</v>
       </c>
       <c r="J67" s="3">
-        <v>67</v>
+        <v>39</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>280</v>
+        <v>53</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>152</v>
+        <v>283</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>281</v>
+        <v>153</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>38</v>
@@ -4115,43 +4156,43 @@
         <v>23</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>217</v>
+        <v>84</v>
       </c>
       <c r="J68" s="3">
-        <v>64</v>
+        <v>81</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>283</v>
+        <v>56</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>263</v>
+        <v>153</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>264</v>
+        <v>49</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>286</v>
+        <v>84</v>
       </c>
       <c r="J69" s="3">
-        <v>22</v>
+        <v>81</v>
       </c>
     </row>
     <row r="70">
@@ -4162,7 +4203,7 @@
         <v>287</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>49</v>
@@ -4178,24 +4219,24 @@
         <v>288</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>84</v>
+        <v>279</v>
       </c>
       <c r="J70" s="3">
-        <v>80</v>
+        <v>23</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>56</v>
+        <v>289</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>289</v>
+        <v>160</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>145</v>
+        <v>290</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>38</v>
@@ -4205,73 +4246,73 @@
         <v>23</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>286</v>
+        <v>208</v>
       </c>
       <c r="J71" s="3">
-        <v>22</v>
+        <v>65</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>152</v>
+        <v>293</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>281</v>
+        <v>166</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>293</v>
+        <v>270</v>
       </c>
       <c r="J72" s="3">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>295</v>
+        <v>160</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H73" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="I73" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="I73" s="3" t="s">
-        <v>156</v>
-      </c>
       <c r="J73" s="3">
-        <v>1</v>
+        <v>32</v>
       </c>
     </row>
     <row r="74">
@@ -4279,73 +4320,75 @@
         <v>298</v>
       </c>
       <c r="B74" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H74" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="C74" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="D74" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E74" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F74" s="3"/>
-      <c r="G74" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H74" s="3" t="s">
+      <c r="I74" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="I74" s="3" t="s">
-        <v>151</v>
-      </c>
       <c r="J74" s="3">
-        <v>0</v>
+        <v>41</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>53</v>
+        <v>301</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>167</v>
+        <v>303</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F75" s="3"/>
       <c r="G75" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="J75" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>303</v>
+        <v>116</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>305</v>
+        <v>166</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>43</v>
@@ -4358,7 +4401,7 @@
         <v>306</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>95</v>
+        <v>174</v>
       </c>
       <c r="J76" s="3">
         <v>6</v>
@@ -4366,16 +4409,16 @@
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>53</v>
+        <v>307</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>167</v>
+        <v>309</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>122</v>
+        <v>162</v>
       </c>
       <c r="E77" s="3" t="s">
         <v>38</v>
@@ -4385,54 +4428,54 @@
         <v>23</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>156</v>
+        <v>139</v>
       </c>
       <c r="J77" s="3">
-        <v>1</v>
+        <v>69</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>53</v>
+        <v>116</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>145</v>
+        <v>312</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>311</v>
+        <v>196</v>
       </c>
       <c r="J78" s="3">
-        <v>38</v>
+        <v>4</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>231</v>
+        <v>315</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>167</v>
+        <v>316</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>122</v>
@@ -4445,54 +4488,54 @@
         <v>23</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>181</v>
+        <v>130</v>
       </c>
       <c r="J79" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>197</v>
+        <v>321</v>
       </c>
       <c r="J80" s="3">
-        <v>27</v>
+        <v>56</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>122</v>
@@ -4505,27 +4548,27 @@
         <v>23</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="J81" s="3">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="B82" s="3" t="s">
         <v>323</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>263</v>
+        <v>328</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>264</v>
+        <v>122</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>43</v>
@@ -4535,24 +4578,24 @@
         <v>23</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>181</v>
+        <v>225</v>
       </c>
       <c r="J82" s="3">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>174</v>
+        <v>331</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>145</v>
+        <v>170</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>49</v>
@@ -4565,54 +4608,56 @@
         <v>23</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>326</v>
+        <v>130</v>
       </c>
       <c r="J83" s="3">
-        <v>55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>318</v>
+        <v>293</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>122</v>
+        <v>145</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F84" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>254</v>
+      </c>
       <c r="G84" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>321</v>
+        <v>230</v>
       </c>
       <c r="J84" s="3">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>304</v>
+        <v>337</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>305</v>
+        <v>338</v>
       </c>
       <c r="D85" s="3" t="s">
         <v>122</v>
@@ -4625,42 +4670,40 @@
         <v>23</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>225</v>
+        <v>115</v>
       </c>
       <c r="J85" s="3">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>232</v>
+        <v>170</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F86" s="3" t="s">
-        <v>260</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F86" s="3"/>
       <c r="G86" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>151</v>
+        <v>130</v>
       </c>
       <c r="J86" s="3">
         <v>0</v>
@@ -4668,13 +4711,13 @@
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>336</v>
+        <v>179</v>
       </c>
       <c r="D87" s="3" t="s">
         <v>122</v>
@@ -4687,10 +4730,10 @@
         <v>23</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>151</v>
+        <v>130</v>
       </c>
       <c r="J87" s="3">
         <v>0</v>
@@ -4698,16 +4741,16 @@
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>338</v>
+        <v>318</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>304</v>
+        <v>345</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>122</v>
+        <v>162</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>43</v>
@@ -4717,24 +4760,24 @@
         <v>23</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>181</v>
+        <v>130</v>
       </c>
       <c r="J88" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>322</v>
+        <v>348</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>167</v>
+        <v>350</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>122</v>
@@ -4747,27 +4790,27 @@
         <v>23</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>151</v>
+        <v>213</v>
       </c>
       <c r="J89" s="3">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>43</v>
@@ -4777,27 +4820,27 @@
         <v>23</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>181</v>
+        <v>130</v>
       </c>
       <c r="J90" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>183</v>
+        <v>331</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>263</v>
+        <v>356</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>264</v>
+        <v>122</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>43</v>
@@ -4807,24 +4850,24 @@
         <v>23</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>286</v>
+        <v>130</v>
       </c>
       <c r="J91" s="3">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>322</v>
+        <v>352</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>348</v>
+        <v>170</v>
       </c>
       <c r="D92" s="3" t="s">
         <v>49</v>
@@ -4837,47 +4880,199 @@
         <v>23</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>165</v>
+        <v>130</v>
       </c>
       <c r="J92" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>246</v>
+        <v>359</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>351</v>
+        <v>153</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>352</v>
+        <v>49</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F93" s="3"/>
       <c r="G93" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>165</v>
+        <v>130</v>
       </c>
       <c r="J93" s="3">
-        <v>4</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F94" s="3"/>
+      <c r="G94" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="J94" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F95" s="3"/>
+      <c r="G95" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H95" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="I95" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="J95" s="3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F96" s="3"/>
+      <c r="G96" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="J96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F97" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="G97" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H97" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="I97" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="J97" s="3">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F98" s="3"/>
+      <c r="G98" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H98" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="I98" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="J98" s="3">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J93"/>
+  <autoFilter ref="A1:J98"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -4971,6 +5166,11 @@
     <hyperlink ref="H91" r:id="rId90"/>
     <hyperlink ref="H92" r:id="rId91"/>
     <hyperlink ref="H93" r:id="rId92"/>
+    <hyperlink ref="H94" r:id="rId93"/>
+    <hyperlink ref="H95" r:id="rId94"/>
+    <hyperlink ref="H96" r:id="rId95"/>
+    <hyperlink ref="H97" r:id="rId96"/>
+    <hyperlink ref="H98" r:id="rId97"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4978,8 +5178,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="35" customWidth="1"/>
-    <col min="2" max="2" width="35" customWidth="1"/>
+    <col min="1" max="1" width="56" customWidth="1"/>
+    <col min="2" max="2" width="27" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -5012,21 +5212,21 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>148</v>
+        <v>127</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>149</v>
+        <v>87</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>150</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3">
@@ -5034,10 +5234,10 @@
         <v>116</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -5045,18 +5245,18 @@
         <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>116</v>
+        <v>183</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -5064,18 +5264,18 @@
         <v>23</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>53</v>
+        <v>314</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>207</v>
+        <v>315</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>145</v>
+        <v>316</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5083,18 +5283,18 @@
         <v>23</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>208</v>
+        <v>317</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>53</v>
+        <v>330</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>234</v>
+        <v>331</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>145</v>
+        <v>170</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -5102,18 +5302,18 @@
         <v>23</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>235</v>
+        <v>332</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>53</v>
+        <v>340</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>236</v>
+        <v>341</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -5121,18 +5321,18 @@
         <v>23</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>237</v>
+        <v>342</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>252</v>
+        <v>318</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>177</v>
+        <v>343</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>204</v>
+        <v>179</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -5140,18 +5340,18 @@
         <v>23</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>253</v>
+        <v>344</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>299</v>
+        <v>345</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>204</v>
+        <v>346</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -5159,18 +5359,18 @@
         <v>23</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>300</v>
+        <v>347</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>332</v>
+        <v>352</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>333</v>
+        <v>353</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>232</v>
+        <v>170</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -5178,18 +5378,18 @@
         <v>23</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>334</v>
+        <v>354</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>322</v>
+        <v>355</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>336</v>
+        <v>356</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -5197,18 +5397,18 @@
         <v>23</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>337</v>
+        <v>357</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>322</v>
+        <v>352</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>341</v>
+        <v>181</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
@@ -5216,11 +5416,49 @@
         <v>23</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>342</v>
+        <v>358</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>369</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G12"/>
+  <autoFilter ref="A1:G14"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -5233,6 +5471,8 @@
     <hyperlink ref="G10" r:id="rId9"/>
     <hyperlink ref="G11" r:id="rId10"/>
     <hyperlink ref="G12" r:id="rId11"/>
+    <hyperlink ref="G13" r:id="rId12"/>
+    <hyperlink ref="G14" r:id="rId13"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5246,111 +5486,111 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>354</v>
+        <v>376</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>355</v>
+        <v>377</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>228</v>
+        <v>189</v>
       </c>
       <c r="B2" s="3">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>356</v>
+        <v>216</v>
       </c>
       <c r="B3" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>215</v>
+        <v>378</v>
       </c>
       <c r="B4" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>357</v>
+        <v>379</v>
       </c>
       <c r="B5" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>358</v>
+        <v>380</v>
       </c>
       <c r="B6" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="B7" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>359</v>
+        <v>381</v>
       </c>
       <c r="B8" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>360</v>
+        <v>185</v>
       </c>
       <c r="B9" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>361</v>
+        <v>382</v>
       </c>
       <c r="B10" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>362</v>
+        <v>383</v>
       </c>
       <c r="B11" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="B12" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="B13" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>364</v>
+        <v>384</v>
       </c>
       <c r="B14" s="3">
         <v>6</v>
@@ -5358,7 +5598,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>365</v>
+        <v>385</v>
       </c>
       <c r="B15" s="3">
         <v>5</v>
@@ -5366,7 +5606,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>366</v>
+        <v>386</v>
       </c>
       <c r="B16" s="3">
         <v>4</v>
@@ -5379,7 +5619,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5388,7 +5628,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>367</v>
+        <v>387</v>
       </c>
     </row>
     <row r="2">
@@ -5409,15 +5649,15 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>183</v>
+        <v>48</v>
       </c>
       <c r="B4" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>48</v>
+        <v>132</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -5425,7 +5665,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -5433,7 +5673,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>304</v>
+        <v>181</v>
       </c>
       <c r="B7" s="3">
         <v>3</v>
@@ -5441,15 +5681,15 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>35</v>
+        <v>200</v>
       </c>
       <c r="B8" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>104</v>
+        <v>35</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
@@ -5457,7 +5697,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>127</v>
+        <v>104</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -5465,7 +5705,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5473,7 +5713,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>174</v>
+        <v>232</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5481,7 +5721,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>177</v>
+        <v>293</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -5489,7 +5729,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>179</v>
+        <v>323</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -5497,7 +5737,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>231</v>
+        <v>331</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -5505,10 +5745,10 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>318</v>
+        <v>59</v>
       </c>
       <c r="B16" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -5519,23 +5759,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>368</v>
+        <v>388</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>369</v>
+        <v>389</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>367</v>
+        <v>387</v>
       </c>
     </row>
     <row r="2">
@@ -5585,13 +5825,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>35</v>
+        <v>132</v>
       </c>
       <c r="C5" s="3">
-        <v>6.2</v>
+        <v>8.8</v>
       </c>
       <c r="D5" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -5599,13 +5839,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>183</v>
+        <v>35</v>
       </c>
       <c r="C6" s="3">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="D6" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -5627,13 +5867,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>127</v>
+        <v>200</v>
       </c>
       <c r="C8" s="3">
         <v>5.0</v>
       </c>
       <c r="D8" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -5641,7 +5881,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="C9" s="3">
         <v>4.2</v>
@@ -5655,10 +5895,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>304</v>
+        <v>181</v>
       </c>
       <c r="C10" s="3">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="D10" s="3">
         <v>3</v>
@@ -5669,13 +5909,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>117</v>
+        <v>293</v>
       </c>
       <c r="C11" s="3">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="D11" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -5683,13 +5923,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>177</v>
+        <v>117</v>
       </c>
       <c r="C12" s="3">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="D12" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -5697,13 +5937,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>157</v>
+        <v>127</v>
       </c>
       <c r="C13" s="3">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="D13" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -5711,7 +5951,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="C14" s="3">
         <v>2.4</v>
@@ -5725,7 +5965,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>179</v>
+        <v>232</v>
       </c>
       <c r="C15" s="3">
         <v>2.4</v>
@@ -5739,7 +5979,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>231</v>
+        <v>323</v>
       </c>
       <c r="C16" s="3">
         <v>2.4</v>
@@ -5765,10 +6005,10 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>370</v>
+        <v>390</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>371</v>
+        <v>391</v>
       </c>
     </row>
     <row r="2">
@@ -5787,10 +6027,10 @@
         <v>43</v>
       </c>
       <c r="B3" s="3">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>372</v>
+        <v>392</v>
       </c>
     </row>
     <row r="4">
@@ -5798,10 +6038,10 @@
         <v>38</v>
       </c>
       <c r="B4" s="3">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>373</v>
+        <v>393</v>
       </c>
     </row>
   </sheetData>
@@ -5820,7 +6060,7 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>370</v>
+        <v>390</v>
       </c>
     </row>
     <row r="2">
@@ -5828,7 +6068,7 @@
         <v>49</v>
       </c>
       <c r="B2" s="3">
-        <v>55</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3">
@@ -5836,7 +6076,7 @@
         <v>122</v>
       </c>
       <c r="B3" s="3">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">
@@ -5849,39 +6089,39 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>264</v>
+        <v>162</v>
       </c>
       <c r="B5" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="B6" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>112</v>
+        <v>223</v>
       </c>
       <c r="B7" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>137</v>
+        <v>262</v>
       </c>
       <c r="B8" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>352</v>
+        <v>112</v>
       </c>
       <c r="B9" s="3">
         <v>1</v>
@@ -5896,7 +6136,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="25" customWidth="1"/>
+    <col min="3" max="3" width="32" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -5908,10 +6148,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>368</v>
+        <v>388</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>26</v>
@@ -5923,10 +6163,10 @@
         <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>375</v>
+        <v>395</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>376</v>
+        <v>396</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>21</v>
@@ -5943,31 +6183,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>377</v>
+        <v>397</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>378</v>
+        <v>398</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>145</v>
+        <v>60</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>379</v>
+        <v>399</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>380</v>
+        <v>400</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>381</v>
+        <v>401</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>156</v>
+        <v>402</v>
       </c>
     </row>
     <row r="3">
@@ -5975,31 +6215,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>382</v>
+        <v>403</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>383</v>
+        <v>172</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>60</v>
+        <v>153</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>384</v>
+        <v>399</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>385</v>
+        <v>404</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>386</v>
+        <v>405</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>387</v>
+        <v>164</v>
       </c>
     </row>
     <row r="4">
@@ -6007,31 +6247,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>388</v>
+        <v>406</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>160</v>
+        <v>407</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>145</v>
+        <v>170</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>384</v>
+        <v>408</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>389</v>
+        <v>409</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>390</v>
+        <v>410</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>156</v>
+        <v>240</v>
       </c>
     </row>
     <row r="5">
@@ -6039,31 +6279,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>391</v>
+        <v>411</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>195</v>
+        <v>412</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>392</v>
+        <v>60</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>393</v>
+        <v>408</v>
       </c>
       <c r="F5" s="3">
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>394</v>
+        <v>413</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>395</v>
+        <v>414</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>176</v>
+        <v>264</v>
       </c>
     </row>
     <row r="6">
@@ -6071,31 +6311,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>91</v>
+        <v>415</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>86</v>
+        <v>416</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>87</v>
+        <v>356</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="F6" s="3">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>397</v>
+        <v>417</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>94</v>
+        <v>418</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>95</v>
+        <v>159</v>
       </c>
     </row>
     <row r="7">
@@ -6103,31 +6343,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>42</v>
+        <v>318</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>35</v>
+        <v>319</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>36</v>
+        <v>153</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="F7" s="3">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>398</v>
+        <v>419</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>45</v>
+        <v>320</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>46</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8">
@@ -6135,31 +6375,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>399</v>
+        <v>91</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>400</v>
+        <v>86</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>145</v>
+        <v>87</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>401</v>
+        <v>420</v>
       </c>
       <c r="F8" s="3">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>402</v>
+        <v>421</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>403</v>
+        <v>94</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>404</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9">
@@ -6167,31 +6407,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>405</v>
+        <v>422</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>177</v>
+        <v>423</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>204</v>
+        <v>424</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>379</v>
+        <v>420</v>
       </c>
       <c r="F9" s="3">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>406</v>
+        <v>425</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>407</v>
+        <v>426</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="10">
@@ -6199,31 +6439,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>379</v>
-      </c>
       <c r="F10" s="3">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>409</v>
+        <v>428</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>410</v>
+        <v>429</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>411</v>
+        <v>196</v>
       </c>
     </row>
     <row r="11">
@@ -6231,31 +6471,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>412</v>
+        <v>42</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>413</v>
+        <v>35</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>145</v>
+        <v>36</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>384</v>
+        <v>420</v>
       </c>
       <c r="F11" s="3">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>415</v>
+        <v>45</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>84</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12">
@@ -6263,31 +6503,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>399</v>
+        <v>431</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>416</v>
+        <v>432</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>417</v>
+        <v>153</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="F12" s="3">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>418</v>
+        <v>433</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>419</v>
+        <v>434</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>420</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13">
@@ -6295,31 +6535,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>421</v>
+        <v>435</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>195</v>
+        <v>436</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>145</v>
+        <v>437</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>401</v>
+        <v>420</v>
       </c>
       <c r="F13" s="3">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>422</v>
+        <v>438</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>423</v>
+        <v>439</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>162</v>
+        <v>246</v>
       </c>
     </row>
     <row r="14">
@@ -6327,31 +6567,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>58</v>
+        <v>440</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>59</v>
+        <v>441</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>60</v>
+        <v>153</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>379</v>
+        <v>420</v>
       </c>
       <c r="F14" s="3">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>424</v>
+        <v>442</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>62</v>
+        <v>443</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>63</v>
+        <v>444</v>
       </c>
     </row>
     <row r="15">
@@ -6359,31 +6599,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>425</v>
+        <v>445</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>401</v>
+        <v>420</v>
       </c>
       <c r="F15" s="3">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>427</v>
+        <v>442</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>428</v>
+        <v>446</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>73</v>
+        <v>225</v>
       </c>
     </row>
     <row r="16">
@@ -6391,31 +6631,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>429</v>
+        <v>352</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>275</v>
+        <v>181</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>145</v>
+        <v>170</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="F16" s="3">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>430</v>
+        <v>447</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>431</v>
+        <v>358</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>432</v>
+        <v>164</v>
       </c>
     </row>
     <row r="17">
@@ -6423,31 +6663,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>433</v>
+        <v>448</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>434</v>
+        <v>35</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>158</v>
+        <v>36</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>379</v>
+        <v>408</v>
       </c>
       <c r="F17" s="3">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>435</v>
+        <v>449</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>436</v>
+        <v>450</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>437</v>
+        <v>451</v>
       </c>
     </row>
     <row r="18">
@@ -6455,31 +6695,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>438</v>
+        <v>452</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>439</v>
+        <v>453</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>351</v>
+        <v>454</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>379</v>
+        <v>399</v>
       </c>
       <c r="F18" s="3">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>440</v>
+        <v>455</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>441</v>
+        <v>456</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>442</v>
+        <v>457</v>
       </c>
     </row>
     <row r="19">
@@ -6487,31 +6727,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>443</v>
+        <v>458</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>444</v>
+        <v>459</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>445</v>
+        <v>153</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>401</v>
+        <v>420</v>
       </c>
       <c r="F19" s="3">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>446</v>
+        <v>460</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>447</v>
+        <v>461</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>448</v>
+        <v>462</v>
       </c>
     </row>
     <row r="20">
@@ -6519,31 +6759,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>449</v>
+        <v>463</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>450</v>
+        <v>464</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="F20" s="3">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>451</v>
+        <v>465</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>452</v>
+        <v>466</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>181</v>
+        <v>467</v>
       </c>
     </row>
     <row r="21">
@@ -6551,31 +6791,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>453</v>
+        <v>468</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>454</v>
+        <v>160</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>417</v>
+        <v>290</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="F21" s="3">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>455</v>
+        <v>469</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>456</v>
+        <v>470</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>457</v>
+        <v>300</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W32.xlsx
+++ b/reports/devops-jobs-israel-2026-W32.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="474">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-04T08:50:11</t>
+    <t xml:space="preserve">2026-08-05T08:47:59</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Junior %</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0%</t>
+    <t xml:space="preserve">1.1%</t>
   </si>
   <si>
     <t xml:space="preserve">Salary disclosure rate %</t>
@@ -477,78 +477,72 @@
     <t xml:space="preserve">https://job-boards.greenhouse.io/melio/jobs/7747499003</t>
   </si>
   <si>
-    <t xml:space="preserve">Connecteam</t>
+    <t xml:space="preserve">NVIDIA AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-ai-4445021674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kiryat Ata, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4437329124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checkmarx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-checkmarx-4439196775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-engineer-at-thales-4343562293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medulla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-medulla-4448331135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wiliot</t>
   </si>
   <si>
     <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4428832411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-ai-4445021674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kiryat Ata, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4437329124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Checkmarx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-checkmarx-4439196775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medulla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-medulla-4448331135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check Point Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-check-point-software-4446179787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wiliot</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiliot-4446820849</t>
   </si>
   <si>
@@ -570,6 +564,39 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4445878493</t>
   </si>
   <si>
+    <t xml:space="preserve">Moon Active</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-moon-active-4447023421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer – Embedded Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-%E2%80%93-embedded-systems-at-abra-4446717885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevSecOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Playtika</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-at-playtika-4417616851</t>
+  </si>
+  <si>
     <t xml:space="preserve">Azure DevOps Administrator</t>
   </si>
   <si>
@@ -582,61 +609,67 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/azure-devops-administrator-at-one-systems-4440105641</t>
   </si>
   <si>
-    <t xml:space="preserve">DevSecOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Playtika</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-at-playtika-4417616851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
+    <t xml:space="preserve">Cloud engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dataspan.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-dataspan-ai-4448953842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aidoc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-aidoc-4449444867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-checkmarx-4446765835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cato-networks-4430441382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OFFROAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-offroad-4448139496</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-abra-4447643479</t>
   </si>
   <si>
-    <t xml:space="preserve">Platform DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D-Fend Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-devops-engineer-at-d-fend-solutions-4447057704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps / Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blast Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-platform-engineer-at-blast-security-4445844401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cato-networks-4430441382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Personetics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-personetics-4428829912</t>
+    <t xml:space="preserve">ThetaRay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-thetaray-4446919831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KMS Lighthouse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-kms-lighthouse-4447696634</t>
   </si>
   <si>
     <t xml:space="preserve">WalkMe</t>
@@ -648,19 +681,250 @@
     <t xml:space="preserve">2026-05-31</t>
   </si>
   <si>
+    <t xml:space="preserve">Senior DevOps / Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lendbuzz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-site-reliability-engineer-sre-at-lendbuzz-4437323317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teads</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-at-teads-4436613100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Head of DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fluent Trade Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-at-fluent-trade-technologies-4372997510</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alpha | Similarweb Partner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-alpha-similarweb-partner-4447362032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bridgify</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-bridgify-4441525178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bagira</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-bagira-4368663100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-23</t>
+  </si>
+  <si>
     <t xml:space="preserve">SecuriThings</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-securithings-4446720959</t>
   </si>
   <si>
-    <t xml:space="preserve">Earnix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-earnix-4437761619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-09</t>
+    <t xml:space="preserve">Senior DevOps Engineer / Technical Lead (AWS &amp; GCP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AnyClip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ness Ziona, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-technical-lead-aws-gcp-at-anyclip-4446636401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior SRE &amp; Linux Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-linux-infrastructure-engineer-at-mobileye-4439143553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cyber-Hive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-cyber-hive-4447364753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE Technical Lead, DevOps Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BigPanda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-technical-lead-devops-group-at-bigpanda-4447980511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior SRE (IT Infrastructure)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-it-infrastructure-at-palo-alto-networks-4387086808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4410866558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps SRE Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Axon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-sre-engineer-at-axon-4440000142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SciPlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-sciplay-4391151881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viz.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-viz-ai-4437383686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DataTeam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-devops-at-datateam-4447383004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineer III, Platform Engineering and Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-iii-platform-engineering-and-infrastructure-at-google-4448296220</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Streaming Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VIDAA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/streaming-platform-engineer-at-vidaa-4444520220</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps / Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tipuli Tech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-engineer-at-tipuli-tech-4447115888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harmonic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-harmonic-4360460066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Automation Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon Web Services (AWS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-automation-engineer-at-amazon-web-services-aws-4448323071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Infrastructure &amp; Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-cloud-engineer-at-moon-active-4447031167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lead Data Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Log-On Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lead-data-platform-engineer-at-log-on-software-4446211103</t>
   </si>
   <si>
     <t xml:space="preserve">DevOps Engineer – AWS</t>
@@ -675,768 +939,456 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-%E2%80%93-aws-at-ur-tech-jobs-4447639616</t>
   </si>
   <si>
-    <t xml:space="preserve">Bridgify</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-bridgify-4441525178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yad2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-yad2-4439486812</t>
+    <t xml:space="preserve">Horizon Technologies LTD.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-architect-at-horizon-technologies-ltd-4446611841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Security Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-at-log-on-software-4445889868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reline IT Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nes Ziona, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-reline-it-solutions-4447375577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Linux Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weizmann Institute of Science</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-linux-administrator-at-weizmann-institute-of-science-4444102865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YouCC Technologies Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashkelon, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ot-infrastructure-engineer-at-youcc-technologies-ltd-4448836015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-infrastructure-engineer-at-nebius-4437660618</t>
   </si>
   <si>
     <t xml:space="preserve">2026-07-15</t>
   </si>
   <si>
+    <t xml:space="preserve">Data Center IT Infrastructure Engineer (Modiin)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-infrastructure-engineer-modiin-at-nebius-4437655743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Technology Infrastructure Engineer - 24262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-infrastructure-engineer-24262-at-comblack-4448306072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calanit by one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-calanit-by-one-4448158765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">איש.אשת DevOps Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dahan Lab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%90%D7%99%D7%A9-%D7%90%D7%A9%D7%AA-devops-linux-at-dahan-lab-4449061474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unilink Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-unilink-ltd-4446581282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Network Infrastructure Engineer - 20690</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-infrastructure-engineer-20690-at-comblack-4448189250</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-gotfriends-4445849138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group Leader - Cloud Platform &amp; SRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/group-leader-cloud-platform-sre-at-confidential-4434818632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4429844723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oasis Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-oasis-security-4431605535</t>
+  </si>
+  <si>
     <t xml:space="preserve">Assured Allies</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-assured-allies-4447671142</t>
   </si>
   <si>
-    <t xml:space="preserve">Pagaya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-pagaya-4316888825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Infrastructure &amp; Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moon Active</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-cloud-engineer-at-moon-active-4447031167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oasis Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-oasis-security-4431605535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader - Infra and DevEx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kaltura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-infra-and-devex-at-kaltura-4442712745</t>
+    <t xml:space="preserve">DevOps Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZOLL Medical Corporation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-zoll-medical-corporation-4399156755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior AI SRE Developer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helfy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Virtualization, Active Directory, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator - Linux, Windows #1350</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-linux-windows-%231350-at-rad-4443763825</t>
   </si>
   <si>
     <t xml:space="preserve">2026-07-23</t>
   </si>
   <si>
-    <t xml:space="preserve">DevOps Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZOLL Medical Corporation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-zoll-medical-corporation-4399156755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aidoc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-aidoc-4437791495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-gotfriends-4445872562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps / Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lendbuzz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-site-reliability-engineer-sre-at-lendbuzz-4437323317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Linux Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weizmann Institute of Science</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-linux-administrator-at-weizmann-institute-of-science-4444102865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps SRE Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Axon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-sre-engineer-at-axon-4440000142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior\Lead DevOps Engineer</t>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test Environment Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Networking, Monitoring, Databases, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/test-environment-support-engineer-at-abra-4442615924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autobrains Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4440209390</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation student- Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-jerusalem-at-radware-4440152008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud &amp; AI Security Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4932015101?gh_jid=4932015101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-4428415454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator &amp; IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inManage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">etoro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-etoro-4434952696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations Engineer I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Innovid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-engineer-i-at-innovid-4443857656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations &amp; Helpdesk Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claroty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-helpdesk-engineer-at-claroty-4412805136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineer - Unmanned Maritime Systems</t>
   </si>
   <si>
     <t xml:space="preserve">Elbit Systems Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-lead-devops-engineer-at-elbit-systems-israel-4375574113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-checkmarx-4446765835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. SRE AI Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-sre-ai-engineer-at-navan-4437742346</t>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Docker, Kubernetes, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-unmanned-maritime-systems-at-elbit-systems-israel-4433797145</t>
   </si>
   <si>
     <t xml:space="preserve">2026-07-07</t>
   </si>
   <si>
-    <t xml:space="preserve">Sr. Principal, DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parallel Wireless</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-principal-devops-at-parallel-wireless-4437772282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-moon-active-4447023421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teads</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-at-teads-4436613100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4429844723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SciPlay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-sciplay-4391151881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viz.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-viz-ai-4437383686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4410866558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobileye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-mobileye-4436210389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior AI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-platform-engineer-at-nvidia-4434371817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Security - AI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-security-ai-platform-engineer-at-cato-networks-4416844175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps / Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tipuli Tech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-engineer-at-tipuli-tech-4447115888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akeyless Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-akeyless-security-4445763841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harmonic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-harmonic-4360460066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ThetaRay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-thetaray-4446919831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YouCC Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashkelon, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ot-infrastructure-engineer-at-youcc-technologies-ltd-4448836015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-infrastructure-engineer-at-nebius-4437660611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Infrastructure Engineer (Modiin)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-infrastructure-engineer-modiin-at-nebius-4437655743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology Infrastructure Engineer - 24262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-infrastructure-engineer-24262-at-comblack-4448306072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior SRE &amp; Linux Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-linux-infrastructure-engineer-at-mobileye-4439143553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Computer System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Camtek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System Engineer (10272)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bynet Data Communications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-10272-at-bynet-data-communications-4446207580</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allpha Innovation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-allpha-innovation-4448822755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GE HealthCare</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-ge-healthcare-4448609363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">‫System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JobsSeek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%E2%80%ABsystem-engineer-at-jobsseek-4427766128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unilink Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-unilink-ltd-4446581282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Network Infrastructure Engineer - 20690</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-infrastructure-engineer-20690-at-comblack-4448189250</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-gotfriends-4445849138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE Technical Lead, DevOps Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BigPanda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-technical-lead-devops-group-at-bigpanda-4447980511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Group Leader - Cloud Platform &amp; SRE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/group-leader-cloud-platform-sre-at-confidential-4434818632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bagira</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-bagira-4368663100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KMS Lighthouse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-kms-lighthouse-4447696634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Automation Engineer - Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-automation-engineer-networking-at-cato-networks-4378169465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior SRE (IT Infrastructure)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-it-infrastructure-at-palo-alto-networks-4387086808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.4%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior AI SRE Developer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helfy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Full Stack Developer - Data Loss Prevention Cloud Service</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-full-stack-developer-data-loss-prevention-cloud-service-at-check-point-software-4446847161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator - Linux, Windows #1350</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-linux-windows-%231350-at-rad-4443763825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calanit by one</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Virtualization, Active Directory, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-calanit-by-one-4448158765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Waterfall Security Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-position-at-waterfall-security-solutions-4444878648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer – Test Environments</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Monitoring, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-%E2%80%93-test-environments-at-comblack-4446757352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Technical Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4442889333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior QA Engineer - Student Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fives</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-qa-engineer-student-position-at-fives-4436801163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation student- Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-jerusalem-at-radware-4440152008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-at-radware-4437695096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud &amp; AI Security Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4932015101?gh_jid=4932015101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414157765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IOT student tester</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Motorola Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/iot-student-tester-at-motorola-solutions-4434451222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator &amp; IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inManage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-4428415454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
     <t xml:space="preserve">Roles requiring it</t>
   </si>
   <si>
@@ -1446,6 +1398,9 @@
     <t xml:space="preserve">Cloud (any)</t>
   </si>
   <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bash/Shell</t>
   </si>
   <si>
@@ -1455,13 +1410,10 @@
     <t xml:space="preserve">Monitoring</t>
   </si>
   <si>
-    <t xml:space="preserve">Active Directory</t>
+    <t xml:space="preserve">Virtualization</t>
   </si>
   <si>
     <t xml:space="preserve">Git</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Virtualization</t>
   </si>
   <si>
     <t xml:space="preserve">Elapsed (s)</t>
@@ -1613,7 +1565,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7">
@@ -1621,7 +1573,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
@@ -1629,7 +1581,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9">
@@ -1637,7 +1589,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>1197</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="10">
@@ -1709,7 +1661,7 @@
         <v>23</v>
       </c>
       <c r="B19" s="3">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20">
@@ -1736,39 +1688,39 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>390</v>
+        <v>376</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>471</v>
+        <v>406</v>
       </c>
       <c r="B2" s="3">
-        <v>21</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>408</v>
+        <v>391</v>
       </c>
       <c r="B3" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>420</v>
+        <v>402</v>
       </c>
       <c r="B4" s="3">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>399</v>
+        <v>385</v>
       </c>
       <c r="B5" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -1784,39 +1736,39 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>376</v>
+        <v>361</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>472</v>
+        <v>456</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>473</v>
+        <v>457</v>
       </c>
       <c r="B2" s="3">
-        <v>32</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>381</v>
+        <v>369</v>
       </c>
       <c r="B3" s="3">
-        <v>27</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>474</v>
+        <v>458</v>
       </c>
       <c r="B4" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>371</v>
+        <v>459</v>
       </c>
       <c r="B5" s="3">
         <v>25</v>
@@ -1824,90 +1776,90 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>254</v>
+        <v>366</v>
       </c>
       <c r="B6" s="3">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>475</v>
+        <v>460</v>
       </c>
       <c r="B7" s="3">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>476</v>
+        <v>252</v>
       </c>
       <c r="B8" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>477</v>
+        <v>461</v>
       </c>
       <c r="B9" s="3">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>478</v>
+        <v>462</v>
       </c>
       <c r="B10" s="3">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>378</v>
+        <v>194</v>
       </c>
       <c r="B11" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>479</v>
+        <v>363</v>
       </c>
       <c r="B12" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>380</v>
+        <v>304</v>
       </c>
       <c r="B13" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>216</v>
+        <v>463</v>
       </c>
       <c r="B14" s="3">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>185</v>
+        <v>464</v>
       </c>
       <c r="B15" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>480</v>
+        <v>365</v>
       </c>
       <c r="B16" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1932,13 +1884,13 @@
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>481</v>
+        <v>465</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>482</v>
+        <v>466</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>483</v>
+        <v>467</v>
       </c>
     </row>
     <row r="2">
@@ -1949,10 +1901,10 @@
         <v>26</v>
       </c>
       <c r="C2" s="3">
-        <v>13.2</v>
+        <v>12.9</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>484</v>
+        <v>468</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -1961,88 +1913,88 @@
         <v>23</v>
       </c>
       <c r="B3" s="3">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C3" s="3">
-        <v>35.0</v>
+        <v>28.7</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>484</v>
+        <v>468</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>485</v>
+        <v>469</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>8.0</v>
+        <v>8.3</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>484</v>
+        <v>468</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>486</v>
+        <v>470</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>484</v>
+        <v>468</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>487</v>
+        <v>471</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>37.6</v>
+        <v>35.5</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>484</v>
+        <v>468</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>488</v>
+        <v>472</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>16.5</v>
+        <v>18.2</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>484</v>
+        <v>468</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>489</v>
+        <v>473</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>28.4</v>
+        <v>17.2</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>484</v>
+        <v>468</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2126,7 +2078,7 @@
         <v>41</v>
       </c>
       <c r="J2" s="3">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3">
@@ -2158,7 +2110,7 @@
         <v>46</v>
       </c>
       <c r="J3" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -2190,7 +2142,7 @@
         <v>52</v>
       </c>
       <c r="J4" s="3">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5">
@@ -2222,7 +2174,7 @@
         <v>41</v>
       </c>
       <c r="J5" s="3">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6">
@@ -2254,7 +2206,7 @@
         <v>41</v>
       </c>
       <c r="J6" s="3">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7">
@@ -2286,7 +2238,7 @@
         <v>63</v>
       </c>
       <c r="J7" s="3">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8">
@@ -2318,7 +2270,7 @@
         <v>41</v>
       </c>
       <c r="J8" s="3">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9">
@@ -2350,7 +2302,7 @@
         <v>73</v>
       </c>
       <c r="J9" s="3">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10">
@@ -2382,7 +2334,7 @@
         <v>77</v>
       </c>
       <c r="J10" s="3">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11">
@@ -2414,7 +2366,7 @@
         <v>73</v>
       </c>
       <c r="J11" s="3">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12">
@@ -2446,7 +2398,7 @@
         <v>84</v>
       </c>
       <c r="J12" s="3">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13">
@@ -2478,7 +2430,7 @@
         <v>90</v>
       </c>
       <c r="J13" s="3">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14">
@@ -2510,7 +2462,7 @@
         <v>95</v>
       </c>
       <c r="J14" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
@@ -2542,7 +2494,7 @@
         <v>46</v>
       </c>
       <c r="J15" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16">
@@ -2574,7 +2526,7 @@
         <v>102</v>
       </c>
       <c r="J16" s="3">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="17">
@@ -2606,7 +2558,7 @@
         <v>77</v>
       </c>
       <c r="J17" s="3">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="18">
@@ -2638,7 +2590,7 @@
         <v>109</v>
       </c>
       <c r="J18" s="3">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="19">
@@ -2670,7 +2622,7 @@
         <v>115</v>
       </c>
       <c r="J19" s="3">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20">
@@ -2702,7 +2654,7 @@
         <v>41</v>
       </c>
       <c r="J20" s="3">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="21">
@@ -2734,7 +2686,7 @@
         <v>125</v>
       </c>
       <c r="J21" s="3">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22">
@@ -2766,7 +2718,7 @@
         <v>130</v>
       </c>
       <c r="J22" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -2798,7 +2750,7 @@
         <v>136</v>
       </c>
       <c r="J23" s="3">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="24">
@@ -2828,7 +2780,7 @@
         <v>139</v>
       </c>
       <c r="J24" s="3">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="25">
@@ -2860,7 +2812,7 @@
         <v>41</v>
       </c>
       <c r="J25" s="3">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="26">
@@ -2890,7 +2842,7 @@
         <v>147</v>
       </c>
       <c r="J26" s="3">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="27">
@@ -2922,7 +2874,7 @@
         <v>77</v>
       </c>
       <c r="J27" s="3">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="28">
@@ -2936,7 +2888,7 @@
         <v>153</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>43</v>
@@ -2952,7 +2904,7 @@
         <v>155</v>
       </c>
       <c r="J28" s="3">
-        <v>50</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2966,7 +2918,7 @@
         <v>157</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>37</v>
+        <v>158</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>43</v>
@@ -2976,13 +2928,13 @@
         <v>23</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J29" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -2990,13 +2942,13 @@
         <v>116</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>162</v>
+        <v>49</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>43</v>
@@ -3012,21 +2964,21 @@
         <v>164</v>
       </c>
       <c r="J30" s="3">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>116</v>
+        <v>165</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>43</v>
@@ -3036,13 +2988,13 @@
         <v>23</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>168</v>
+        <v>84</v>
       </c>
       <c r="J31" s="3">
-        <v>21</v>
+        <v>82</v>
       </c>
     </row>
     <row r="32">
@@ -3072,7 +3024,7 @@
         <v>130</v>
       </c>
       <c r="J32" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -3083,7 +3035,7 @@
         <v>172</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>153</v>
+        <v>173</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>49</v>
@@ -3096,10 +3048,10 @@
         <v>23</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="J33" s="3">
         <v>6</v>
@@ -3110,13 +3062,13 @@
         <v>116</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>153</v>
+        <v>177</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>43</v>
@@ -3126,13 +3078,13 @@
         <v>23</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>177</v>
+        <v>155</v>
       </c>
       <c r="J34" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -3140,10 +3092,10 @@
         <v>116</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>122</v>
@@ -3159,10 +3111,10 @@
         <v>180</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="J35" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -3173,10 +3125,10 @@
         <v>181</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>43</v>
@@ -3189,50 +3141,48 @@
         <v>182</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>159</v>
+        <v>183</v>
       </c>
       <c r="J36" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>49</v>
+        <v>145</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F37" s="3" t="s">
-        <v>185</v>
-      </c>
+      <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>130</v>
+        <v>175</v>
       </c>
       <c r="J37" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>60</v>
@@ -3244,63 +3194,65 @@
         <v>43</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I38" s="3" t="s">
         <v>77</v>
       </c>
       <c r="J38" s="3">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>53</v>
+        <v>192</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F39" s="3"/>
+        <v>43</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>194</v>
+      </c>
       <c r="G39" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>164</v>
+        <v>130</v>
       </c>
       <c r="J39" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>157</v>
+        <v>173</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>43</v>
@@ -3310,24 +3262,24 @@
         <v>23</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="J40" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>197</v>
+        <v>53</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>49</v>
@@ -3340,24 +3292,24 @@
         <v>23</v>
       </c>
       <c r="H41" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="I41" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>159</v>
-      </c>
       <c r="J41" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>116</v>
+        <v>202</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>200</v>
+        <v>161</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>49</v>
@@ -3370,13 +3322,13 @@
         <v>23</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>202</v>
+        <v>183</v>
       </c>
       <c r="J42" s="3">
-        <v>46</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43">
@@ -3384,10 +3336,10 @@
         <v>116</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>204</v>
+        <v>170</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>49</v>
@@ -3403,42 +3355,40 @@
         <v>205</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>155</v>
+        <v>206</v>
       </c>
       <c r="J43" s="3">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>153</v>
+        <v>173</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>189</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>208</v>
+        <v>155</v>
       </c>
       <c r="J44" s="3">
-        <v>65</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -3446,13 +3396,13 @@
         <v>53</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>209</v>
+        <v>185</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>38</v>
@@ -3462,30 +3412,30 @@
         <v>23</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="J45" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>53</v>
+        <v>116</v>
       </c>
       <c r="B46" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="C46" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="C46" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="D46" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="s">
@@ -3495,72 +3445,72 @@
         <v>212</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>213</v>
+        <v>183</v>
       </c>
       <c r="J46" s="3">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C47" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="D47" s="3" t="s">
         <v>215</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>122</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F47" s="3" t="s">
+      <c r="F47" s="3"/>
+      <c r="G47" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H47" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>217</v>
-      </c>
       <c r="I47" s="3" t="s">
-        <v>164</v>
+        <v>130</v>
       </c>
       <c r="J47" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B48" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H48" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C48" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F48" s="3"/>
-      <c r="G48" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H48" s="3" t="s">
+      <c r="I48" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>159</v>
-      </c>
       <c r="J48" s="3">
-        <v>1</v>
+        <v>66</v>
       </c>
     </row>
     <row r="49">
@@ -3571,10 +3521,10 @@
         <v>221</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>222</v>
+        <v>173</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>223</v>
+        <v>49</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>38</v>
@@ -3584,57 +3534,57 @@
         <v>23</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="J49" s="3">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>53</v>
+        <v>224</v>
       </c>
       <c r="B50" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C50" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="C50" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="D50" s="3" t="s">
-        <v>49</v>
+        <v>227</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>159</v>
+        <v>229</v>
       </c>
       <c r="J50" s="3">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>53</v>
+        <v>230</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>153</v>
+        <v>186</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>49</v>
+        <v>145</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>38</v>
@@ -3644,43 +3594,43 @@
         <v>23</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>230</v>
+        <v>84</v>
       </c>
       <c r="J51" s="3">
-        <v>22</v>
+        <v>82</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>231</v>
+        <v>53</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>153</v>
+        <v>173</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="J52" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3688,10 +3638,10 @@
         <v>53</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>153</v>
+        <v>173</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>49</v>
@@ -3704,13 +3654,13 @@
         <v>23</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>236</v>
+        <v>155</v>
       </c>
       <c r="J53" s="3">
-        <v>42</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -3721,43 +3671,43 @@
         <v>238</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>166</v>
+        <v>239</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="J54" s="3">
-        <v>12</v>
+        <v>43</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>241</v>
+        <v>53</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>242</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>60</v>
+        <v>162</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
@@ -3767,143 +3717,145 @@
         <v>243</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>139</v>
+        <v>175</v>
       </c>
       <c r="J55" s="3">
-        <v>69</v>
+        <v>6</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>53</v>
+        <v>244</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>153</v>
+        <v>246</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F56" s="3"/>
+      <c r="F56" s="3" t="s">
+        <v>247</v>
+      </c>
       <c r="G56" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>246</v>
+        <v>199</v>
       </c>
       <c r="J56" s="3">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>220</v>
+        <v>249</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>181</v>
+        <v>250</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>170</v>
+        <v>251</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>49</v>
+        <v>145</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F57" s="3"/>
+      <c r="F57" s="3" t="s">
+        <v>252</v>
+      </c>
       <c r="G57" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>159</v>
+        <v>254</v>
       </c>
       <c r="J57" s="3">
-        <v>1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>153</v>
+        <v>257</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="J58" s="3">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>253</v>
+        <v>173</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>254</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>196</v>
+        <v>130</v>
       </c>
       <c r="J59" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>153</v>
+        <v>173</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>49</v>
@@ -3916,27 +3868,27 @@
         <v>23</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>168</v>
+        <v>77</v>
       </c>
       <c r="J60" s="3">
-        <v>21</v>
+        <v>69</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>260</v>
+        <v>156</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>262</v>
+        <v>122</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>38</v>
@@ -3946,54 +3898,54 @@
         <v>23</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>264</v>
+        <v>219</v>
       </c>
       <c r="J61" s="3">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>165</v>
+        <v>269</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>196</v>
+        <v>164</v>
       </c>
       <c r="J62" s="3">
-        <v>4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>267</v>
+        <v>53</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>153</v>
+        <v>173</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>49</v>
@@ -4006,27 +3958,27 @@
         <v>23</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>270</v>
+        <v>84</v>
       </c>
       <c r="J63" s="3">
-        <v>28</v>
+        <v>82</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>271</v>
+        <v>56</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>273</v>
+        <v>173</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>38</v>
@@ -4039,54 +3991,54 @@
         <v>274</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>246</v>
+        <v>84</v>
       </c>
       <c r="J64" s="3">
-        <v>27</v>
+        <v>82</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>116</v>
+        <v>56</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>232</v>
+        <v>275</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>153</v>
+        <v>173</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>196</v>
+        <v>229</v>
       </c>
       <c r="J65" s="3">
-        <v>4</v>
+        <v>24</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>261</v>
+        <v>170</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>262</v>
+        <v>49</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>43</v>
@@ -4096,117 +4048,117 @@
         <v>23</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>279</v>
+        <v>199</v>
       </c>
       <c r="J66" s="3">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>53</v>
+        <v>280</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>282</v>
+        <v>199</v>
       </c>
       <c r="J67" s="3">
-        <v>39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>53</v>
+        <v>283</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>153</v>
+        <v>170</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>84</v>
+        <v>183</v>
       </c>
       <c r="J68" s="3">
-        <v>81</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>56</v>
+        <v>286</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>153</v>
+        <v>257</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>84</v>
+        <v>160</v>
       </c>
       <c r="J69" s="3">
-        <v>81</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>56</v>
+        <v>289</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>153</v>
+        <v>291</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>49</v>
+        <v>158</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>38</v>
@@ -4216,54 +4168,54 @@
         <v>23</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>279</v>
+        <v>139</v>
       </c>
       <c r="J70" s="3">
-        <v>23</v>
+        <v>70</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>160</v>
+        <v>294</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>122</v>
+        <v>158</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="J71" s="3">
-        <v>65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>293</v>
+        <v>181</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>49</v>
@@ -4276,24 +4228,24 @@
         <v>23</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>270</v>
+        <v>183</v>
       </c>
       <c r="J72" s="3">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>160</v>
+        <v>300</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>290</v>
+        <v>177</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>122</v>
@@ -4306,86 +4258,86 @@
         <v>23</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>297</v>
+        <v>199</v>
       </c>
       <c r="J73" s="3">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>200</v>
+        <v>303</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>43</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>189</v>
+        <v>304</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>300</v>
+        <v>160</v>
       </c>
       <c r="J74" s="3">
-        <v>41</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>301</v>
+        <v>34</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F75" s="3"/>
       <c r="G75" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>164</v>
+        <v>199</v>
       </c>
       <c r="J75" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>116</v>
+        <v>309</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>49</v>
@@ -4393,59 +4345,61 @@
       <c r="E76" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F76" s="3"/>
+      <c r="F76" s="3" t="s">
+        <v>190</v>
+      </c>
       <c r="G76" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>174</v>
+        <v>199</v>
       </c>
       <c r="J76" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>162</v>
+        <v>122</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>139</v>
+        <v>199</v>
       </c>
       <c r="J77" s="3">
-        <v>69</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>116</v>
+        <v>315</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>312</v>
+        <v>167</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>122</v>
@@ -4453,29 +4407,31 @@
       <c r="E78" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F78" s="3"/>
+      <c r="F78" s="3" t="s">
+        <v>252</v>
+      </c>
       <c r="G78" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="J78" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>122</v>
@@ -4488,24 +4444,24 @@
         <v>23</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="I79" s="3" t="s">
         <v>130</v>
       </c>
       <c r="J79" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>153</v>
+        <v>173</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>49</v>
@@ -4518,24 +4474,24 @@
         <v>23</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="J80" s="3">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>122</v>
@@ -4548,24 +4504,24 @@
         <v>23</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="J81" s="3">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="B82" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="B82" s="3" t="s">
-        <v>323</v>
-      </c>
       <c r="C82" s="3" t="s">
-        <v>328</v>
+        <v>239</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>122</v>
@@ -4578,21 +4534,21 @@
         <v>23</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>225</v>
+        <v>330</v>
       </c>
       <c r="J82" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C83" s="3" t="s">
         <v>170</v>
@@ -4608,56 +4564,56 @@
         <v>23</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="I83" s="3" t="s">
         <v>130</v>
       </c>
       <c r="J83" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>293</v>
+        <v>337</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>334</v>
+        <v>307</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>145</v>
+        <v>122</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="G84" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>230</v>
+        <v>199</v>
       </c>
       <c r="J84" s="3">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>338</v>
+        <v>167</v>
       </c>
       <c r="D85" s="3" t="s">
         <v>122</v>
@@ -4665,26 +4621,28 @@
       <c r="E85" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F85" s="3"/>
+      <c r="F85" s="3" t="s">
+        <v>252</v>
+      </c>
       <c r="G85" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>115</v>
+        <v>199</v>
       </c>
       <c r="J85" s="3">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>340</v>
+        <v>311</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C86" s="3" t="s">
         <v>170</v>
@@ -4693,31 +4651,31 @@
         <v>49</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F86" s="3"/>
       <c r="G86" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="I86" s="3" t="s">
         <v>130</v>
       </c>
       <c r="J86" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>318</v>
+        <v>344</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>179</v>
+        <v>307</v>
       </c>
       <c r="D87" s="3" t="s">
         <v>122</v>
@@ -4730,27 +4688,27 @@
         <v>23</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="I87" s="3" t="s">
         <v>130</v>
       </c>
       <c r="J87" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>345</v>
+        <v>179</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>346</v>
+        <v>170</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>162</v>
+        <v>49</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>43</v>
@@ -4760,24 +4718,24 @@
         <v>23</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="I88" s="3" t="s">
         <v>130</v>
       </c>
       <c r="J88" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="B89" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="B89" s="3" t="s">
-        <v>349</v>
-      </c>
       <c r="C89" s="3" t="s">
-        <v>350</v>
+        <v>177</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>122</v>
@@ -4790,289 +4748,137 @@
         <v>23</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>213</v>
+        <v>350</v>
       </c>
       <c r="J89" s="3">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>352</v>
+        <v>53</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="D90" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F90" s="3"/>
       <c r="G90" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>130</v>
+        <v>353</v>
       </c>
       <c r="J90" s="3">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>355</v>
+        <v>53</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>331</v>
+        <v>354</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>356</v>
+        <v>173</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F91" s="3"/>
       <c r="G91" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>130</v>
+        <v>241</v>
       </c>
       <c r="J91" s="3">
-        <v>0</v>
+        <v>43</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>352</v>
+        <v>53</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>181</v>
+        <v>356</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="D92" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F92" s="3"/>
       <c r="G92" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>130</v>
+        <v>155</v>
       </c>
       <c r="J92" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="B93" s="3" t="s">
         <v>359</v>
       </c>
-      <c r="B93" s="3" t="s">
-        <v>360</v>
-      </c>
       <c r="C93" s="3" t="s">
-        <v>153</v>
+        <v>60</v>
       </c>
       <c r="D93" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F93" s="3"/>
       <c r="G93" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="J93" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="B94" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="C94" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="D94" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F94" s="3"/>
-      <c r="G94" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="J94" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="B95" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="D95" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="E95" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F95" s="3"/>
-      <c r="G95" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H95" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="I95" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="J95" s="3">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="B96" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="C96" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="D96" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="E96" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F96" s="3"/>
-      <c r="G96" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H96" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="I96" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="B97" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="C97" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="D97" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E97" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F97" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="G97" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H97" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="I97" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="J97" s="3">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="B98" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="C98" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="D98" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E98" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F98" s="3"/>
-      <c r="G98" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H98" s="3" t="s">
-        <v>375</v>
-      </c>
-      <c r="I98" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="J98" s="3">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J98"/>
+  <autoFilter ref="A1:J93"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5166,11 +4972,6 @@
     <hyperlink ref="H91" r:id="rId90"/>
     <hyperlink ref="H92" r:id="rId91"/>
     <hyperlink ref="H93" r:id="rId92"/>
-    <hyperlink ref="H94" r:id="rId93"/>
-    <hyperlink ref="H95" r:id="rId94"/>
-    <hyperlink ref="H96" r:id="rId95"/>
-    <hyperlink ref="H97" r:id="rId96"/>
-    <hyperlink ref="H98" r:id="rId97"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5178,8 +4979,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="56" customWidth="1"/>
-    <col min="2" max="2" width="27" customWidth="1"/>
+    <col min="1" max="1" width="60" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -5212,32 +5013,32 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>126</v>
+        <v>196</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>127</v>
+        <v>197</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>87</v>
+        <v>173</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>129</v>
+        <v>198</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>116</v>
+        <v>53</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>169</v>
+        <v>200</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -5245,18 +5046,18 @@
         <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>171</v>
+        <v>201</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>183</v>
+        <v>53</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>184</v>
+        <v>233</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -5264,18 +5065,18 @@
         <v>23</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>186</v>
+        <v>234</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>314</v>
+        <v>244</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>315</v>
+        <v>245</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>316</v>
+        <v>246</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5283,18 +5084,18 @@
         <v>23</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>317</v>
+        <v>248</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>330</v>
+        <v>255</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>331</v>
+        <v>256</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>170</v>
+        <v>257</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -5302,15 +5103,15 @@
         <v>23</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>332</v>
+        <v>258</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>340</v>
+        <v>277</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>341</v>
+        <v>278</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>170</v>
@@ -5321,18 +5122,18 @@
         <v>23</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>342</v>
+        <v>279</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>318</v>
+        <v>280</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>343</v>
+        <v>281</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>179</v>
+        <v>162</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -5340,18 +5141,18 @@
         <v>23</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>344</v>
+        <v>282</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>318</v>
+        <v>293</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>345</v>
+        <v>294</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>346</v>
+        <v>295</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -5359,18 +5160,18 @@
         <v>23</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>347</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>352</v>
+        <v>299</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>353</v>
+        <v>300</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -5378,18 +5179,18 @@
         <v>23</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>354</v>
+        <v>301</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>355</v>
+        <v>34</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>331</v>
+        <v>306</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>356</v>
+        <v>307</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -5397,15 +5198,15 @@
         <v>23</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>357</v>
+        <v>308</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>352</v>
+        <v>309</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>181</v>
+        <v>300</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>170</v>
@@ -5416,18 +5217,18 @@
         <v>23</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>358</v>
+        <v>310</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>359</v>
+        <v>311</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>360</v>
+        <v>312</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>153</v>
+        <v>313</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
@@ -5435,18 +5236,18 @@
         <v>23</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>361</v>
+        <v>314</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>265</v>
+        <v>336</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>368</v>
+        <v>337</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
@@ -5454,11 +5255,30 @@
         <v>23</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>369</v>
+        <v>338</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>341</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G14"/>
+  <autoFilter ref="A1:G15"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -5473,6 +5293,7 @@
     <hyperlink ref="G12" r:id="rId11"/>
     <hyperlink ref="G13" r:id="rId12"/>
     <hyperlink ref="G14" r:id="rId13"/>
+    <hyperlink ref="G15" r:id="rId14"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5486,15 +5307,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>376</v>
+        <v>361</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>377</v>
+        <v>362</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>189</v>
+        <v>304</v>
       </c>
       <c r="B2" s="3">
         <v>16</v>
@@ -5502,15 +5323,15 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>216</v>
+        <v>190</v>
       </c>
       <c r="B3" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>378</v>
+        <v>363</v>
       </c>
       <c r="B4" s="3">
         <v>15</v>
@@ -5518,7 +5339,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>379</v>
+        <v>364</v>
       </c>
       <c r="B5" s="3">
         <v>14</v>
@@ -5526,15 +5347,15 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>380</v>
+        <v>252</v>
       </c>
       <c r="B6" s="3">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>254</v>
+        <v>365</v>
       </c>
       <c r="B7" s="3">
         <v>11</v>
@@ -5542,7 +5363,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>381</v>
+        <v>366</v>
       </c>
       <c r="B8" s="3">
         <v>10</v>
@@ -5550,7 +5371,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="B9" s="3">
         <v>9</v>
@@ -5558,7 +5379,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>382</v>
+        <v>367</v>
       </c>
       <c r="B10" s="3">
         <v>9</v>
@@ -5566,15 +5387,15 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>383</v>
+        <v>368</v>
       </c>
       <c r="B11" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>371</v>
+        <v>150</v>
       </c>
       <c r="B12" s="3">
         <v>8</v>
@@ -5582,15 +5403,15 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>150</v>
+        <v>369</v>
       </c>
       <c r="B13" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>384</v>
+        <v>370</v>
       </c>
       <c r="B14" s="3">
         <v>6</v>
@@ -5598,7 +5419,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>385</v>
+        <v>371</v>
       </c>
       <c r="B15" s="3">
         <v>5</v>
@@ -5606,7 +5427,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>386</v>
+        <v>372</v>
       </c>
       <c r="B16" s="3">
         <v>4</v>
@@ -5628,7 +5449,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>387</v>
+        <v>373</v>
       </c>
     </row>
     <row r="2">
@@ -5665,31 +5486,31 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>160</v>
+        <v>35</v>
       </c>
       <c r="B6" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>181</v>
+        <v>104</v>
       </c>
       <c r="B7" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>200</v>
+        <v>156</v>
       </c>
       <c r="B8" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>35</v>
+        <v>161</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
@@ -5697,7 +5518,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>104</v>
+        <v>179</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -5705,7 +5526,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5713,7 +5534,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>232</v>
+        <v>185</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5721,7 +5542,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -5729,7 +5550,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -5737,7 +5558,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -5766,16 +5587,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>388</v>
+        <v>374</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>389</v>
+        <v>375</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>387</v>
+        <v>373</v>
       </c>
     </row>
     <row r="2">
@@ -5867,13 +5688,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="C8" s="3">
-        <v>5.0</v>
+        <v>3.1</v>
       </c>
       <c r="D8" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -5881,13 +5702,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>160</v>
+        <v>117</v>
       </c>
       <c r="C9" s="3">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="D9" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -5895,13 +5716,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>181</v>
+        <v>156</v>
       </c>
       <c r="C10" s="3">
-        <v>4.2</v>
+        <v>2.8</v>
       </c>
       <c r="D10" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -5909,10 +5730,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>293</v>
+        <v>185</v>
       </c>
       <c r="C11" s="3">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="D11" s="3">
         <v>2</v>
@@ -5923,10 +5744,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="C12" s="3">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="D12" s="3">
         <v>1</v>
@@ -5937,13 +5758,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>127</v>
+        <v>161</v>
       </c>
       <c r="C13" s="3">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="D13" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -5951,7 +5772,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="C14" s="3">
         <v>2.4</v>
@@ -5965,7 +5786,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>232</v>
+        <v>181</v>
       </c>
       <c r="C15" s="3">
         <v>2.4</v>
@@ -5979,7 +5800,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="C16" s="3">
         <v>2.4</v>
@@ -6005,10 +5826,10 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>390</v>
+        <v>376</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>391</v>
+        <v>377</v>
       </c>
     </row>
     <row r="2">
@@ -6030,7 +5851,7 @@
         <v>50</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>392</v>
+        <v>378</v>
       </c>
     </row>
     <row r="4">
@@ -6038,10 +5859,10 @@
         <v>38</v>
       </c>
       <c r="B4" s="3">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>393</v>
+        <v>379</v>
       </c>
     </row>
   </sheetData>
@@ -6060,7 +5881,7 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>390</v>
+        <v>376</v>
       </c>
     </row>
     <row r="2">
@@ -6068,7 +5889,7 @@
         <v>49</v>
       </c>
       <c r="B2" s="3">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3">
@@ -6076,12 +5897,12 @@
         <v>122</v>
       </c>
       <c r="B3" s="3">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>37</v>
+        <v>145</v>
       </c>
       <c r="B4" s="3">
         <v>4</v>
@@ -6089,7 +5910,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>162</v>
+        <v>37</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -6097,31 +5918,31 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="B6" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>223</v>
+        <v>112</v>
       </c>
       <c r="B7" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>262</v>
+        <v>215</v>
       </c>
       <c r="B8" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>112</v>
+        <v>227</v>
       </c>
       <c r="B9" s="3">
         <v>1</v>
@@ -6136,7 +5957,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="32" customWidth="1"/>
+    <col min="3" max="3" width="31" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -6148,10 +5969,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>388</v>
+        <v>374</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>394</v>
+        <v>380</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>26</v>
@@ -6163,10 +5984,10 @@
         <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>395</v>
+        <v>381</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>396</v>
+        <v>382</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>21</v>
@@ -6183,31 +6004,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>397</v>
+        <v>383</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>398</v>
+        <v>384</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>60</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>399</v>
+        <v>385</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>400</v>
+        <v>386</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>401</v>
+        <v>387</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>402</v>
+        <v>388</v>
       </c>
     </row>
     <row r="3">
@@ -6215,31 +6036,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>403</v>
+        <v>389</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>172</v>
+        <v>390</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>153</v>
+        <v>60</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>404</v>
+        <v>392</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>405</v>
+        <v>393</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>164</v>
+        <v>394</v>
       </c>
     </row>
     <row r="4">
@@ -6247,31 +6068,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>406</v>
+        <v>336</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>407</v>
+        <v>337</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>170</v>
+        <v>307</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>408</v>
+        <v>391</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>409</v>
+        <v>395</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>410</v>
+        <v>338</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>240</v>
+        <v>155</v>
       </c>
     </row>
     <row r="5">
@@ -6279,31 +6100,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>411</v>
+        <v>396</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>412</v>
+        <v>397</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>60</v>
+        <v>170</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>408</v>
+        <v>391</v>
       </c>
       <c r="F5" s="3">
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>413</v>
+        <v>398</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>414</v>
+        <v>399</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>264</v>
+        <v>400</v>
       </c>
     </row>
     <row r="6">
@@ -6311,31 +6132,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>415</v>
+        <v>322</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>416</v>
+        <v>323</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>356</v>
+        <v>173</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>408</v>
+        <v>391</v>
       </c>
       <c r="F6" s="3">
         <v>100</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>417</v>
+        <v>401</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>418</v>
+        <v>324</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>159</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7">
@@ -6343,31 +6164,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>318</v>
+        <v>91</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>319</v>
+        <v>86</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>153</v>
+        <v>87</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="F7" s="3">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>419</v>
+        <v>403</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>320</v>
+        <v>94</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>125</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8">
@@ -6375,31 +6196,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>91</v>
+        <v>42</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>86</v>
+        <v>35</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>87</v>
+        <v>36</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>420</v>
+        <v>402</v>
       </c>
       <c r="F8" s="3">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>421</v>
+        <v>404</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>94</v>
+        <v>45</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>95</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9">
@@ -6407,31 +6228,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>422</v>
+        <v>405</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>423</v>
+        <v>185</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>424</v>
+        <v>177</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>420</v>
+        <v>406</v>
       </c>
       <c r="F9" s="3">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>425</v>
+        <v>407</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>426</v>
+        <v>408</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>159</v>
+        <v>409</v>
       </c>
     </row>
     <row r="10">
@@ -6439,31 +6260,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>427</v>
+        <v>410</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>331</v>
+        <v>411</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="F10" s="3">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>428</v>
+        <v>412</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>429</v>
+        <v>413</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>196</v>
+        <v>414</v>
       </c>
     </row>
     <row r="11">
@@ -6471,31 +6292,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>42</v>
+        <v>415</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>35</v>
+        <v>416</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>36</v>
+        <v>173</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>420</v>
+        <v>402</v>
       </c>
       <c r="F11" s="3">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>430</v>
+        <v>417</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>45</v>
+        <v>418</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>46</v>
+        <v>419</v>
       </c>
     </row>
     <row r="12">
@@ -6503,31 +6324,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>431</v>
+        <v>311</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>432</v>
+        <v>179</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>153</v>
+        <v>170</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>408</v>
+        <v>391</v>
       </c>
       <c r="F12" s="3">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>433</v>
+        <v>420</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>434</v>
+        <v>346</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>95</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -6535,31 +6356,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>435</v>
+        <v>421</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>436</v>
+        <v>35</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>437</v>
+        <v>36</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>420</v>
+        <v>391</v>
       </c>
       <c r="F13" s="3">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>438</v>
+        <v>422</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>439</v>
+        <v>423</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>246</v>
+        <v>409</v>
       </c>
     </row>
     <row r="14">
@@ -6567,31 +6388,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>440</v>
+        <v>424</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>441</v>
+        <v>281</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>153</v>
+        <v>173</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>420</v>
+        <v>385</v>
       </c>
       <c r="F14" s="3">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>442</v>
+        <v>425</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>443</v>
+        <v>426</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>444</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15">
@@ -6599,31 +6420,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>445</v>
+        <v>427</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>441</v>
+        <v>156</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>153</v>
+        <v>266</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>420</v>
+        <v>391</v>
       </c>
       <c r="F15" s="3">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>442</v>
+        <v>428</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>446</v>
+        <v>429</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>225</v>
+        <v>430</v>
       </c>
     </row>
     <row r="16">
@@ -6631,31 +6452,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>352</v>
+        <v>431</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>181</v>
+        <v>432</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>408</v>
+        <v>391</v>
       </c>
       <c r="F16" s="3">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>447</v>
+        <v>433</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>358</v>
+        <v>434</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>164</v>
+        <v>435</v>
       </c>
     </row>
     <row r="17">
@@ -6663,31 +6484,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>448</v>
+        <v>410</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>35</v>
+        <v>436</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>36</v>
+        <v>437</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="F17" s="3">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>449</v>
+        <v>438</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>450</v>
+        <v>439</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>451</v>
+        <v>440</v>
       </c>
     </row>
     <row r="18">
@@ -6695,31 +6516,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>452</v>
+        <v>441</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>453</v>
+        <v>442</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>454</v>
+        <v>162</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="F18" s="3">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>455</v>
+        <v>443</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>456</v>
+        <v>444</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>457</v>
+        <v>130</v>
       </c>
     </row>
     <row r="19">
@@ -6727,31 +6548,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>458</v>
+        <v>58</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>459</v>
+        <v>59</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>153</v>
+        <v>60</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>420</v>
+        <v>391</v>
       </c>
       <c r="F19" s="3">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>460</v>
+        <v>445</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>461</v>
+        <v>62</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>462</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20">
@@ -6759,31 +6580,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>463</v>
+        <v>446</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>464</v>
+        <v>447</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>153</v>
+        <v>173</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="F20" s="3">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>465</v>
+        <v>448</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>466</v>
+        <v>449</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>467</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21">
@@ -6791,31 +6612,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>468</v>
+        <v>450</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>160</v>
+        <v>451</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>290</v>
+        <v>452</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>408</v>
+        <v>391</v>
       </c>
       <c r="F21" s="3">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>469</v>
+        <v>453</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>470</v>
+        <v>454</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>300</v>
+        <v>455</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W32.xlsx
+++ b/reports/devops-jobs-israel-2026-W32.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="474">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="475">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-05T08:47:59</t>
+    <t xml:space="preserve">2026-08-06T08:49:18</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Junior %</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1%</t>
+    <t xml:space="preserve">2.2%</t>
   </si>
   <si>
     <t xml:space="preserve">Salary disclosure rate %</t>
@@ -465,526 +465,739 @@
     <t xml:space="preserve">2026-06-04</t>
   </si>
   <si>
-    <t xml:space="preserve">Engineering Manager, AI Platform Enablement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melio</t>
+    <t xml:space="preserve">Scytale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-scytale-4449488382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checkmarx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-checkmarx-4439196775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buildots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-buildots-4448083785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-engineer-at-thales-4343562293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medulla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-medulla-4448331135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dialog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-dialog-4446200013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4445878493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moon Active</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-moon-active-4447023421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps / Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tipuli Tech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-engineer-at-tipuli-tech-4447115888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mid-Senior DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ArtAc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/mid-senior-devops-engineer-at-artac-4449656279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-elbit-systems-israel-4394529806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chaos Engineer (Chaos DevOps)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Point Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/chaos-engineer-chaos-devops-at-check-point-software-4449688636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-artac-4449652341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bagira</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-bagira-4368663100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps engineer - Data Security DevOps Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-data-security-devops-team-at-thales-4428647317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4449116821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cato-networks-4430441382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OFFROAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-offroad-4448139496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WalkMe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-walkme-4380911237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ThetaRay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-thetaray-4446919831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevSecOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Playtika</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-at-playtika-4417616851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Descope</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-descope-4431665949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cyber-Hive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-cyber-hive-4447364753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bridgify</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-bridgify-4441525178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yad2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-yad2-4439486812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assured Allies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-assured-allies-4447671142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pagaya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-pagaya-4316888825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Infrastructure &amp; Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-cloud-engineer-at-moon-active-4447031167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">איש.אשת DevOps Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dahan Lab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%90%D7%99%D7%A9-%D7%90%D7%A9%D7%AA-devops-linux-at-dahan-lab-4449061474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oasis Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-oasis-security-4431605535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alpha | Similarweb Partner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-alpha-similarweb-partner-4447362032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voyantis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-voyantis-4448003083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader - Infra and DevEx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaltura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-infra-and-devex-at-kaltura-4442712745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aidoc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-aidoc-4449444867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Tech Lead (BigBrain)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">monday.com AI engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-bigbrain-at-monday-com-ai-engineering-4449050085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZOLL Medical Corporation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-zoll-medical-corporation-4399156755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-gotfriends-4445872562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chainalysis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-chainalysis-4413448060</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Team leader, DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zadara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/team-leader-devops-at-zadara-4448858731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps / Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAIRC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or HaNer, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-tairc-4447391644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-tairc-4448004083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior SRE &amp; Linux Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-linux-infrastructure-engineer-at-mobileye-4439143553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps / Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lendbuzz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-site-reliability-engineer-sre-at-lendbuzz-4437323317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE Technical Lead, DevOps Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BigPanda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-technical-lead-devops-group-at-bigpanda-4447980511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior SRE (IT Infrastructure)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-it-infrastructure-at-palo-alto-networks-4387086808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4410866558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps SRE Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Axon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-sre-engineer-at-axon-4440000142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (OpenShift Specialist)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accel Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-openshift-specialist-at-accel-solutions-4448097045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4429844723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SciPlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-sciplay-4391151881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viz.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-viz-ai-4437383686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer / Technical Lead (AWS &amp; GCP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AnyClip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ness Ziona, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-technical-lead-aws-gcp-at-anyclip-4446636401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineer III, Platform Engineering and Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-iii-platform-engineering-and-infrastructure-at-google-4448296220</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior DevOps Engineer — AI-Native</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-devops-engineer-%E2%80%94-ai-native-at-artac-4449655270</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Automation Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon Web Services (AWS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-automation-engineer-at-amazon-web-services-aws-4448323071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Akiva, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-tairc-4447388666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Security Engineer - Microsoft 365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantum Machines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-microsoft-365-at-quantum-machines-4362195136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reline IT Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nes Ziona, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-reline-it-solutions-4447375577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Immunai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-immunai-4450225101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevSecOps Engineer (AI-Driven Security)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-ai-driven-security-at-wix-4439730458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YouCC Technologies Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashkelon, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ot-infrastructure-engineer-at-youcc-technologies-ltd-4448836015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-infrastructure-engineer-at-nebius-4437660611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Infrastructure Engineer (Modiin)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-infrastructure-engineer-modiin-at-nebius-4437655743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Technology Infrastructure Engineer - 24262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-infrastructure-engineer-24262-at-comblack-4448306072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calanit by one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-calanit-by-one-4448158765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Network Infrastructure Engineer - 20690</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-infrastructure-engineer-20690-at-comblack-4448189250</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
   </si>
   <si>
     <t xml:space="preserve">Observability</t>
   </si>
   <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/melio/jobs/7747499003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-ai-4445021674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kiryat Ata, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4437329124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Checkmarx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-checkmarx-4439196775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-engineer-at-thales-4343562293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medulla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-medulla-4448331135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wiliot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiliot-4446820849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dialog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-dialog-4446200013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4445878493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moon Active</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-moon-active-4447023421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer – Embedded Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-%E2%80%93-embedded-systems-at-abra-4446717885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevSecOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Playtika</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-at-playtika-4417616851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure DevOps Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">One Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/azure-devops-administrator-at-one-systems-4440105641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dataspan.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-dataspan-ai-4448953842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aidoc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-aidoc-4449444867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-checkmarx-4446765835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cato-networks-4430441382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OFFROAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-offroad-4448139496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-abra-4447643479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ThetaRay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-thetaray-4446919831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KMS Lighthouse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-kms-lighthouse-4447696634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WalkMe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-walkme-4380911237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps / Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lendbuzz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-site-reliability-engineer-sre-at-lendbuzz-4437323317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teads</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-at-teads-4436613100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Head of DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fluent Trade Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-at-fluent-trade-technologies-4372997510</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alpha | Similarweb Partner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-alpha-similarweb-partner-4447362032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bridgify</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-bridgify-4441525178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bagira</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-bagira-4368663100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SecuriThings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-securithings-4446720959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer / Technical Lead (AWS &amp; GCP)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AnyClip</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ness Ziona, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-technical-lead-aws-gcp-at-anyclip-4446636401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior SRE &amp; Linux Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobileye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-linux-infrastructure-engineer-at-mobileye-4439143553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cyber-Hive</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-cyber-hive-4447364753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE Technical Lead, DevOps Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BigPanda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-technical-lead-devops-group-at-bigpanda-4447980511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior SRE (IT Infrastructure)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-it-infrastructure-at-palo-alto-networks-4387086808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4410866558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps SRE Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Axon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-sre-engineer-at-axon-4440000142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SciPlay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-sciplay-4391151881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viz.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-viz-ai-4437383686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DataTeam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-devops-at-datateam-4447383004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineer III, Platform Engineering and Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-iii-platform-engineering-and-infrastructure-at-google-4448296220</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Streaming Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VIDAA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/streaming-platform-engineer-at-vidaa-4444520220</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps / Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tipuli Tech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-engineer-at-tipuli-tech-4447115888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harmonic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-harmonic-4360460066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Automation Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amazon Web Services (AWS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-automation-engineer-at-amazon-web-services-aws-4448323071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Infrastructure &amp; Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-cloud-engineer-at-moon-active-4447031167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lead Data Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Log-On Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lead-data-platform-engineer-at-log-on-software-4446211103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer – AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UR Tech Jobs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-%E2%80%93-aws-at-ur-tech-jobs-4447639616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Horizon Technologies LTD.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-architect-at-horizon-technologies-ltd-4446611841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Security Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-at-log-on-software-4445889868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reline IT Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nes Ziona, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-reline-it-solutions-4447375577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Linux Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weizmann Institute of Science</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-linux-administrator-at-weizmann-institute-of-science-4444102865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YouCC Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashkelon, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ot-infrastructure-engineer-at-youcc-technologies-ltd-4448836015</t>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior AI SRE Developer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helfy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Virtualization, Active Directory, Automation</t>
   </si>
   <si>
     <t xml:space="preserve">System Engineer</t>
@@ -993,306 +1206,126 @@
     <t xml:space="preserve">Paragon</t>
   </si>
   <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-infrastructure-engineer-at-nebius-4437660618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Infrastructure Engineer (Modiin)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-infrastructure-engineer-modiin-at-nebius-4437655743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology Infrastructure Engineer - 24262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-infrastructure-engineer-24262-at-comblack-4448306072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calanit by one</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-calanit-by-one-4448158765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">איש.אשת DevOps Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dahan Lab</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%90%D7%99%D7%A9-%D7%90%D7%A9%D7%AA-devops-linux-at-dahan-lab-4449061474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unilink Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-unilink-ltd-4446581282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Network Infrastructure Engineer - 20690</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-infrastructure-engineer-20690-at-comblack-4448189250</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-gotfriends-4445849138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Group Leader - Cloud Platform &amp; SRE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/group-leader-cloud-platform-sre-at-confidential-4434818632</t>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waterfall Security Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-position-at-waterfall-security-solutions-4444878648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Technical Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4442889333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior QA Engineer - Student Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fives Intralogistics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-qa-engineer-student-position-at-fives-intralogistics-4446042176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fives</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-qa-engineer-student-position-at-fives-4436801163</t>
   </si>
   <si>
     <t xml:space="preserve">2026-07-08</t>
   </si>
   <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4429844723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oasis Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-oasis-security-4431605535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assured Allies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-assured-allies-4447671142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZOLL Medical Corporation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-zoll-medical-corporation-4399156755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.3%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.6%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior AI SRE Developer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helfy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Virtualization, Active Directory, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator - Linux, Windows #1350</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-linux-windows-%231350-at-rad-4443763825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test Environment Support Engineer</t>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autobrains Technologies</t>
   </si>
   <si>
     <t xml:space="preserve">Help Desk / IT Support</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Networking, Monitoring, Databases, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/test-environment-support-engineer-at-abra-4442615924</t>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4440209390</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation student- Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-jerusalem-at-radware-4440152008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-at-radware-4437695096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud &amp; AI Security Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4932015101?gh_jid=4932015101</t>
   </si>
   <si>
     <t xml:space="preserve">2026-07-22</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Autobrains Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4440209390</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation student- Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-jerusalem-at-radware-4440152008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud &amp; AI Security Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4932015101?gh_jid=4932015101</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
   </si>
   <si>
@@ -1302,6 +1335,21 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
   </si>
   <si>
+    <t xml:space="preserve">IOT student tester</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Motorola Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/iot-student-tester-at-motorola-solutions-4434451222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-29</t>
+  </si>
+  <si>
     <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
   </si>
   <si>
@@ -1311,9 +1359,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-4428415454</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-24</t>
-  </si>
-  <si>
     <t xml:space="preserve">System Administrator &amp; IT</t>
   </si>
   <si>
@@ -1344,67 +1389,25 @@
     <t xml:space="preserve">2026-07-01</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Operations Engineer I</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Innovid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-engineer-i-at-innovid-4443857656</t>
-  </si>
-  <si>
     <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Operations &amp; Helpdesk Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claroty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-helpdesk-engineer-at-claroty-4412805136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineer - Unmanned Maritime Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Docker, Kubernetes, Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-unmanned-maritime-systems-at-elbit-systems-israel-4433797145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-07</t>
-  </si>
-  <si>
     <t xml:space="preserve">Roles requiring it</t>
   </si>
   <si>
     <t xml:space="preserve">Troubleshooting</t>
   </si>
   <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cloud (any)</t>
   </si>
   <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
     <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation</t>
   </si>
   <si>
     <t xml:space="preserve">Monitoring</t>
@@ -1565,7 +1568,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7">
@@ -1573,7 +1576,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
@@ -1581,7 +1584,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9">
@@ -1589,7 +1592,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>1211</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="10">
@@ -1597,7 +1600,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1669,7 +1672,7 @@
         <v>24</v>
       </c>
       <c r="B20" s="3">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1688,20 +1691,20 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>406</v>
+        <v>420</v>
       </c>
       <c r="B2" s="3">
-        <v>48</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="B3" s="3">
         <v>18</v>
@@ -1709,15 +1712,15 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="B4" s="3">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="B5" s="3">
         <v>2</v>
@@ -1736,23 +1739,23 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B2" s="3">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="B3" s="3">
         <v>45</v>
@@ -1760,10 +1763,10 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>458</v>
+        <v>241</v>
       </c>
       <c r="B4" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5">
@@ -1771,52 +1774,52 @@
         <v>459</v>
       </c>
       <c r="B5" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>366</v>
+        <v>460</v>
       </c>
       <c r="B6" s="3">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B7" s="3">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>252</v>
+        <v>361</v>
       </c>
       <c r="B8" s="3">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B9" s="3">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B10" s="3">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>194</v>
+        <v>364</v>
       </c>
       <c r="B11" s="3">
         <v>12</v>
@@ -1824,7 +1827,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="B12" s="3">
         <v>12</v>
@@ -1832,23 +1835,23 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>304</v>
+        <v>464</v>
       </c>
       <c r="B13" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B14" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>464</v>
+        <v>360</v>
       </c>
       <c r="B15" s="3">
         <v>10</v>
@@ -1856,10 +1859,10 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="B16" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -1884,13 +1887,13 @@
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="2">
@@ -1898,13 +1901,13 @@
         <v>24</v>
       </c>
       <c r="B2" s="3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C2" s="3">
-        <v>12.9</v>
+        <v>14.6</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -1916,85 +1919,85 @@
         <v>68</v>
       </c>
       <c r="C3" s="3">
-        <v>28.7</v>
+        <v>38.7</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>8.3</v>
+        <v>7.8</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>35.5</v>
+        <v>33.1</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>18.2</v>
+        <v>19.6</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>17.2</v>
+        <v>15.2</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2006,7 +2009,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="31" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
     <col min="3" max="3" width="47" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -2078,7 +2081,7 @@
         <v>41</v>
       </c>
       <c r="J2" s="3">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3">
@@ -2110,7 +2113,7 @@
         <v>46</v>
       </c>
       <c r="J3" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -2142,7 +2145,7 @@
         <v>52</v>
       </c>
       <c r="J4" s="3">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5">
@@ -2174,7 +2177,7 @@
         <v>41</v>
       </c>
       <c r="J5" s="3">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6">
@@ -2206,7 +2209,7 @@
         <v>41</v>
       </c>
       <c r="J6" s="3">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7">
@@ -2238,7 +2241,7 @@
         <v>63</v>
       </c>
       <c r="J7" s="3">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8">
@@ -2270,7 +2273,7 @@
         <v>41</v>
       </c>
       <c r="J8" s="3">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9">
@@ -2302,7 +2305,7 @@
         <v>73</v>
       </c>
       <c r="J9" s="3">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10">
@@ -2334,7 +2337,7 @@
         <v>77</v>
       </c>
       <c r="J10" s="3">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11">
@@ -2366,7 +2369,7 @@
         <v>73</v>
       </c>
       <c r="J11" s="3">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12">
@@ -2398,7 +2401,7 @@
         <v>84</v>
       </c>
       <c r="J12" s="3">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13">
@@ -2430,7 +2433,7 @@
         <v>90</v>
       </c>
       <c r="J13" s="3">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14">
@@ -2462,7 +2465,7 @@
         <v>95</v>
       </c>
       <c r="J14" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -2494,7 +2497,7 @@
         <v>46</v>
       </c>
       <c r="J15" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
@@ -2526,7 +2529,7 @@
         <v>102</v>
       </c>
       <c r="J16" s="3">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17">
@@ -2558,7 +2561,7 @@
         <v>77</v>
       </c>
       <c r="J17" s="3">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18">
@@ -2590,7 +2593,7 @@
         <v>109</v>
       </c>
       <c r="J18" s="3">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19">
@@ -2622,7 +2625,7 @@
         <v>115</v>
       </c>
       <c r="J19" s="3">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20">
@@ -2654,7 +2657,7 @@
         <v>41</v>
       </c>
       <c r="J20" s="3">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="21">
@@ -2686,7 +2689,7 @@
         <v>125</v>
       </c>
       <c r="J21" s="3">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22">
@@ -2718,7 +2721,7 @@
         <v>130</v>
       </c>
       <c r="J22" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -2750,7 +2753,7 @@
         <v>136</v>
       </c>
       <c r="J23" s="3">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24">
@@ -2780,7 +2783,7 @@
         <v>139</v>
       </c>
       <c r="J24" s="3">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="25">
@@ -2812,7 +2815,7 @@
         <v>41</v>
       </c>
       <c r="J25" s="3">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="26">
@@ -2842,39 +2845,37 @@
         <v>147</v>
       </c>
       <c r="J26" s="3">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="C27" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="C27" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="D27" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F27" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H27" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H27" s="3" t="s">
+      <c r="I27" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="I27" s="3" t="s">
-        <v>77</v>
-      </c>
       <c r="J27" s="3">
-        <v>69</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2888,7 +2889,7 @@
         <v>153</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>43</v>
@@ -2904,7 +2905,7 @@
         <v>155</v>
       </c>
       <c r="J28" s="3">
-        <v>2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29">
@@ -2918,7 +2919,7 @@
         <v>157</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>158</v>
+        <v>49</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>43</v>
@@ -2928,27 +2929,27 @@
         <v>23</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="J29" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>116</v>
+        <v>159</v>
       </c>
       <c r="B30" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C30" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="C30" s="3" t="s">
-        <v>162</v>
-      </c>
       <c r="D30" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>43</v>
@@ -2958,27 +2959,27 @@
         <v>23</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>164</v>
+        <v>84</v>
       </c>
       <c r="J30" s="3">
-        <v>22</v>
+        <v>83</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>165</v>
+        <v>116</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>43</v>
@@ -2988,13 +2989,13 @@
         <v>23</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>84</v>
+        <v>130</v>
       </c>
       <c r="J31" s="3">
-        <v>82</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -3002,13 +3003,13 @@
         <v>116</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>170</v>
+        <v>149</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>43</v>
@@ -3018,13 +3019,13 @@
         <v>23</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>130</v>
+        <v>167</v>
       </c>
       <c r="J32" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -3032,13 +3033,13 @@
         <v>116</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>43</v>
@@ -3048,13 +3049,13 @@
         <v>23</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="J33" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
@@ -3062,13 +3063,13 @@
         <v>116</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>43</v>
@@ -3078,27 +3079,27 @@
         <v>23</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="J34" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>116</v>
+        <v>174</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>43</v>
@@ -3108,30 +3109,30 @@
         <v>23</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="J35" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>116</v>
+        <v>179</v>
       </c>
       <c r="B36" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="C36" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="C36" s="3" t="s">
-        <v>173</v>
-      </c>
       <c r="D36" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
@@ -3141,24 +3142,24 @@
         <v>182</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>183</v>
+        <v>151</v>
       </c>
       <c r="J36" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C37" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="D37" s="3" t="s">
         <v>185</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>145</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>43</v>
@@ -3168,13 +3169,13 @@
         <v>23</v>
       </c>
       <c r="H37" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="I37" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="I37" s="3" t="s">
-        <v>175</v>
-      </c>
       <c r="J37" s="3">
-        <v>6</v>
+        <v>62</v>
       </c>
     </row>
     <row r="38">
@@ -3185,7 +3186,7 @@
         <v>189</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>60</v>
+        <v>171</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>49</v>
@@ -3193,142 +3194,140 @@
       <c r="E38" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F38" s="3" t="s">
+      <c r="F38" s="3"/>
+      <c r="G38" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H38" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="G38" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>191</v>
-      </c>
       <c r="I38" s="3" t="s">
-        <v>77</v>
+        <v>151</v>
       </c>
       <c r="J38" s="3">
-        <v>69</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>192</v>
+        <v>53</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>194</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="J39" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="J40" s="3">
-        <v>0</v>
+        <v>44</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>53</v>
+        <v>197</v>
       </c>
       <c r="B41" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="I41" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="C41" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F41" s="3"/>
-      <c r="G41" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="J41" s="3">
-        <v>0</v>
+        <v>52</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>202</v>
+        <v>53</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>161</v>
+        <v>201</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>183</v>
+        <v>151</v>
       </c>
       <c r="J42" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -3336,10 +3335,10 @@
         <v>116</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>49</v>
@@ -3352,13 +3351,13 @@
         <v>23</v>
       </c>
       <c r="H43" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="I43" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>206</v>
-      </c>
       <c r="J43" s="3">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="44">
@@ -3366,10 +3365,10 @@
         <v>53</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>49</v>
@@ -3382,32 +3381,34 @@
         <v>23</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="J44" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>185</v>
+        <v>208</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F45" s="3"/>
+        <v>43</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>198</v>
+      </c>
       <c r="G45" s="3" t="s">
         <v>23</v>
       </c>
@@ -3415,10 +3416,10 @@
         <v>209</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>160</v>
+        <v>210</v>
       </c>
       <c r="J45" s="3">
-        <v>3</v>
+        <v>67</v>
       </c>
     </row>
     <row r="46">
@@ -3426,10 +3427,10 @@
         <v>116</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>122</v>
@@ -3442,32 +3443,34 @@
         <v>23</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="J46" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>214</v>
+        <v>60</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>215</v>
+        <v>49</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F47" s="3"/>
+      <c r="F47" s="3" t="s">
+        <v>198</v>
+      </c>
       <c r="G47" s="3" t="s">
         <v>23</v>
       </c>
@@ -3475,31 +3478,29 @@
         <v>216</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>130</v>
+        <v>77</v>
       </c>
       <c r="J47" s="3">
-        <v>1</v>
+        <v>70</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>217</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>173</v>
+        <v>157</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>190</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
         <v>23</v>
       </c>
@@ -3510,7 +3511,7 @@
         <v>219</v>
       </c>
       <c r="J48" s="3">
-        <v>66</v>
+        <v>43</v>
       </c>
     </row>
     <row r="49">
@@ -3521,13 +3522,13 @@
         <v>221</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
@@ -3540,51 +3541,51 @@
         <v>223</v>
       </c>
       <c r="J49" s="3">
-        <v>27</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B50" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="B50" s="3" t="s">
-        <v>225</v>
-      </c>
       <c r="C50" s="3" t="s">
-        <v>226</v>
+        <v>171</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>227</v>
+        <v>49</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>229</v>
+        <v>167</v>
       </c>
       <c r="J50" s="3">
-        <v>24</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>186</v>
+        <v>228</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>145</v>
+        <v>229</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>38</v>
@@ -3594,13 +3595,13 @@
         <v>23</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>84</v>
+        <v>231</v>
       </c>
       <c r="J51" s="3">
-        <v>82</v>
+        <v>22</v>
       </c>
     </row>
     <row r="52">
@@ -3608,10 +3609,10 @@
         <v>53</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>49</v>
@@ -3624,13 +3625,13 @@
         <v>23</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>199</v>
+        <v>167</v>
       </c>
       <c r="J52" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53">
@@ -3638,10 +3639,10 @@
         <v>53</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>49</v>
@@ -3654,13 +3655,13 @@
         <v>23</v>
       </c>
       <c r="H53" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="I53" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="I53" s="3" t="s">
-        <v>155</v>
-      </c>
       <c r="J53" s="3">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="54">
@@ -3668,150 +3669,148 @@
         <v>237</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>238</v>
+        <v>170</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>239</v>
+        <v>171</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>241</v>
+        <v>173</v>
       </c>
       <c r="J54" s="3">
-        <v>43</v>
+        <v>6</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>53</v>
+        <v>239</v>
       </c>
       <c r="B55" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H55" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="C55" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E55" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F55" s="3"/>
-      <c r="G55" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H55" s="3" t="s">
-        <v>243</v>
-      </c>
       <c r="I55" s="3" t="s">
-        <v>175</v>
+        <v>223</v>
       </c>
       <c r="J55" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>244</v>
+        <v>53</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>246</v>
+        <v>171</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F56" s="3" t="s">
-        <v>247</v>
-      </c>
+      <c r="F56" s="3"/>
       <c r="G56" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="J56" s="3">
-        <v>0</v>
+        <v>44</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>249</v>
+        <v>53</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>251</v>
+        <v>171</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>145</v>
+        <v>49</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F57" s="3" t="s">
-        <v>252</v>
-      </c>
+      <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>254</v>
+        <v>223</v>
       </c>
       <c r="J57" s="3">
-        <v>23</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>257</v>
+        <v>171</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>199</v>
+        <v>151</v>
       </c>
       <c r="J58" s="3">
         <v>0</v>
@@ -3819,43 +3818,43 @@
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>130</v>
+        <v>253</v>
       </c>
       <c r="J59" s="3">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>262</v>
+        <v>53</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>49</v>
@@ -3868,27 +3867,27 @@
         <v>23</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>77</v>
+        <v>223</v>
       </c>
       <c r="J60" s="3">
-        <v>69</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>156</v>
+        <v>257</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>266</v>
+        <v>171</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>38</v>
@@ -3898,54 +3897,54 @@
         <v>23</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>219</v>
+        <v>151</v>
       </c>
       <c r="J61" s="3">
-        <v>66</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>173</v>
+        <v>60</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>164</v>
+        <v>139</v>
       </c>
       <c r="J62" s="3">
-        <v>22</v>
+        <v>71</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>53</v>
+        <v>226</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>271</v>
+        <v>168</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>173</v>
+        <v>157</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>49</v>
@@ -3958,24 +3957,24 @@
         <v>23</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>84</v>
+        <v>167</v>
       </c>
       <c r="J63" s="3">
-        <v>82</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>56</v>
+        <v>263</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>49</v>
@@ -3988,57 +3987,57 @@
         <v>23</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="I64" s="3" t="s">
         <v>84</v>
       </c>
       <c r="J64" s="3">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>56</v>
+        <v>266</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>229</v>
+        <v>151</v>
       </c>
       <c r="J65" s="3">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>170</v>
+        <v>271</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>43</v>
@@ -4048,10 +4047,10 @@
         <v>23</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>199</v>
+        <v>151</v>
       </c>
       <c r="J66" s="3">
         <v>0</v>
@@ -4059,16 +4058,16 @@
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>162</v>
+        <v>271</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>43</v>
@@ -4078,10 +4077,10 @@
         <v>23</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>199</v>
+        <v>151</v>
       </c>
       <c r="J67" s="3">
         <v>0</v>
@@ -4089,76 +4088,78 @@
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>170</v>
+        <v>277</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>49</v>
+        <v>145</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F68" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>241</v>
+      </c>
       <c r="G68" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>183</v>
+        <v>236</v>
       </c>
       <c r="J68" s="3">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>257</v>
+        <v>171</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>160</v>
+        <v>282</v>
       </c>
       <c r="J69" s="3">
-        <v>3</v>
+        <v>28</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>291</v>
+        <v>171</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>158</v>
+        <v>49</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>38</v>
@@ -4168,87 +4169,87 @@
         <v>23</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="J70" s="3">
-        <v>70</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>295</v>
+        <v>171</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>158</v>
+        <v>49</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>199</v>
+        <v>77</v>
       </c>
       <c r="J71" s="3">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>181</v>
+        <v>290</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>173</v>
+        <v>291</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>183</v>
+        <v>210</v>
       </c>
       <c r="J72" s="3">
-        <v>5</v>
+        <v>67</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>38</v>
@@ -4258,59 +4259,57 @@
         <v>23</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>199</v>
+        <v>155</v>
       </c>
       <c r="J73" s="3">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F74" s="3" t="s">
-        <v>304</v>
-      </c>
+      <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="J74" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>307</v>
+        <v>171</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>38</v>
@@ -4320,121 +4319,119 @@
         <v>23</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>199</v>
+        <v>301</v>
       </c>
       <c r="J75" s="3">
-        <v>0</v>
+        <v>41</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>309</v>
+        <v>56</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F76" s="3" t="s">
-        <v>190</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>199</v>
+        <v>84</v>
       </c>
       <c r="J76" s="3">
-        <v>0</v>
+        <v>83</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>311</v>
+        <v>56</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>313</v>
+        <v>171</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>199</v>
+        <v>306</v>
       </c>
       <c r="J77" s="3">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>167</v>
+        <v>309</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>122</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>252</v>
+        <v>310</v>
       </c>
       <c r="G78" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>183</v>
+        <v>223</v>
       </c>
       <c r="J78" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>320</v>
+        <v>153</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E79" s="3" t="s">
         <v>43</v>
@@ -4444,10 +4441,10 @@
         <v>23</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>130</v>
+        <v>223</v>
       </c>
       <c r="J79" s="3">
         <v>1</v>
@@ -4455,46 +4452,46 @@
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>323</v>
+        <v>180</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>43</v>
+        <v>92</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>325</v>
+        <v>151</v>
       </c>
       <c r="J80" s="3">
-        <v>57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>122</v>
+        <v>185</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>43</v>
@@ -4504,27 +4501,27 @@
         <v>23</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>330</v>
+        <v>223</v>
       </c>
       <c r="J81" s="3">
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>327</v>
+        <v>270</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>239</v>
+        <v>322</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>122</v>
+        <v>185</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>43</v>
@@ -4534,24 +4531,24 @@
         <v>23</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>330</v>
+        <v>151</v>
       </c>
       <c r="J82" s="3">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>49</v>
@@ -4559,29 +4556,31 @@
       <c r="E83" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F83" s="3"/>
+      <c r="F83" s="3" t="s">
+        <v>198</v>
+      </c>
       <c r="G83" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>130</v>
+        <v>84</v>
       </c>
       <c r="J83" s="3">
-        <v>1</v>
+        <v>83</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>307</v>
+        <v>329</v>
       </c>
       <c r="D84" s="3" t="s">
         <v>122</v>
@@ -4589,49 +4588,45 @@
       <c r="E84" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F84" s="3" t="s">
-        <v>252</v>
-      </c>
+      <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>199</v>
+        <v>223</v>
       </c>
       <c r="J84" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>339</v>
+        <v>53</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F85" s="3" t="s">
-        <v>252</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F85" s="3"/>
       <c r="G85" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>199</v>
+        <v>151</v>
       </c>
       <c r="J85" s="3">
         <v>0</v>
@@ -4639,13 +4634,13 @@
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>311</v>
+        <v>333</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D86" s="3" t="s">
         <v>49</v>
@@ -4653,29 +4648,31 @@
       <c r="E86" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F86" s="3"/>
+      <c r="F86" s="3" t="s">
+        <v>198</v>
+      </c>
       <c r="G86" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="J86" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>307</v>
+        <v>338</v>
       </c>
       <c r="D87" s="3" t="s">
         <v>122</v>
@@ -4688,27 +4685,27 @@
         <v>23</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="I87" s="3" t="s">
         <v>130</v>
       </c>
       <c r="J87" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>311</v>
+        <v>340</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>179</v>
+        <v>341</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>43</v>
@@ -4718,24 +4715,24 @@
         <v>23</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>130</v>
+        <v>343</v>
       </c>
       <c r="J88" s="3">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>177</v>
+        <v>194</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>122</v>
@@ -4748,137 +4745,109 @@
         <v>23</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>350</v>
+        <v>231</v>
       </c>
       <c r="J89" s="3">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>53</v>
+        <v>346</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>173</v>
+        <v>157</v>
       </c>
       <c r="D90" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F90" s="3"/>
       <c r="G90" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>353</v>
+        <v>130</v>
       </c>
       <c r="J90" s="3">
-        <v>40</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>53</v>
+        <v>349</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>173</v>
+        <v>351</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F91" s="3"/>
+        <v>43</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>241</v>
+      </c>
       <c r="G91" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>241</v>
+        <v>223</v>
       </c>
       <c r="J91" s="3">
-        <v>43</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>53</v>
+        <v>353</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>162</v>
+        <v>351</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F92" s="3"/>
       <c r="G92" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="J92" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="B93" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="C93" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D93" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E93" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F93" s="3"/>
-      <c r="G93" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H93" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="I93" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="J93" s="3">
-        <v>70</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J93"/>
+  <autoFilter ref="A1:J92"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -4971,7 +4940,6 @@
     <hyperlink ref="H90" r:id="rId89"/>
     <hyperlink ref="H91" r:id="rId90"/>
     <hyperlink ref="H92" r:id="rId91"/>
-    <hyperlink ref="H93" r:id="rId92"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4979,8 +4947,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="1" max="1" width="50" customWidth="1"/>
+    <col min="2" max="2" width="27" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -5013,13 +4981,13 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>196</v>
+        <v>116</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>197</v>
+        <v>148</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -5027,18 +4995,18 @@
         <v>23</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>198</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>53</v>
+        <v>116</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>200</v>
+        <v>156</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>173</v>
+        <v>157</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -5046,18 +5014,18 @@
         <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>201</v>
+        <v>158</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>53</v>
+        <v>179</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>233</v>
+        <v>180</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -5065,18 +5033,18 @@
         <v>23</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>234</v>
+        <v>182</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>244</v>
+        <v>188</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>245</v>
+        <v>189</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>246</v>
+        <v>171</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5084,18 +5052,18 @@
         <v>23</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>248</v>
+        <v>190</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>255</v>
+        <v>53</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>256</v>
+        <v>180</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>257</v>
+        <v>181</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -5103,18 +5071,18 @@
         <v>23</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>258</v>
+        <v>191</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>277</v>
+        <v>53</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>278</v>
+        <v>201</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -5122,18 +5090,18 @@
         <v>23</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>279</v>
+        <v>202</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>280</v>
+        <v>247</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>281</v>
+        <v>248</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -5141,18 +5109,18 @@
         <v>23</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>282</v>
+        <v>249</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>293</v>
+        <v>256</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>294</v>
+        <v>257</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>295</v>
+        <v>171</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -5160,18 +5128,18 @@
         <v>23</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>296</v>
+        <v>258</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>299</v>
+        <v>266</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>300</v>
+        <v>267</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -5179,18 +5147,18 @@
         <v>23</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>301</v>
+        <v>268</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>34</v>
+        <v>269</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>306</v>
+        <v>270</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>307</v>
+        <v>271</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -5198,18 +5166,18 @@
         <v>23</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>308</v>
+        <v>272</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>309</v>
+        <v>273</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>300</v>
+        <v>270</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>170</v>
+        <v>271</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
@@ -5217,18 +5185,18 @@
         <v>23</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>310</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>311</v>
+        <v>296</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>312</v>
+        <v>297</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>313</v>
+        <v>176</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
@@ -5236,18 +5204,18 @@
         <v>23</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>314</v>
+        <v>298</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>336</v>
+        <v>315</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>337</v>
+        <v>180</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>307</v>
+        <v>181</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
@@ -5255,18 +5223,18 @@
         <v>23</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>338</v>
+        <v>316</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>339</v>
+        <v>321</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>340</v>
+        <v>270</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>167</v>
+        <v>322</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -5274,11 +5242,49 @@
         <v>23</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>341</v>
+        <v>323</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>335</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G15"/>
+  <autoFilter ref="A1:G17"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -5294,6 +5300,8 @@
     <hyperlink ref="G13" r:id="rId12"/>
     <hyperlink ref="G14" r:id="rId13"/>
     <hyperlink ref="G15" r:id="rId14"/>
+    <hyperlink ref="G16" r:id="rId15"/>
+    <hyperlink ref="G17" r:id="rId16"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5307,31 +5315,31 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>304</v>
+        <v>198</v>
       </c>
       <c r="B2" s="3">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>190</v>
+        <v>357</v>
       </c>
       <c r="B3" s="3">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="B4" s="3">
         <v>15</v>
@@ -5339,7 +5347,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="B5" s="3">
         <v>14</v>
@@ -5347,15 +5355,15 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="B6" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="B7" s="3">
         <v>11</v>
@@ -5363,7 +5371,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="B8" s="3">
         <v>10</v>
@@ -5371,7 +5379,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>194</v>
+        <v>362</v>
       </c>
       <c r="B9" s="3">
         <v>9</v>
@@ -5379,7 +5387,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="B10" s="3">
         <v>9</v>
@@ -5387,23 +5395,23 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="B11" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>150</v>
+        <v>365</v>
       </c>
       <c r="B12" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="B13" s="3">
         <v>7</v>
@@ -5411,7 +5419,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="B14" s="3">
         <v>6</v>
@@ -5419,7 +5427,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="B15" s="3">
         <v>5</v>
@@ -5427,7 +5435,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="B16" s="3">
         <v>4</v>
@@ -5449,7 +5457,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
     </row>
     <row r="2">
@@ -5486,23 +5494,23 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>35</v>
+        <v>180</v>
       </c>
       <c r="B6" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>104</v>
+        <v>270</v>
       </c>
       <c r="B7" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>156</v>
+        <v>35</v>
       </c>
       <c r="B8" s="3">
         <v>2</v>
@@ -5510,7 +5518,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>161</v>
+        <v>104</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
@@ -5518,7 +5526,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>179</v>
+        <v>160</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -5526,7 +5534,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5534,7 +5542,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5542,7 +5550,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>300</v>
+        <v>341</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -5550,7 +5558,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>327</v>
+        <v>347</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -5558,15 +5566,15 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>334</v>
+        <v>59</v>
       </c>
       <c r="B15" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="B16" s="3">
         <v>1</v>
@@ -5587,16 +5595,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
     </row>
     <row r="2">
@@ -5688,13 +5696,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>300</v>
+        <v>180</v>
       </c>
       <c r="C8" s="3">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="D8" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -5702,13 +5710,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>117</v>
+        <v>270</v>
       </c>
       <c r="C9" s="3">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="D9" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -5716,13 +5724,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>156</v>
+        <v>117</v>
       </c>
       <c r="C10" s="3">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="D10" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -5730,7 +5738,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>185</v>
+        <v>168</v>
       </c>
       <c r="C11" s="3">
         <v>2.8</v>
@@ -5758,10 +5766,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C13" s="3">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="D13" s="3">
         <v>2</v>
@@ -5772,7 +5780,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="C14" s="3">
         <v>2.4</v>
@@ -5786,7 +5794,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>181</v>
+        <v>341</v>
       </c>
       <c r="C15" s="3">
         <v>2.4</v>
@@ -5800,7 +5808,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>327</v>
+        <v>347</v>
       </c>
       <c r="C16" s="3">
         <v>2.4</v>
@@ -5826,10 +5834,10 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
     </row>
     <row r="2">
@@ -5837,7 +5845,7 @@
         <v>92</v>
       </c>
       <c r="B2" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>12</v>
@@ -5848,10 +5856,10 @@
         <v>43</v>
       </c>
       <c r="B3" s="3">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="4">
@@ -5859,10 +5867,10 @@
         <v>38</v>
       </c>
       <c r="B4" s="3">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
     </row>
   </sheetData>
@@ -5881,7 +5889,7 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
     </row>
     <row r="2">
@@ -5889,7 +5897,7 @@
         <v>49</v>
       </c>
       <c r="B2" s="3">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3">
@@ -5902,10 +5910,10 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>145</v>
+        <v>185</v>
       </c>
       <c r="B4" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -5913,15 +5921,15 @@
         <v>37</v>
       </c>
       <c r="B5" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="B6" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -5934,17 +5942,9 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="B8" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="B9" s="3">
         <v>1</v>
       </c>
     </row>
@@ -5957,7 +5957,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="31" customWidth="1"/>
+    <col min="3" max="3" width="32" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -5969,10 +5969,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>26</v>
@@ -5984,10 +5984,10 @@
         <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>21</v>
@@ -6004,31 +6004,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>60</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="3">
@@ -6036,31 +6036,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>60</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
     </row>
     <row r="4">
@@ -6068,31 +6068,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>337</v>
+        <v>350</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>307</v>
+        <v>351</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>338</v>
+        <v>352</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5">
@@ -6100,31 +6100,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="F5" s="3">
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>400</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6">
@@ -6132,31 +6132,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>322</v>
+        <v>91</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>323</v>
+        <v>86</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>173</v>
+        <v>87</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="F6" s="3">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>324</v>
+        <v>94</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>125</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7">
@@ -6164,31 +6164,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>91</v>
+        <v>399</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>86</v>
+        <v>400</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>87</v>
+        <v>401</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="F7" s="3">
         <v>92</v>
       </c>
       <c r="G7" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>403</v>
       </c>
-      <c r="H7" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>94</v>
-      </c>
       <c r="J7" s="3" t="s">
-        <v>95</v>
+        <v>167</v>
       </c>
     </row>
     <row r="8">
@@ -6205,7 +6205,7 @@
         <v>36</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="F8" s="3">
         <v>83</v>
@@ -6231,16 +6231,16 @@
         <v>405</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>185</v>
+        <v>406</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>406</v>
+        <v>388</v>
       </c>
       <c r="F9" s="3">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>407</v>
@@ -6252,7 +6252,7 @@
         <v>408</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>409</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10">
@@ -6260,16 +6260,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>410</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="3" t="s">
         <v>411</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>173</v>
-      </c>
       <c r="E10" s="3" t="s">
-        <v>406</v>
+        <v>397</v>
       </c>
       <c r="F10" s="3">
         <v>74</v>
@@ -6292,31 +6292,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>415</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="F11" s="3">
+        <v>74</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>416</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>402</v>
-      </c>
-      <c r="F11" s="3">
-        <v>70</v>
-      </c>
-      <c r="G11" s="3" t="s">
+      <c r="J11" s="3" t="s">
         <v>417</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>418</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="12">
@@ -6324,31 +6324,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>311</v>
+        <v>418</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>179</v>
+        <v>419</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>391</v>
+        <v>420</v>
       </c>
       <c r="F12" s="3">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>346</v>
+        <v>422</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>160</v>
+        <v>423</v>
       </c>
     </row>
     <row r="13">
@@ -6356,31 +6356,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>35</v>
+        <v>425</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>36</v>
+        <v>171</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="F13" s="3">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>409</v>
+        <v>428</v>
       </c>
     </row>
     <row r="14">
@@ -6388,31 +6388,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>281</v>
+        <v>425</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>385</v>
+        <v>397</v>
       </c>
       <c r="F14" s="3">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>84</v>
+        <v>231</v>
       </c>
     </row>
     <row r="15">
@@ -6420,31 +6420,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>156</v>
+        <v>35</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>266</v>
+        <v>36</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="F15" s="3">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="16">
@@ -6452,31 +6452,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>432</v>
+        <v>313</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="F16" s="3">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>435</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17">
@@ -6484,31 +6484,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>410</v>
+        <v>438</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>437</v>
+        <v>171</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>406</v>
+        <v>397</v>
       </c>
       <c r="F17" s="3">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="18">
@@ -6516,31 +6516,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>442</v>
+        <v>290</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>162</v>
+        <v>291</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="F18" s="3">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>130</v>
+        <v>219</v>
       </c>
     </row>
     <row r="19">
@@ -6548,31 +6548,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>58</v>
+        <v>446</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>59</v>
+        <v>447</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>60</v>
+        <v>171</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="F19" s="3">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>62</v>
+        <v>449</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>63</v>
+        <v>450</v>
       </c>
     </row>
     <row r="20">
@@ -6580,31 +6580,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>446</v>
+        <v>418</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>173</v>
+        <v>452</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>406</v>
+        <v>420</v>
       </c>
       <c r="F20" s="3">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>73</v>
+        <v>455</v>
       </c>
     </row>
     <row r="21">
@@ -6612,31 +6612,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>450</v>
+        <v>58</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>451</v>
+        <v>59</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>452</v>
+        <v>60</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="F21" s="3">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>454</v>
+        <v>62</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>455</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W32.xlsx
+++ b/reports/devops-jobs-israel-2026-W32.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="475">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="481">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-06T08:49:18</t>
+    <t xml:space="preserve">2026-08-07T07:36:16</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -477,6 +477,15 @@
     <t xml:space="preserve">2026-08-06</t>
   </si>
   <si>
+    <t xml:space="preserve">Connecteam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4290904319</t>
+  </si>
+  <si>
     <t xml:space="preserve">Checkmarx</t>
   </si>
   <si>
@@ -531,862 +540,871 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4445878493</t>
   </si>
   <si>
-    <t xml:space="preserve">Moon Active</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-moon-active-4447023421</t>
+    <t xml:space="preserve">DevOps / Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tipuli Tech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-engineer-at-tipuli-tech-4447115888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mid-Senior DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ArtAc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/mid-senior-devops-engineer-at-artac-4449647364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bagira</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-bagira-4368663100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps engineer - Data Security DevOps Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-data-security-devops-team-at-thales-4428647317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4449116821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compie Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-compie-technologies-4450271080</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cato-networks-4430441382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viz.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-viz-ai-4449757750</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ERGO NEXT Insurance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-engineer-at-ergo-next-insurance-4440256247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WalkMe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-walkme-4380911237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (37184)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-37184-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4450224745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GenAI Group DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/genai-group-devops-engineer-at-elbit-systems-israel-4395652910</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevSecOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Playtika</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-at-playtika-4417616851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Descope</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-descope-4431665949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bridgify</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-bridgify-4441525178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assured Allies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-assured-allies-4447671142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pagaya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-pagaya-4316888825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Lead (Hands-on)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sigal Dori (Tepper)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-hands-on-at-sigal-dori-tepper-4448430054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voyantis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-voyantis-4448003083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aidoc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-aidoc-4449444867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Immunai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-immunai-4450225101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-gotfriends-4445872562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chainalysis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-chainalysis-4413448060</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Team leader, DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zadara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/team-leader-devops-at-zadara-4448858731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4410866558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps / Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lendbuzz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-site-reliability-engineer-sre-at-lendbuzz-4437323317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glassbox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-glassbox-4426303995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps SRE Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Axon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-sre-engineer-at-axon-4440000142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer (Secrets Manager)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-secrets-manager-at-palo-alto-networks-4419602029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4429844723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevSecOps Engineer (AI-Driven Security)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-ai-driven-security-at-wix-4439730458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KMS Lighthouse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-kms-lighthouse-4447696634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chaos Engineer (Chaos DevOps)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Point Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/chaos-engineer-chaos-devops-at-check-point-software-4449688636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior SRE &amp; Linux Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-linux-infrastructure-engineer-at-mobileye-4439143553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE Technical Lead, DevOps Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BigPanda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-technical-lead-devops-group-at-bigpanda-4447980511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior SRE (IT Infrastructure)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-it-infrastructure-at-palo-alto-networks-4387086808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OFFROAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-offroad-4448139496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SciPlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-sciplay-4391151881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Tech Lead (BigBrain)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">monday.com AI engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-bigbrain-at-monday-com-ai-engineering-4449050085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer / Technical Lead (AWS &amp; GCP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AnyClip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ness Ziona, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-technical-lead-aws-gcp-at-anyclip-4446636401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Platform &amp; SRE Group Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-sre-group-leader-at-extreme-4450267100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer 24246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-24246-at-comblack-4450246628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">איש.אשת DevOps Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dahan Lab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%90%D7%99%D7%A9-%D7%90%D7%A9%D7%AA-devops-linux-at-dahan-lab-4449061474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rafael Advanced Defense Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/reliability-engineer-at-rafael-advanced-defense-systems-4437152427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineer III, Platform Engineering and Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-iii-platform-engineering-and-infrastructure-at-google-4448296220</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior DevOps Engineer — AI-Native</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-devops-engineer-%E2%80%94-ai-native-at-artac-4449655270</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-elbit-systems-israel-4394529806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAIRC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or HaNer, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-tairc-4448004083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Automation Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon Web Services (AWS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-automation-engineer-at-amazon-web-services-aws-4448323071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Akiva, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-tairc-4447388666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peak Innovation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-administrator-at-peak-innovation-4450276163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Security Engineer - Microsoft 365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantum Machines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-microsoft-365-at-quantum-machines-4362195136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Security Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logica-IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-at-logica-it-4448093647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Cloud Architect (37188)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-architect-37188-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4450240052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reline IT Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nes Ziona, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-reline-it-solutions-4447375577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YouCC Technologies Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashkelon, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ot-infrastructure-engineer-at-youcc-technologies-ltd-4448836015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps / Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-tairc-4447391644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calanit by one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-calanit-by-one-4448158765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alpha | Similarweb Partner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-alpha-similarweb-partner-4447362032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-artac-4449652341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior AI SRE Developer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helfy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Virtualization, Active Directory, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator - Linux, Windows #1350</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-linux-windows-%231350-at-rad-4443763825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waterfall Security Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-position-at-waterfall-security-solutions-4444878648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test Environment Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Networking, Monitoring, Databases, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/test-environment-support-engineer-at-abra-4442615924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Technical Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4442889333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, CI/CD, Virtualization, Active Directory, Windows Server, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-system-engineer-at-experis-israel-4437265103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autobrains Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4440209390</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud &amp; AI Security Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4932015101?gh_jid=4932015101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computer System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camtek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-4428415454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator &amp; IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inManage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">etoro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-etoro-4434952696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations Engineer I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Innovid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-engineer-i-at-innovid-4443857656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unilink Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-unilink-ltd-4446581282</t>
   </si>
   <si>
     <t xml:space="preserve">2026-07-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps / Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tipuli Tech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-engineer-at-tipuli-tech-4447115888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mid-Senior DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ArtAc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/mid-senior-devops-engineer-at-artac-4449656279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-elbit-systems-israel-4394529806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chaos Engineer (Chaos DevOps)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check Point Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/chaos-engineer-chaos-devops-at-check-point-software-4449688636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-artac-4449652341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bagira</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-bagira-4368663100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps engineer - Data Security DevOps Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-data-security-devops-team-at-thales-4428647317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4449116821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cato-networks-4430441382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OFFROAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-offroad-4448139496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WalkMe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-walkme-4380911237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ThetaRay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-thetaray-4446919831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevSecOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Playtika</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-at-playtika-4417616851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Descope</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-descope-4431665949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cyber-Hive</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-cyber-hive-4447364753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bridgify</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-bridgify-4441525178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yad2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-yad2-4439486812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assured Allies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-assured-allies-4447671142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pagaya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-pagaya-4316888825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Infrastructure &amp; Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-cloud-engineer-at-moon-active-4447031167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">איש.אשת DevOps Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dahan Lab</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%90%D7%99%D7%A9-%D7%90%D7%A9%D7%AA-devops-linux-at-dahan-lab-4449061474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oasis Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-oasis-security-4431605535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alpha | Similarweb Partner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-alpha-similarweb-partner-4447362032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Voyantis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-voyantis-4448003083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader - Infra and DevEx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kaltura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-infra-and-devex-at-kaltura-4442712745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aidoc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-aidoc-4449444867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Tech Lead (BigBrain)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monday.com AI engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-bigbrain-at-monday-com-ai-engineering-4449050085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZOLL Medical Corporation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-zoll-medical-corporation-4399156755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-gotfriends-4445872562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chainalysis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-chainalysis-4413448060</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Team leader, DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zadara</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/team-leader-devops-at-zadara-4448858731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps / Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAIRC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or HaNer, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-tairc-4447391644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-tairc-4448004083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior SRE &amp; Linux Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobileye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-linux-infrastructure-engineer-at-mobileye-4439143553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps / Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lendbuzz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-site-reliability-engineer-sre-at-lendbuzz-4437323317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE Technical Lead, DevOps Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BigPanda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-technical-lead-devops-group-at-bigpanda-4447980511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior SRE (IT Infrastructure)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-it-infrastructure-at-palo-alto-networks-4387086808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4410866558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps SRE Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Axon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-sre-engineer-at-axon-4440000142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (OpenShift Specialist)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Accel Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-openshift-specialist-at-accel-solutions-4448097045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4429844723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SciPlay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-sciplay-4391151881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viz.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-viz-ai-4437383686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer / Technical Lead (AWS &amp; GCP)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AnyClip</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ness Ziona, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-technical-lead-aws-gcp-at-anyclip-4446636401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineer III, Platform Engineering and Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-iii-platform-engineering-and-infrastructure-at-google-4448296220</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps Engineer — AI-Native</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-devops-engineer-%E2%80%94-ai-native-at-artac-4449655270</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Automation Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amazon Web Services (AWS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-automation-engineer-at-amazon-web-services-aws-4448323071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Akiva, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-tairc-4447388666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Security Engineer - Microsoft 365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantum Machines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-microsoft-365-at-quantum-machines-4362195136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reline IT Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nes Ziona, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-reline-it-solutions-4447375577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Immunai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-immunai-4450225101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevSecOps Engineer (AI-Driven Security)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-ai-driven-security-at-wix-4439730458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YouCC Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashkelon, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ot-infrastructure-engineer-at-youcc-technologies-ltd-4448836015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-infrastructure-engineer-at-nebius-4437660611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Infrastructure Engineer (Modiin)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-infrastructure-engineer-modiin-at-nebius-4437655743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology Infrastructure Engineer - 24262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-infrastructure-engineer-24262-at-comblack-4448306072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calanit by one</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-calanit-by-one-4448158765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Network Infrastructure Engineer - 20690</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-infrastructure-engineer-20690-at-comblack-4448189250</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.4%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior AI SRE Developer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helfy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Virtualization, Active Directory, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Waterfall Security Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-position-at-waterfall-security-solutions-4444878648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Technical Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4442889333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior QA Engineer - Student Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fives Intralogistics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-qa-engineer-student-position-at-fives-intralogistics-4446042176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fives</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-qa-engineer-student-position-at-fives-4436801163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Autobrains Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4440209390</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation student- Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-jerusalem-at-radware-4440152008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-at-radware-4437695096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud &amp; AI Security Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4932015101?gh_jid=4932015101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IOT student tester</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Motorola Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/iot-student-tester-at-motorola-solutions-4434451222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-4428415454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator &amp; IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inManage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">etoro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-etoro-4434952696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-01</t>
   </si>
   <si>
     <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
@@ -1568,7 +1586,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7">
@@ -1576,7 +1594,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -1584,7 +1602,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>41</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9">
@@ -1592,7 +1610,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>1227</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="10">
@@ -1664,7 +1682,7 @@
         <v>23</v>
       </c>
       <c r="B19" s="3">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20">
@@ -1691,20 +1709,20 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="B2" s="3">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="B3" s="3">
         <v>18</v>
@@ -1712,18 +1730,18 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="B4" s="3">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="B5" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1739,55 +1757,55 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="B2" s="3">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B3" s="3">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>241</v>
+        <v>281</v>
       </c>
       <c r="B4" s="3">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="B5" s="3">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="B6" s="3">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="B7" s="3">
         <v>26</v>
@@ -1795,7 +1813,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>361</v>
+        <v>468</v>
       </c>
       <c r="B8" s="3">
         <v>25</v>
@@ -1803,7 +1821,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>462</v>
+        <v>364</v>
       </c>
       <c r="B9" s="3">
         <v>24</v>
@@ -1811,31 +1829,31 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="B10" s="3">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="B11" s="3">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>358</v>
+        <v>470</v>
       </c>
       <c r="B12" s="3">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>464</v>
+        <v>361</v>
       </c>
       <c r="B13" s="3">
         <v>12</v>
@@ -1843,15 +1861,15 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>465</v>
+        <v>360</v>
       </c>
       <c r="B14" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="B15" s="3">
         <v>10</v>
@@ -1859,10 +1877,10 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>357</v>
+        <v>471</v>
       </c>
       <c r="B16" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1887,13 +1905,13 @@
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
     </row>
     <row r="2">
@@ -1904,10 +1922,10 @@
         <v>25</v>
       </c>
       <c r="C2" s="3">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -1916,88 +1934,88 @@
         <v>23</v>
       </c>
       <c r="B3" s="3">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C3" s="3">
-        <v>38.7</v>
+        <v>36.9</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>2.2</v>
+        <v>2.0</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>33.1</v>
+        <v>34.5</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>19.6</v>
+        <v>18.0</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>15.2</v>
+        <v>14.3</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2009,7 +2027,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="47" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -2081,7 +2099,7 @@
         <v>41</v>
       </c>
       <c r="J2" s="3">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3">
@@ -2113,7 +2131,7 @@
         <v>46</v>
       </c>
       <c r="J3" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -2145,7 +2163,7 @@
         <v>52</v>
       </c>
       <c r="J4" s="3">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5">
@@ -2177,7 +2195,7 @@
         <v>41</v>
       </c>
       <c r="J5" s="3">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6">
@@ -2209,7 +2227,7 @@
         <v>41</v>
       </c>
       <c r="J6" s="3">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7">
@@ -2241,7 +2259,7 @@
         <v>63</v>
       </c>
       <c r="J7" s="3">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8">
@@ -2273,7 +2291,7 @@
         <v>41</v>
       </c>
       <c r="J8" s="3">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9">
@@ -2305,7 +2323,7 @@
         <v>73</v>
       </c>
       <c r="J9" s="3">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10">
@@ -2337,7 +2355,7 @@
         <v>77</v>
       </c>
       <c r="J10" s="3">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11">
@@ -2369,7 +2387,7 @@
         <v>73</v>
       </c>
       <c r="J11" s="3">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12">
@@ -2401,7 +2419,7 @@
         <v>84</v>
       </c>
       <c r="J12" s="3">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="13">
@@ -2433,7 +2451,7 @@
         <v>90</v>
       </c>
       <c r="J13" s="3">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14">
@@ -2465,7 +2483,7 @@
         <v>95</v>
       </c>
       <c r="J14" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -2497,7 +2515,7 @@
         <v>46</v>
       </c>
       <c r="J15" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16">
@@ -2529,7 +2547,7 @@
         <v>102</v>
       </c>
       <c r="J16" s="3">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17">
@@ -2561,7 +2579,7 @@
         <v>77</v>
       </c>
       <c r="J17" s="3">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18">
@@ -2593,7 +2611,7 @@
         <v>109</v>
       </c>
       <c r="J18" s="3">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19">
@@ -2625,7 +2643,7 @@
         <v>115</v>
       </c>
       <c r="J19" s="3">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20">
@@ -2657,7 +2675,7 @@
         <v>41</v>
       </c>
       <c r="J20" s="3">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="21">
@@ -2689,7 +2707,7 @@
         <v>125</v>
       </c>
       <c r="J21" s="3">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="22">
@@ -2721,7 +2739,7 @@
         <v>130</v>
       </c>
       <c r="J22" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -2753,7 +2771,7 @@
         <v>136</v>
       </c>
       <c r="J23" s="3">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="24">
@@ -2783,7 +2801,7 @@
         <v>139</v>
       </c>
       <c r="J24" s="3">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="25">
@@ -2815,7 +2833,7 @@
         <v>41</v>
       </c>
       <c r="J25" s="3">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="26">
@@ -2845,7 +2863,7 @@
         <v>147</v>
       </c>
       <c r="J26" s="3">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="27">
@@ -2875,7 +2893,7 @@
         <v>151</v>
       </c>
       <c r="J27" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2902,10 +2920,10 @@
         <v>154</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>155</v>
+        <v>84</v>
       </c>
       <c r="J28" s="3">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="29">
@@ -2913,10 +2931,10 @@
         <v>116</v>
       </c>
       <c r="B29" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>156</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>157</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>49</v>
@@ -2929,27 +2947,27 @@
         <v>23</v>
       </c>
       <c r="H29" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="I29" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="I29" s="3" t="s">
-        <v>151</v>
-      </c>
       <c r="J29" s="3">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B30" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="C30" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="C30" s="3" t="s">
-        <v>161</v>
-      </c>
       <c r="D30" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>43</v>
@@ -2959,27 +2977,27 @@
         <v>23</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>84</v>
+        <v>151</v>
       </c>
       <c r="J30" s="3">
-        <v>83</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>116</v>
+        <v>162</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>163</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>43</v>
@@ -2989,13 +3007,13 @@
         <v>23</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>130</v>
+        <v>84</v>
       </c>
       <c r="J31" s="3">
-        <v>2</v>
+        <v>84</v>
       </c>
     </row>
     <row r="32">
@@ -3003,13 +3021,13 @@
         <v>116</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>43</v>
@@ -3019,10 +3037,10 @@
         <v>23</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>167</v>
+        <v>130</v>
       </c>
       <c r="J32" s="3">
         <v>3</v>
@@ -3052,10 +3070,10 @@
         <v>169</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="J33" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34">
@@ -3063,13 +3081,13 @@
         <v>116</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>43</v>
@@ -3082,21 +3100,21 @@
         <v>172</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="J34" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="C35" s="3" t="s">
         <v>175</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>176</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>49</v>
@@ -3109,24 +3127,24 @@
         <v>23</v>
       </c>
       <c r="H35" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="I35" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="I35" s="3" t="s">
-        <v>178</v>
-      </c>
       <c r="J35" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="C36" s="3" t="s">
         <v>180</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>181</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>122</v>
@@ -3139,10 +3157,10 @@
         <v>23</v>
       </c>
       <c r="H36" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="I36" s="3" t="s">
         <v>182</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>151</v>
       </c>
       <c r="J36" s="3">
         <v>0</v>
@@ -3150,19 +3168,19 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>116</v>
+        <v>183</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>185</v>
+        <v>122</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
@@ -3175,7 +3193,7 @@
         <v>187</v>
       </c>
       <c r="J37" s="3">
-        <v>62</v>
+        <v>45</v>
       </c>
     </row>
     <row r="38">
@@ -3183,10 +3201,10 @@
         <v>188</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>189</v>
+        <v>163</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>49</v>
@@ -3194,7 +3212,9 @@
       <c r="E38" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F38" s="3"/>
+      <c r="F38" s="3" t="s">
+        <v>189</v>
+      </c>
       <c r="G38" s="3" t="s">
         <v>23</v>
       </c>
@@ -3202,10 +3222,10 @@
         <v>190</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>151</v>
+        <v>191</v>
       </c>
       <c r="J38" s="3">
-        <v>0</v>
+        <v>53</v>
       </c>
     </row>
     <row r="39">
@@ -3213,13 +3233,13 @@
         <v>53</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>38</v>
@@ -3229,30 +3249,30 @@
         <v>23</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I39" s="3" t="s">
         <v>151</v>
       </c>
       <c r="J39" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>192</v>
+        <v>116</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>194</v>
+        <v>160</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
@@ -3262,21 +3282,21 @@
         <v>195</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="J40" s="3">
-        <v>44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>197</v>
+        <v>116</v>
       </c>
       <c r="B41" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C41" s="3" t="s">
         <v>160</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>171</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>49</v>
@@ -3284,20 +3304,18 @@
       <c r="E41" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F41" s="3" t="s">
+      <c r="F41" s="3"/>
+      <c r="G41" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="I41" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>200</v>
-      </c>
       <c r="J41" s="3">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="42">
@@ -3305,10 +3323,10 @@
         <v>53</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>49</v>
@@ -3321,10 +3339,10 @@
         <v>23</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>151</v>
+        <v>182</v>
       </c>
       <c r="J42" s="3">
         <v>0</v>
@@ -3332,16 +3350,16 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>116</v>
+        <v>162</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>157</v>
+        <v>202</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>43</v>
@@ -3351,89 +3369,89 @@
         <v>23</v>
       </c>
       <c r="H43" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="I43" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>205</v>
-      </c>
       <c r="J43" s="3">
-        <v>48</v>
+        <v>22</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B44" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H44" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="C44" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F44" s="3"/>
-      <c r="G44" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H44" s="3" t="s">
+      <c r="I44" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>167</v>
-      </c>
       <c r="J44" s="3">
-        <v>3</v>
+        <v>68</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>47</v>
+        <v>208</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>198</v>
-      </c>
+      <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>210</v>
+        <v>182</v>
       </c>
       <c r="J45" s="3">
-        <v>67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>116</v>
+        <v>211</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>122</v>
+        <v>214</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>43</v>
@@ -3443,21 +3461,21 @@
         <v>23</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>173</v>
+        <v>147</v>
       </c>
       <c r="J46" s="3">
-        <v>6</v>
+        <v>64</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>60</v>
@@ -3469,19 +3487,19 @@
         <v>43</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>77</v>
       </c>
       <c r="J47" s="3">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="48">
@@ -3489,10 +3507,10 @@
         <v>53</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>49</v>
@@ -3505,43 +3523,43 @@
         <v>23</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="J48" s="3">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>220</v>
+        <v>53</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>176</v>
+        <v>153</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>223</v>
+        <v>170</v>
       </c>
       <c r="J49" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50">
@@ -3552,7 +3570,7 @@
         <v>224</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>49</v>
@@ -3568,24 +3586,24 @@
         <v>225</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="J50" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B51" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="B51" s="3" t="s">
-        <v>227</v>
-      </c>
       <c r="C51" s="3" t="s">
-        <v>228</v>
+        <v>153</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>229</v>
+        <v>49</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>38</v>
@@ -3595,24 +3613,24 @@
         <v>23</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="J51" s="3">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>53</v>
+        <v>229</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>49</v>
@@ -3625,24 +3643,24 @@
         <v>23</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="J52" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>53</v>
+        <v>232</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>49</v>
@@ -3655,72 +3673,70 @@
         <v>23</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>236</v>
+        <v>151</v>
       </c>
       <c r="J53" s="3">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>237</v>
+        <v>53</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>170</v>
+        <v>235</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>173</v>
+        <v>237</v>
       </c>
       <c r="J54" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F55" s="3"/>
+      <c r="G55" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H55" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="B55" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="E55" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="G55" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H55" s="3" t="s">
-        <v>242</v>
-      </c>
       <c r="I55" s="3" t="s">
-        <v>223</v>
+        <v>151</v>
       </c>
       <c r="J55" s="3">
         <v>1</v>
@@ -3728,13 +3744,13 @@
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>53</v>
+        <v>240</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>243</v>
+        <v>171</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>49</v>
@@ -3747,24 +3763,24 @@
         <v>23</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>196</v>
+        <v>170</v>
       </c>
       <c r="J56" s="3">
-        <v>44</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>53</v>
+        <v>242</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>49</v>
@@ -3777,84 +3793,84 @@
         <v>23</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>223</v>
+        <v>84</v>
       </c>
       <c r="J57" s="3">
-        <v>1</v>
+        <v>84</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="I58" s="3" t="s">
         <v>151</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="C59" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="B59" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>153</v>
-      </c>
       <c r="D59" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>253</v>
+        <v>207</v>
       </c>
       <c r="J59" s="3">
-        <v>14</v>
+        <v>68</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>53</v>
+        <v>252</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>49</v>
@@ -3867,27 +3883,27 @@
         <v>23</v>
       </c>
       <c r="H60" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="I60" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>223</v>
-      </c>
       <c r="J60" s="3">
-        <v>1</v>
+        <v>29</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="B61" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="B61" s="3" t="s">
+      <c r="C61" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="C61" s="3" t="s">
-        <v>171</v>
-      </c>
       <c r="D61" s="3" t="s">
-        <v>49</v>
+        <v>258</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>38</v>
@@ -3897,10 +3913,10 @@
         <v>23</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>151</v>
+        <v>182</v>
       </c>
       <c r="J61" s="3">
         <v>0</v>
@@ -3908,46 +3924,46 @@
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>60</v>
+        <v>153</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>139</v>
+        <v>158</v>
       </c>
       <c r="J62" s="3">
-        <v>71</v>
+        <v>24</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>226</v>
+        <v>263</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>168</v>
+        <v>264</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>157</v>
+        <v>257</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>49</v>
+        <v>258</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>38</v>
@@ -3957,24 +3973,24 @@
         <v>23</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="J63" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>263</v>
+        <v>53</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>49</v>
@@ -3987,24 +4003,24 @@
         <v>23</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>84</v>
+        <v>268</v>
       </c>
       <c r="J64" s="3">
-        <v>83</v>
+        <v>42</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>49</v>
@@ -4012,32 +4028,34 @@
       <c r="E65" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F65" s="3"/>
+      <c r="F65" s="3" t="s">
+        <v>189</v>
+      </c>
       <c r="G65" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="I65" s="3" t="s">
         <v>151</v>
       </c>
       <c r="J65" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>271</v>
+        <v>257</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>122</v>
+        <v>258</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>43</v>
@@ -4047,27 +4065,27 @@
         <v>23</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>151</v>
+        <v>130</v>
       </c>
       <c r="J66" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>271</v>
+        <v>153</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>43</v>
@@ -4077,24 +4095,24 @@
         <v>23</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="I67" s="3" t="s">
         <v>151</v>
       </c>
       <c r="J67" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>145</v>
@@ -4103,30 +4121,30 @@
         <v>38</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>241</v>
+        <v>281</v>
       </c>
       <c r="G68" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="J68" s="3">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>49</v>
@@ -4139,24 +4157,24 @@
         <v>23</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>282</v>
+        <v>130</v>
       </c>
       <c r="J69" s="3">
-        <v>28</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>284</v>
+        <v>264</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>49</v>
@@ -4169,24 +4187,24 @@
         <v>23</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>130</v>
+        <v>77</v>
       </c>
       <c r="J70" s="3">
-        <v>2</v>
+        <v>71</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>286</v>
+        <v>53</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>49</v>
@@ -4199,27 +4217,27 @@
         <v>23</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>77</v>
+        <v>170</v>
       </c>
       <c r="J71" s="3">
-        <v>70</v>
+        <v>4</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>289</v>
+        <v>56</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>290</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>291</v>
+        <v>153</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>38</v>
@@ -4229,24 +4247,24 @@
         <v>23</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>210</v>
+        <v>84</v>
       </c>
       <c r="J72" s="3">
-        <v>67</v>
+        <v>84</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="B73" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="B73" s="3" t="s">
-        <v>294</v>
-      </c>
       <c r="C73" s="3" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>49</v>
@@ -4259,154 +4277,156 @@
         <v>23</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="J73" s="3">
-        <v>23</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="B74" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="B74" s="3" t="s">
+      <c r="C74" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="C74" s="3" t="s">
-        <v>176</v>
-      </c>
       <c r="D74" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F74" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>298</v>
+      </c>
       <c r="G74" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>151</v>
+        <v>237</v>
       </c>
       <c r="J74" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>53</v>
+        <v>300</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F75" s="3"/>
       <c r="G75" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>301</v>
+        <v>182</v>
       </c>
       <c r="J75" s="3">
-        <v>41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>56</v>
+        <v>303</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>84</v>
+        <v>182</v>
       </c>
       <c r="J76" s="3">
-        <v>83</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>56</v>
+        <v>306</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F77" s="3"/>
+        <v>43</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>281</v>
+      </c>
       <c r="G77" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>306</v>
+        <v>237</v>
       </c>
       <c r="J77" s="3">
-        <v>25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>309</v>
+        <v>149</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>122</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F78" s="3" t="s">
-        <v>310</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
         <v>23</v>
       </c>
@@ -4414,10 +4434,10 @@
         <v>311</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>223</v>
+        <v>182</v>
       </c>
       <c r="J78" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -4428,7 +4448,7 @@
         <v>313</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>49</v>
@@ -4444,10 +4464,10 @@
         <v>314</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="J79" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
@@ -4455,10 +4475,10 @@
         <v>315</v>
       </c>
       <c r="B80" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C80" s="3" t="s">
         <v>180</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>181</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>122</v>
@@ -4477,21 +4497,21 @@
         <v>151</v>
       </c>
       <c r="J80" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>317</v>
+        <v>116</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>318</v>
+        <v>212</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>319</v>
+        <v>213</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>185</v>
+        <v>214</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>43</v>
@@ -4501,27 +4521,27 @@
         <v>23</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>223</v>
+        <v>318</v>
       </c>
       <c r="J81" s="3">
-        <v>1</v>
+        <v>63</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="C82" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="B82" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>322</v>
-      </c>
       <c r="D82" s="3" t="s">
-        <v>185</v>
+        <v>122</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>43</v>
@@ -4531,34 +4551,32 @@
         <v>23</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I82" s="3" t="s">
         <v>151</v>
       </c>
       <c r="J82" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="B83" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="B83" s="3" t="s">
+      <c r="C83" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="C83" s="3" t="s">
-        <v>171</v>
-      </c>
       <c r="D83" s="3" t="s">
-        <v>49</v>
+        <v>214</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F83" s="3" t="s">
-        <v>198</v>
-      </c>
+      <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
         <v>23</v>
       </c>
@@ -4566,10 +4584,10 @@
         <v>326</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>84</v>
+        <v>237</v>
       </c>
       <c r="J83" s="3">
-        <v>83</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
@@ -4577,13 +4595,13 @@
         <v>327</v>
       </c>
       <c r="B84" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="C84" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="C84" s="3" t="s">
-        <v>329</v>
-      </c>
       <c r="D84" s="3" t="s">
-        <v>122</v>
+        <v>214</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>43</v>
@@ -4593,10 +4611,10 @@
         <v>23</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>223</v>
+        <v>151</v>
       </c>
       <c r="J84" s="3">
         <v>1</v>
@@ -4604,19 +4622,19 @@
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>53</v>
+        <v>330</v>
       </c>
       <c r="B85" s="3" t="s">
         <v>331</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F85" s="3"/>
       <c r="G85" s="3" t="s">
@@ -4626,7 +4644,7 @@
         <v>332</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>151</v>
+        <v>182</v>
       </c>
       <c r="J85" s="3">
         <v>0</v>
@@ -4640,7 +4658,7 @@
         <v>334</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="D86" s="3" t="s">
         <v>49</v>
@@ -4649,7 +4667,7 @@
         <v>43</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="G86" s="3" t="s">
         <v>23</v>
@@ -4658,10 +4676,10 @@
         <v>335</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>151</v>
+        <v>84</v>
       </c>
       <c r="J86" s="3">
-        <v>0</v>
+        <v>84</v>
       </c>
     </row>
     <row r="87">
@@ -4672,67 +4690,69 @@
         <v>337</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>338</v>
+        <v>153</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F87" s="3"/>
+      <c r="F87" s="3" t="s">
+        <v>189</v>
+      </c>
       <c r="G87" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>130</v>
+        <v>182</v>
       </c>
       <c r="J87" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>341</v>
+        <v>209</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>181</v>
+        <v>149</v>
       </c>
       <c r="D88" s="3" t="s">
         <v>122</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F88" s="3"/>
       <c r="G88" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>343</v>
+        <v>182</v>
       </c>
       <c r="J88" s="3">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>194</v>
+        <v>343</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>122</v>
@@ -4745,27 +4765,27 @@
         <v>23</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="J89" s="3">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="B90" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="B90" s="3" t="s">
+      <c r="C90" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="C90" s="3" t="s">
-        <v>157</v>
-      </c>
       <c r="D90" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>43</v>
@@ -4781,7 +4801,7 @@
         <v>130</v>
       </c>
       <c r="J90" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="91">
@@ -4789,10 +4809,10 @@
         <v>349</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>350</v>
+        <v>320</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>351</v>
+        <v>321</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>122</v>
@@ -4800,17 +4820,15 @@
       <c r="E91" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F91" s="3" t="s">
-        <v>241</v>
-      </c>
+      <c r="F91" s="3"/>
       <c r="G91" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>223</v>
+        <v>151</v>
       </c>
       <c r="J91" s="3">
         <v>1</v>
@@ -4818,13 +4836,13 @@
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="C92" s="3" t="s">
         <v>353</v>
-      </c>
-      <c r="B92" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="C92" s="3" t="s">
-        <v>351</v>
       </c>
       <c r="D92" s="3" t="s">
         <v>122</v>
@@ -4832,7 +4850,9 @@
       <c r="E92" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F92" s="3"/>
+      <c r="F92" s="3" t="s">
+        <v>281</v>
+      </c>
       <c r="G92" s="3" t="s">
         <v>23</v>
       </c>
@@ -4840,14 +4860,74 @@
         <v>354</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>130</v>
+        <v>237</v>
       </c>
       <c r="J92" s="3">
         <v>2</v>
       </c>
     </row>
+    <row r="93">
+      <c r="A93" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F93" s="3"/>
+      <c r="G93" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H93" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="I93" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="J93" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F94" s="3"/>
+      <c r="G94" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="J94" s="3">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J92"/>
+  <autoFilter ref="A1:J94"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -4940,6 +5020,8 @@
     <hyperlink ref="H90" r:id="rId89"/>
     <hyperlink ref="H91" r:id="rId90"/>
     <hyperlink ref="H92" r:id="rId91"/>
+    <hyperlink ref="H93" r:id="rId92"/>
+    <hyperlink ref="H94" r:id="rId93"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4947,8 +5029,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="50" customWidth="1"/>
-    <col min="2" max="2" width="27" customWidth="1"/>
+    <col min="1" max="1" width="42" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -4981,13 +5063,13 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>116</v>
+        <v>178</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>148</v>
+        <v>179</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>149</v>
+        <v>180</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -4995,7 +5077,7 @@
         <v>23</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>150</v>
+        <v>181</v>
       </c>
     </row>
     <row r="3">
@@ -5003,10 +5085,10 @@
         <v>116</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>156</v>
+        <v>194</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -5014,18 +5096,18 @@
         <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>158</v>
+        <v>195</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>179</v>
+        <v>53</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -5033,18 +5115,18 @@
         <v>23</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>182</v>
+        <v>200</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>188</v>
+        <v>208</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>189</v>
+        <v>209</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5052,18 +5134,18 @@
         <v>23</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>190</v>
+        <v>210</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>53</v>
+        <v>229</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>180</v>
+        <v>230</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>181</v>
+        <v>160</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -5071,18 +5153,18 @@
         <v>23</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>191</v>
+        <v>231</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>53</v>
+        <v>240</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>201</v>
+        <v>256</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>171</v>
+        <v>257</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -5090,18 +5172,18 @@
         <v>23</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>202</v>
+        <v>259</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>247</v>
+        <v>263</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>248</v>
+        <v>264</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>171</v>
+        <v>257</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -5109,18 +5191,18 @@
         <v>23</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>249</v>
+        <v>265</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>256</v>
+        <v>300</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>257</v>
+        <v>301</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -5128,18 +5210,18 @@
         <v>23</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>258</v>
+        <v>302</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>266</v>
+        <v>303</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>267</v>
+        <v>304</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -5147,18 +5229,18 @@
         <v>23</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>268</v>
+        <v>305</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>269</v>
+        <v>309</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>270</v>
+        <v>310</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>271</v>
+        <v>149</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -5166,18 +5248,18 @@
         <v>23</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>272</v>
+        <v>311</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>273</v>
+        <v>330</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>270</v>
+        <v>331</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>271</v>
+        <v>149</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
@@ -5185,18 +5267,18 @@
         <v>23</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>274</v>
+        <v>332</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>296</v>
+        <v>336</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>297</v>
+        <v>337</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>176</v>
+        <v>153</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
@@ -5204,18 +5286,18 @@
         <v>23</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>298</v>
+        <v>338</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>315</v>
+        <v>339</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>180</v>
+        <v>209</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>181</v>
+        <v>149</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
@@ -5223,68 +5305,11 @@
         <v>23</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G17"/>
+  <autoFilter ref="A1:G14"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -5299,9 +5324,6 @@
     <hyperlink ref="G12" r:id="rId11"/>
     <hyperlink ref="G13" r:id="rId12"/>
     <hyperlink ref="G14" r:id="rId13"/>
-    <hyperlink ref="G15" r:id="rId14"/>
-    <hyperlink ref="G16" r:id="rId15"/>
-    <hyperlink ref="G17" r:id="rId16"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5315,23 +5337,23 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="B2" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B3" s="3">
         <v>15</v>
@@ -5339,7 +5361,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="B4" s="3">
         <v>15</v>
@@ -5347,7 +5369,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B5" s="3">
         <v>14</v>
@@ -5355,7 +5377,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>241</v>
+        <v>281</v>
       </c>
       <c r="B6" s="3">
         <v>12</v>
@@ -5363,7 +5385,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="B7" s="3">
         <v>11</v>
@@ -5371,7 +5393,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="B8" s="3">
         <v>10</v>
@@ -5379,7 +5401,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B9" s="3">
         <v>9</v>
@@ -5387,7 +5409,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B10" s="3">
         <v>9</v>
@@ -5395,7 +5417,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="B11" s="3">
         <v>8</v>
@@ -5403,7 +5425,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B12" s="3">
         <v>7</v>
@@ -5411,7 +5433,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B13" s="3">
         <v>7</v>
@@ -5419,7 +5441,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="B14" s="3">
         <v>6</v>
@@ -5427,7 +5449,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B15" s="3">
         <v>5</v>
@@ -5435,7 +5457,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B16" s="3">
         <v>4</v>
@@ -5448,7 +5470,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="1" max="1" width="34" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5457,7 +5479,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="2">
@@ -5494,7 +5516,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -5502,7 +5524,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>270</v>
+        <v>320</v>
       </c>
       <c r="B7" s="3">
         <v>3</v>
@@ -5526,7 +5548,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -5534,7 +5556,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5542,7 +5564,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>170</v>
+        <v>209</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5550,7 +5572,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>341</v>
+        <v>212</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -5558,7 +5580,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>347</v>
+        <v>264</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -5588,23 +5610,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="2">
@@ -5696,7 +5718,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C8" s="3">
         <v>4.2</v>
@@ -5710,7 +5732,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>270</v>
+        <v>320</v>
       </c>
       <c r="C9" s="3">
         <v>3.6</v>
@@ -5738,7 +5760,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C11" s="3">
         <v>2.8</v>
@@ -5752,13 +5774,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>127</v>
+        <v>209</v>
       </c>
       <c r="C12" s="3">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="D12" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -5766,13 +5788,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>160</v>
+        <v>127</v>
       </c>
       <c r="C13" s="3">
         <v>2.6</v>
       </c>
       <c r="D13" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -5780,10 +5802,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="C14" s="3">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="D14" s="3">
         <v>2</v>
@@ -5794,7 +5816,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>341</v>
+        <v>212</v>
       </c>
       <c r="C15" s="3">
         <v>2.4</v>
@@ -5808,7 +5830,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>347</v>
+        <v>264</v>
       </c>
       <c r="C16" s="3">
         <v>2.4</v>
@@ -5834,10 +5856,10 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="2">
@@ -5859,7 +5881,7 @@
         <v>45</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="4">
@@ -5867,10 +5889,10 @@
         <v>38</v>
       </c>
       <c r="B4" s="3">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
   </sheetData>
@@ -5889,7 +5911,7 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="2">
@@ -5897,7 +5919,7 @@
         <v>49</v>
       </c>
       <c r="B2" s="3">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3">
@@ -5905,28 +5927,28 @@
         <v>122</v>
       </c>
       <c r="B3" s="3">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>185</v>
+        <v>214</v>
       </c>
       <c r="B4" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>37</v>
+        <v>258</v>
       </c>
       <c r="B5" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>145</v>
+        <v>37</v>
       </c>
       <c r="B6" s="3">
         <v>2</v>
@@ -5934,15 +5956,15 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>112</v>
+        <v>145</v>
       </c>
       <c r="B7" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>229</v>
+        <v>112</v>
       </c>
       <c r="B8" s="3">
         <v>1</v>
@@ -5969,10 +5991,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>26</v>
@@ -5984,10 +6006,10 @@
         <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>21</v>
@@ -6004,31 +6026,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>60</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="3">
@@ -6036,31 +6058,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>60</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="4">
@@ -6068,31 +6090,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="5">
@@ -6100,31 +6122,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="F5" s="3">
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>125</v>
+        <v>400</v>
       </c>
     </row>
     <row r="6">
@@ -6132,31 +6154,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>91</v>
+        <v>401</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>86</v>
+        <v>402</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>87</v>
+        <v>153</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="F6" s="3">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>94</v>
+        <v>404</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>95</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7">
@@ -6164,31 +6186,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>399</v>
+        <v>91</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>400</v>
+        <v>86</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>401</v>
+        <v>87</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="F7" s="3">
         <v>92</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>403</v>
+        <v>94</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>167</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8">
@@ -6196,31 +6218,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>42</v>
+        <v>407</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>35</v>
+        <v>408</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>36</v>
+        <v>409</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="F8" s="3">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>45</v>
+        <v>411</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>46</v>
+        <v>170</v>
       </c>
     </row>
     <row r="9">
@@ -6228,31 +6250,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>405</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>388</v>
-      </c>
       <c r="F9" s="3">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>408</v>
+        <v>45</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>95</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10">
@@ -6260,31 +6282,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>411</v>
+        <v>149</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>397</v>
+        <v>415</v>
       </c>
       <c r="F10" s="3">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="11">
@@ -6292,31 +6314,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>411</v>
+        <v>153</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="F11" s="3">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>417</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12">
@@ -6324,31 +6346,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>171</v>
+        <v>60</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>420</v>
+        <v>391</v>
       </c>
       <c r="F12" s="3">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="13">
@@ -6356,31 +6378,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>397</v>
+        <v>415</v>
       </c>
       <c r="F13" s="3">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>428</v>
+        <v>204</v>
       </c>
     </row>
     <row r="14">
@@ -6388,31 +6410,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>425</v>
+        <v>35</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>171</v>
+        <v>36</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="F14" s="3">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>231</v>
+        <v>418</v>
       </c>
     </row>
     <row r="15">
@@ -6420,31 +6442,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>35</v>
+        <v>436</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>36</v>
+        <v>437</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="F15" s="3">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
     </row>
     <row r="16">
@@ -6452,31 +6474,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>313</v>
+        <v>249</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>171</v>
+        <v>250</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="F16" s="3">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>84</v>
+        <v>221</v>
       </c>
     </row>
     <row r="17">
@@ -6484,31 +6506,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="F17" s="3">
         <v>52</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
     </row>
     <row r="18">
@@ -6516,31 +6538,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>443</v>
+        <v>428</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>290</v>
+        <v>449</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>291</v>
+        <v>450</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>388</v>
+        <v>415</v>
       </c>
       <c r="F18" s="3">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>219</v>
+        <v>453</v>
       </c>
     </row>
     <row r="19">
@@ -6548,31 +6570,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="F19" s="3">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>450</v>
+        <v>130</v>
       </c>
     </row>
     <row r="20">
@@ -6580,31 +6602,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>418</v>
+        <v>341</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>452</v>
+        <v>160</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>420</v>
+        <v>391</v>
       </c>
       <c r="F20" s="3">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
     </row>
     <row r="21">
@@ -6621,13 +6643,13 @@
         <v>60</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="F21" s="3">
         <v>44</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>24</v>

--- a/reports/devops-jobs-israel-2026-W32.xlsx
+++ b/reports/devops-jobs-israel-2026-W32.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="465">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-07T07:36:16</t>
+    <t xml:space="preserve">2026-08-09T07:08:34</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Junior %</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2%</t>
+    <t xml:space="preserve">3.3%</t>
   </si>
   <si>
     <t xml:space="preserve">Salary disclosure rate %</t>
@@ -264,228 +264,219 @@
     <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4673075006</t>
   </si>
   <si>
-    <t xml:space="preserve">Software Architect - DevOps Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Networking, Security, Observability, FinOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668071006</t>
+    <t xml:space="preserve">Data Platform Engineering Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taboola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Linux, Kafka, Airflow, dbt, Spark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/7903597?gh_jid=7903597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Release Engineering Intern (Part-Time, 80%, One-year temporary position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Docker, CI/CD, Linux, Python, Helm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8069193?gh_jid=8069193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Terraform, Ansible, Docker, CI/CD, Linux, Python, Prometheus, Grafana, ELK/Elastic, Networking, Argo CD, Rust, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8070135?gh_jid=8070135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Development Team Leader – Production Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/7903594?gh_jid=7903594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Backend Engineer, Platform Foundations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Similarweb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Ansible, Docker, CI/CD, Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7962665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, GCP, Docker, Linux, Python, Networking, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7938197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Engineer - Billing Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Python, Airflow, Spark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8620283002?gh_jid=8620283002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Python, Bash/Shell, Prometheus, Grafana, Security, Argo CD, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/5810373004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riskified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lisbon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel (other)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Terraform, Linux, Python, Go, Networking, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8587299002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevEx/DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Axonius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, GCP, Terraform, Ansible, Docker, CI/CD, Linux, Python, Security, Observability, FinOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7824320003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Science &amp; ML-Ops Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security, Observability, AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8539030002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QA Automation Engineer (Temporary Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8542303002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Talent Acquisition Partner - R&amp;D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lightricks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8576517002&amp;gh_jid=8576517002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scytale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-scytale-4449488382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connecteam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4290904319</t>
   </si>
   <si>
     <t xml:space="preserve">2026-05-15</t>
   </si>
   <si>
-    <t xml:space="preserve">Data Platform Engineering Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taboola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Linux, Kafka, Airflow, dbt, Spark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/7903597?gh_jid=7903597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Release Engineering Intern (Part-Time, 80%, One-year temporary position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Docker, CI/CD, Linux, Python, Helm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8069193?gh_jid=8069193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Terraform, Ansible, Docker, CI/CD, Linux, Python, Prometheus, Grafana, ELK/Elastic, Networking, Argo CD, Rust, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8070135?gh_jid=8070135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Development Team Leader – Production Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/7903594?gh_jid=7903594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Backend Engineer, Platform Foundations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Similarweb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Ansible, Docker, CI/CD, Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7962665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, GCP, Docker, Linux, Python, Networking, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7938197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Engineer - Billing Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Python, Airflow, Spark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8620283002?gh_jid=8620283002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Python, Bash/Shell, Prometheus, Grafana, Security, Argo CD, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/5810373004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riskified</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lisbon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel (other)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Terraform, Linux, Python, Go, Networking, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8587299002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevEx/DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Axonius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, GCP, Terraform, Ansible, Docker, CI/CD, Linux, Python, Security, Observability, FinOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7824320003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Science &amp; ML-Ops Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security, Observability, AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8539030002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QA Automation Engineer (Temporary Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8542303002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Talent Acquisition Partner - R&amp;D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lightricks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8576517002&amp;gh_jid=8576517002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scytale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-scytale-4449488382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connecteam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4290904319</t>
-  </si>
-  <si>
     <t xml:space="preserve">Checkmarx</t>
   </si>
   <si>
@@ -534,27 +525,24 @@
     <t xml:space="preserve">2026-08-03</t>
   </si>
   <si>
+    <t xml:space="preserve">DevOps Engineer Cloud Engineering Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WalkMe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-engineering-team-at-walkme-4413022554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-17</t>
+  </si>
+  <si>
     <t xml:space="preserve">Gotfriends</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4445878493</t>
   </si>
   <si>
-    <t xml:space="preserve">DevOps / Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tipuli Tech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-engineer-at-tipuli-tech-4447115888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-02</t>
-  </si>
-  <si>
     <t xml:space="preserve">Mid-Senior DevOps Engineer</t>
   </si>
   <si>
@@ -570,6 +558,45 @@
     <t xml:space="preserve">2026-08-07</t>
   </si>
   <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-elbit-systems-israel-4394529806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chaos Engineer (Chaos DevOps)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Point Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/chaos-engineer-chaos-devops-at-check-point-software-4449688636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-4441121726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-artac-4449652341</t>
+  </si>
+  <si>
     <t xml:space="preserve">DevOps Lead</t>
   </si>
   <si>
@@ -597,6 +624,18 @@
     <t xml:space="preserve">2026-06-15</t>
   </si>
   <si>
+    <t xml:space="preserve">DevOps Engineer III</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CrowdStrike</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-iii-at-crowdstrike-4438706386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-17</t>
+  </si>
+  <si>
     <t xml:space="preserve">Matia</t>
   </si>
   <si>
@@ -609,13 +648,10 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-compie-technologies-4450271080</t>
   </si>
   <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cato-networks-4430441382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-19</t>
+    <t xml:space="preserve">OFFROAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-offroad-4448139496</t>
   </si>
   <si>
     <t xml:space="preserve">Viz.ai</t>
@@ -636,9 +672,6 @@
     <t xml:space="preserve">2026-07-16</t>
   </si>
   <si>
-    <t xml:space="preserve">WalkMe</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-walkme-4380911237</t>
   </si>
   <si>
@@ -657,27 +690,9 @@
     <t xml:space="preserve">GenAI Group DevOps Engineer</t>
   </si>
   <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/genai-group-devops-engineer-at-elbit-systems-israel-4395652910</t>
   </si>
   <si>
-    <t xml:space="preserve">DevSecOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Playtika</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-at-playtika-4417616851</t>
-  </si>
-  <si>
     <t xml:space="preserve">Descope</t>
   </si>
   <si>
@@ -717,6 +732,27 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-hands-on-at-sigal-dori-tepper-4448430054</t>
   </si>
   <si>
+    <t xml:space="preserve">איש.אשת DevOps Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dahan Lab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%90%D7%99%D7%A9-%D7%90%D7%A9%D7%AA-devops-linux-at-dahan-lab-4449061474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alpha | Similarweb Partner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-alpha-similarweb-partner-4447362032</t>
+  </si>
+  <si>
     <t xml:space="preserve">Devops Team Lead</t>
   </si>
   <si>
@@ -732,21 +768,57 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-aidoc-4449444867</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-05</t>
-  </si>
-  <si>
     <t xml:space="preserve">Immunai</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-immunai-4450225101</t>
   </si>
   <si>
+    <t xml:space="preserve">DevOps Tech Lead (BigBrain)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">monday.com AI engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-bigbrain-at-monday-com-ai-engineering-4449050085</t>
+  </si>
+  <si>
     <t xml:space="preserve">DevOps Team Lead</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-gotfriends-4445872562</t>
   </si>
   <si>
+    <t xml:space="preserve">Team leader, DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zadara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/team-leader-devops-at-zadara-4448858731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps / Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAIRC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or HaNer, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-tairc-4447391644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer- Posture</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dream</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-posture-at-dream-4415919013</t>
+  </si>
+  <si>
     <t xml:space="preserve">Senior Site Reliability Engineer</t>
   </si>
   <si>
@@ -756,49 +828,52 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-chainalysis-4413448060</t>
   </si>
   <si>
-    <t xml:space="preserve">Team leader, DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zadara</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/team-leader-devops-at-zadara-4448858731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4410866558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps / Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lendbuzz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-site-reliability-engineer-sre-at-lendbuzz-4437323317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Glassbox</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-glassbox-4426303995</t>
+    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Platform Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IgniteTech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-reliability-engineer-at-ignitetech-4442432462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-tairc-4448004083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior SRE &amp; Linux Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-linux-infrastructure-engineer-at-mobileye-4439143553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE Technical Lead, DevOps Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BigPanda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-technical-lead-devops-group-at-bigpanda-4447980511</t>
   </si>
   <si>
     <t xml:space="preserve">Senior DevOps SRE Engineer</t>
@@ -810,15 +885,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-sre-engineer-at-axon-4440000142</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior DevOps Engineer (Secrets Manager)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-secrets-manager-at-palo-alto-networks-4419602029</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fetcherr</t>
   </si>
   <si>
@@ -828,67 +894,10 @@
     <t xml:space="preserve">2026-06-26</t>
   </si>
   <si>
-    <t xml:space="preserve">DevSecOps Engineer (AI-Driven Security)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-ai-driven-security-at-wix-4439730458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KMS Lighthouse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-kms-lighthouse-4447696634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chaos Engineer (Chaos DevOps)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check Point Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/chaos-engineer-chaos-devops-at-check-point-software-4449688636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior SRE &amp; Linux Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobileye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-linux-infrastructure-engineer-at-mobileye-4439143553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE Technical Lead, DevOps Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BigPanda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-technical-lead-devops-group-at-bigpanda-4447980511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior SRE (IT Infrastructure)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-it-infrastructure-at-palo-alto-networks-4387086808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OFFROAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-offroad-4448139496</t>
+    <t xml:space="preserve">Alictus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-alictus-4450008323</t>
   </si>
   <si>
     <t xml:space="preserve">SciPlay</t>
@@ -897,13 +906,13 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-sciplay-4391151881</t>
   </si>
   <si>
-    <t xml:space="preserve">DevOps Tech Lead (BigBrain)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monday.com AI engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-bigbrain-at-monday-com-ai-engineering-4449050085</t>
+    <t xml:space="preserve">Junior AI SRE Developer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helfy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
   </si>
   <si>
     <t xml:space="preserve">Senior DevOps Engineer / Technical Lead (AWS &amp; GCP)</t>
@@ -930,6 +939,87 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-sre-group-leader-at-extreme-4450267100</t>
   </si>
   <si>
+    <t xml:space="preserve">Research Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/research-infra-engineer-at-dream-4370342612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineer III, Platform Engineering and Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-iii-platform-engineering-and-infrastructure-at-google-4448296220</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior DevOps Engineer — AI-Native</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-devops-engineer-%E2%80%94-ai-native-at-artac-4449655270</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Software and DevOps Engineer, DOCA Verification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kiryat Ata, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-software-and-devops-engineer-doca-verification-at-nvidia-4404233510</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Automation Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon Web Services (AWS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-automation-engineer-at-amazon-web-services-aws-4448323071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Akiva, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-tairc-4447388666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peak Innovation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-administrator-at-peak-innovation-4450276163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Security Engineer - Microsoft 365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantum Machines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-microsoft-365-at-quantum-machines-4362195136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Security Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logica-IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-at-logica-it-4448093647</t>
+  </si>
+  <si>
     <t xml:space="preserve">System Engineer 24246</t>
   </si>
   <si>
@@ -939,111 +1029,24 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-24246-at-comblack-4450246628</t>
   </si>
   <si>
-    <t xml:space="preserve">איש.אשת DevOps Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dahan Lab</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%90%D7%99%D7%A9-%D7%90%D7%A9%D7%AA-devops-linux-at-dahan-lab-4449061474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rafael Advanced Defense Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/reliability-engineer-at-rafael-advanced-defense-systems-4437152427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineer III, Platform Engineering and Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-iii-platform-engineering-and-infrastructure-at-google-4448296220</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps Engineer — AI-Native</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-devops-engineer-%E2%80%94-ai-native-at-artac-4449655270</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-elbit-systems-israel-4394529806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAIRC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or HaNer, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-tairc-4448004083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Automation Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amazon Web Services (AWS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-automation-engineer-at-amazon-web-services-aws-4448323071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Akiva, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-tairc-4447388666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peak Innovation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-administrator-at-peak-innovation-4450276163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Security Engineer - Microsoft 365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantum Machines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-microsoft-365-at-quantum-machines-4362195136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Security Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logica-IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-at-logica-it-4448093647</t>
-  </si>
-  <si>
     <t xml:space="preserve">Senior Cloud Architect (37188)</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-architect-37188-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4450240052</t>
   </si>
   <si>
+    <t xml:space="preserve">OT Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YouCC Technologies Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashkelon, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ot-infrastructure-engineer-at-youcc-technologies-ltd-4448836015</t>
+  </si>
+  <si>
     <t xml:space="preserve">System Administrator</t>
   </si>
   <si>
@@ -1056,22 +1059,106 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-reline-it-solutions-4447375577</t>
   </si>
   <si>
-    <t xml:space="preserve">OT Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YouCC Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashkelon, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ot-infrastructure-engineer-at-youcc-technologies-ltd-4448836015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps / Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-tairc-4447391644</t>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
   </si>
   <si>
     <t xml:space="preserve">Linux System Engineer</t>
@@ -1083,132 +1170,12 @@
     <t xml:space="preserve">North District, Israel</t>
   </si>
   <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Virtualization, Active Directory, Automation</t>
+  </si>
+  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-calanit-by-one-4448158765</t>
   </si>
   <si>
-    <t xml:space="preserve">Alpha | Similarweb Partner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-alpha-similarweb-partner-4447362032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-artac-4449652341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.4%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior AI SRE Developer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helfy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Virtualization, Active Directory, Automation</t>
-  </si>
-  <si>
     <t xml:space="preserve">System Administrator - Linux, Windows #1350</t>
   </si>
   <si>
@@ -1257,123 +1224,108 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-position-at-waterfall-security-solutions-4444878648</t>
   </si>
   <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, GCP, Cloud (any), Terraform/IaC, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
     <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
   </si>
   <si>
-    <t xml:space="preserve">Test Environment Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
+    <t xml:space="preserve">Junior Technical Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4442889333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, CI/CD, Virtualization, Active Directory, Windows Server, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-system-engineer-at-experis-israel-4437265103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud &amp; AI Security Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4932015101?gh_jid=4932015101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computer System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camtek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-4428415454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator &amp; IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inManage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">etoro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
   </si>
   <si>
     <t xml:space="preserve">Help Desk / IT Support</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Networking, Monitoring, Databases, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/test-environment-support-engineer-at-abra-4442615924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Technical Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4442889333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, CI/CD, Virtualization, Active Directory, Windows Server, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-system-engineer-at-experis-israel-4437265103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Autobrains Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4440209390</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud &amp; AI Security Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4932015101?gh_jid=4932015101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Computer System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Camtek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-4428415454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator &amp; IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inManage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">etoro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
   </si>
   <si>
@@ -1383,18 +1335,6 @@
     <t xml:space="preserve">2026-07-01</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Operations Engineer I</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Innovid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-engineer-i-at-innovid-4443857656</t>
-  </si>
-  <si>
     <t xml:space="preserve">Unilink Ltd.</t>
   </si>
   <si>
@@ -1408,6 +1348,18 @@
   </si>
   <si>
     <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L3 Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/l3-support-engineer-at-nebius-4437652850</t>
   </si>
   <si>
     <t xml:space="preserve">Roles requiring it</t>
@@ -1586,7 +1538,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7">
@@ -1594,7 +1546,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -1602,7 +1554,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9">
@@ -1610,7 +1562,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>1240</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="10">
@@ -1618,7 +1570,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1682,7 +1634,7 @@
         <v>23</v>
       </c>
       <c r="B19" s="3">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20">
@@ -1690,7 +1642,7 @@
         <v>24</v>
       </c>
       <c r="B20" s="3">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -1709,28 +1661,28 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>415</v>
+        <v>434</v>
       </c>
       <c r="B2" s="3">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>391</v>
+        <v>376</v>
       </c>
       <c r="B3" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>405</v>
+        <v>394</v>
       </c>
       <c r="B4" s="3">
         <v>6</v>
@@ -1738,7 +1690,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>385</v>
+        <v>371</v>
       </c>
       <c r="B5" s="3">
         <v>1</v>
@@ -1757,31 +1709,31 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>358</v>
+        <v>346</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>463</v>
+        <v>447</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>464</v>
+        <v>448</v>
       </c>
       <c r="B2" s="3">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>368</v>
+        <v>356</v>
       </c>
       <c r="B3" s="3">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
       <c r="B4" s="3">
         <v>30</v>
@@ -1789,79 +1741,79 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>465</v>
+        <v>449</v>
       </c>
       <c r="B5" s="3">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>466</v>
+        <v>450</v>
       </c>
       <c r="B6" s="3">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>467</v>
+        <v>451</v>
       </c>
       <c r="B7" s="3">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>468</v>
+        <v>352</v>
       </c>
       <c r="B8" s="3">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>364</v>
+        <v>452</v>
       </c>
       <c r="B9" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>469</v>
+        <v>453</v>
       </c>
       <c r="B10" s="3">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>367</v>
+        <v>355</v>
       </c>
       <c r="B11" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>470</v>
+        <v>454</v>
       </c>
       <c r="B12" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>361</v>
+        <v>349</v>
       </c>
       <c r="B13" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>360</v>
+        <v>348</v>
       </c>
       <c r="B14" s="3">
         <v>10</v>
@@ -1869,18 +1821,18 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>363</v>
+        <v>351</v>
       </c>
       <c r="B15" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>471</v>
+        <v>455</v>
       </c>
       <c r="B16" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1905,13 +1857,13 @@
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>472</v>
+        <v>456</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>473</v>
+        <v>457</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>474</v>
+        <v>458</v>
       </c>
     </row>
     <row r="2">
@@ -1919,13 +1871,13 @@
         <v>24</v>
       </c>
       <c r="B2" s="3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C2" s="3">
-        <v>14.5</v>
+        <v>12.7</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>475</v>
+        <v>459</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -1934,88 +1886,88 @@
         <v>23</v>
       </c>
       <c r="B3" s="3">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C3" s="3">
-        <v>36.9</v>
+        <v>32.0</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>475</v>
+        <v>459</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>476</v>
+        <v>460</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>8.1</v>
+        <v>9.0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>475</v>
+        <v>459</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>477</v>
+        <v>461</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>2.0</v>
+        <v>2.7</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>475</v>
+        <v>459</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>478</v>
+        <v>462</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>34.5</v>
+        <v>45.4</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>475</v>
+        <v>459</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>479</v>
+        <v>463</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>18.0</v>
+        <v>18.6</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>475</v>
+        <v>459</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>480</v>
+        <v>464</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>14.3</v>
+        <v>14.1</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>475</v>
+        <v>459</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2099,7 +2051,7 @@
         <v>41</v>
       </c>
       <c r="J2" s="3">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3">
@@ -2131,7 +2083,7 @@
         <v>46</v>
       </c>
       <c r="J3" s="3">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
@@ -2163,7 +2115,7 @@
         <v>52</v>
       </c>
       <c r="J4" s="3">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5">
@@ -2195,7 +2147,7 @@
         <v>41</v>
       </c>
       <c r="J5" s="3">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6">
@@ -2227,7 +2179,7 @@
         <v>41</v>
       </c>
       <c r="J6" s="3">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7">
@@ -2259,7 +2211,7 @@
         <v>63</v>
       </c>
       <c r="J7" s="3">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8">
@@ -2291,7 +2243,7 @@
         <v>41</v>
       </c>
       <c r="J8" s="3">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9">
@@ -2323,7 +2275,7 @@
         <v>73</v>
       </c>
       <c r="J9" s="3">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10">
@@ -2355,7 +2307,7 @@
         <v>77</v>
       </c>
       <c r="J10" s="3">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11">
@@ -2387,7 +2339,7 @@
         <v>73</v>
       </c>
       <c r="J11" s="3">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12">
@@ -2395,10 +2347,10 @@
         <v>81</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>49</v>
+        <v>83</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>49</v>
@@ -2407,68 +2359,68 @@
         <v>38</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="J12" s="3">
-        <v>84</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J13" s="3">
-        <v>50</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>92</v>
+        <v>38</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>93</v>
@@ -2480,21 +2432,21 @@
         <v>94</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>95</v>
+        <v>46</v>
       </c>
       <c r="J14" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>49</v>
@@ -2503,19 +2455,19 @@
         <v>38</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H15" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="I15" s="3" t="s">
-        <v>46</v>
-      </c>
       <c r="J15" s="3">
-        <v>11</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -2523,10 +2475,10 @@
         <v>99</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>49</v>
@@ -2535,30 +2487,30 @@
         <v>38</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="J16" s="3">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>103</v>
+        <v>53</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>87</v>
+        <v>49</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>49</v>
@@ -2567,158 +2519,158 @@
         <v>38</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="J17" s="3">
-        <v>71</v>
+        <v>83</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>53</v>
+        <v>106</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>49</v>
+        <v>108</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>49</v>
+        <v>108</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="J18" s="3">
-        <v>81</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>112</v>
+        <v>49</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>112</v>
+        <v>49</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>43</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>115</v>
+        <v>41</v>
       </c>
       <c r="J19" s="3">
-        <v>33</v>
+        <v>89</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="C20" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="D20" s="3" t="s">
-        <v>49</v>
+        <v>118</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>43</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>41</v>
+        <v>121</v>
       </c>
       <c r="J20" s="3">
-        <v>87</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>47</v>
+        <v>122</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>121</v>
+        <v>83</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J21" s="3">
-        <v>56</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>87</v>
+        <v>129</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>49</v>
@@ -2727,70 +2679,70 @@
         <v>38</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="J22" s="3">
-        <v>3</v>
+        <v>63</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>134</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="F23" s="3"/>
       <c r="G23" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H23" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="I23" s="3" t="s">
-        <v>136</v>
-      </c>
       <c r="J23" s="3">
-        <v>61</v>
+        <v>74</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F24" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F24" s="3"/>
       <c r="G24" s="3" t="s">
         <v>24</v>
       </c>
@@ -2798,31 +2750,29 @@
         <v>138</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>139</v>
+        <v>41</v>
       </c>
       <c r="J24" s="3">
-        <v>72</v>
+        <v>89</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B25" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>132</v>
-      </c>
       <c r="C25" s="3" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>49</v>
+        <v>141</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F25" s="3" t="s">
-        <v>141</v>
-      </c>
+      <c r="F25" s="3"/>
       <c r="G25" s="3" t="s">
         <v>24</v>
       </c>
@@ -2830,15 +2780,15 @@
         <v>142</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>41</v>
+        <v>143</v>
       </c>
       <c r="J25" s="3">
-        <v>87</v>
+        <v>66</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>143</v>
+        <v>112</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>144</v>
@@ -2847,14 +2797,14 @@
         <v>145</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>145</v>
+        <v>118</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>146</v>
@@ -2863,12 +2813,12 @@
         <v>147</v>
       </c>
       <c r="J26" s="3">
-        <v>64</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>148</v>
@@ -2877,7 +2827,7 @@
         <v>149</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>43</v>
@@ -2893,12 +2843,12 @@
         <v>151</v>
       </c>
       <c r="J27" s="3">
-        <v>1</v>
+        <v>86</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>152</v>
@@ -2920,21 +2870,21 @@
         <v>154</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>84</v>
+        <v>155</v>
       </c>
       <c r="J28" s="3">
-        <v>84</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>49</v>
@@ -2947,27 +2897,27 @@
         <v>23</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="J29" s="3">
-        <v>24</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>116</v>
+        <v>159</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>49</v>
+        <v>118</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>43</v>
@@ -2977,27 +2927,27 @@
         <v>23</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I30" s="3" t="s">
         <v>151</v>
       </c>
       <c r="J30" s="3">
-        <v>1</v>
+        <v>86</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>162</v>
+        <v>112</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>163</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>43</v>
@@ -3007,27 +2957,27 @@
         <v>23</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>84</v>
+        <v>126</v>
       </c>
       <c r="J31" s="3">
-        <v>84</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>49</v>
+        <v>118</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>43</v>
@@ -3037,27 +2987,27 @@
         <v>23</v>
       </c>
       <c r="H32" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="I32" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>130</v>
-      </c>
       <c r="J32" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>116</v>
+        <v>168</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>149</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>43</v>
@@ -3067,27 +3017,27 @@
         <v>23</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J33" s="3">
-        <v>4</v>
+        <v>84</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>43</v>
@@ -3097,48 +3047,48 @@
         <v>23</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="J34" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>49</v>
+        <v>118</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J35" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>178</v>
+        <v>112</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>179</v>
@@ -3147,40 +3097,40 @@
         <v>180</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>122</v>
+        <v>181</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="J36" s="3">
-        <v>0</v>
+        <v>65</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>185</v>
+        <v>149</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
@@ -3190,42 +3140,40 @@
         <v>186</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>187</v>
+        <v>147</v>
       </c>
       <c r="J37" s="3">
-        <v>45</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C38" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>153</v>
-      </c>
       <c r="D38" s="3" t="s">
-        <v>49</v>
+        <v>118</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F38" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H38" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="G38" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H38" s="3" t="s">
+      <c r="I38" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="I38" s="3" t="s">
-        <v>191</v>
-      </c>
       <c r="J38" s="3">
-        <v>53</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -3233,13 +3181,13 @@
         <v>53</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>192</v>
+        <v>175</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>153</v>
+        <v>176</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>49</v>
+        <v>118</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>38</v>
@@ -3249,30 +3197,30 @@
         <v>23</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="J39" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>116</v>
+        <v>192</v>
       </c>
       <c r="B40" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C40" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="C40" s="3" t="s">
-        <v>160</v>
-      </c>
       <c r="D40" s="3" t="s">
-        <v>49</v>
+        <v>118</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
@@ -3282,21 +3230,21 @@
         <v>195</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="J40" s="3">
-        <v>0</v>
+        <v>47</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>116</v>
+        <v>197</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>196</v>
+        <v>160</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>49</v>
@@ -3304,89 +3252,91 @@
       <c r="E41" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F41" s="3"/>
+      <c r="F41" s="3" t="s">
+        <v>198</v>
+      </c>
       <c r="G41" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="J41" s="3">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>53</v>
+        <v>201</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>182</v>
+        <v>204</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>162</v>
+        <v>53</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>202</v>
+        <v>149</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>204</v>
+        <v>147</v>
       </c>
       <c r="J43" s="3">
-        <v>22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>47</v>
+        <v>112</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>49</v>
@@ -3394,25 +3344,23 @@
       <c r="E44" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>189</v>
-      </c>
+      <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>207</v>
+        <v>178</v>
       </c>
       <c r="J44" s="3">
-        <v>68</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>208</v>
+        <v>53</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>209</v>
@@ -3421,10 +3369,10 @@
         <v>149</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
@@ -3434,162 +3382,162 @@
         <v>210</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B46" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="B46" s="3" t="s">
-        <v>212</v>
-      </c>
       <c r="C46" s="3" t="s">
-        <v>213</v>
+        <v>149</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>214</v>
+        <v>49</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>147</v>
+        <v>178</v>
       </c>
       <c r="J46" s="3">
-        <v>64</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>216</v>
+        <v>159</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>60</v>
+        <v>214</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>49</v>
+        <v>118</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>189</v>
-      </c>
+      <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>77</v>
+        <v>216</v>
       </c>
       <c r="J47" s="3">
-        <v>71</v>
+        <v>24</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>219</v>
+        <v>169</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F48" s="3"/>
+        <v>43</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>198</v>
+      </c>
       <c r="G48" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="J48" s="3">
-        <v>44</v>
+        <v>70</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>53</v>
+        <v>219</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>49</v>
+        <v>118</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="J49" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>53</v>
+        <v>222</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>224</v>
+        <v>179</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>156</v>
+        <v>180</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>49</v>
+        <v>181</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>170</v>
+        <v>143</v>
       </c>
       <c r="J50" s="3">
-        <v>4</v>
+        <v>66</v>
       </c>
     </row>
     <row r="51">
@@ -3597,10 +3545,10 @@
         <v>53</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>49</v>
@@ -3613,24 +3561,24 @@
         <v>23</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="J51" s="3">
-        <v>25</v>
+        <v>46</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>229</v>
+        <v>53</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>49</v>
@@ -3643,21 +3591,21 @@
         <v>23</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="J52" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>232</v>
+        <v>53</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>153</v>
@@ -3673,13 +3621,13 @@
         <v>23</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="J53" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="54">
@@ -3687,10 +3635,10 @@
         <v>53</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>49</v>
@@ -3703,24 +3651,24 @@
         <v>23</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="J54" s="3">
-        <v>2</v>
+        <v>27</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>53</v>
+        <v>234</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>49</v>
@@ -3733,40 +3681,42 @@
         <v>23</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>151</v>
+        <v>178</v>
       </c>
       <c r="J55" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H56" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="B56" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E56" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F56" s="3"/>
-      <c r="G56" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H56" s="3" t="s">
+      <c r="I56" s="3" t="s">
         <v>241</v>
-      </c>
-      <c r="I56" s="3" t="s">
-        <v>170</v>
       </c>
       <c r="J56" s="3">
         <v>4</v>
@@ -3774,13 +3724,13 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B57" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="B57" s="3" t="s">
-        <v>243</v>
-      </c>
       <c r="C57" s="3" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>49</v>
@@ -3793,57 +3743,57 @@
         <v>23</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>84</v>
+        <v>241</v>
       </c>
       <c r="J57" s="3">
-        <v>84</v>
+        <v>4</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="B58" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="B58" s="3" t="s">
-        <v>246</v>
-      </c>
       <c r="C58" s="3" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="J58" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>248</v>
+        <v>53</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>250</v>
+        <v>149</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>38</v>
@@ -3853,21 +3803,21 @@
         <v>23</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>207</v>
+        <v>241</v>
       </c>
       <c r="J59" s="3">
-        <v>68</v>
+        <v>4</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>252</v>
+        <v>53</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>153</v>
@@ -3883,27 +3833,27 @@
         <v>23</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>255</v>
+        <v>147</v>
       </c>
       <c r="J60" s="3">
-        <v>29</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>257</v>
+        <v>149</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>258</v>
+        <v>49</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>38</v>
@@ -3913,24 +3863,24 @@
         <v>23</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>182</v>
+        <v>147</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>261</v>
+        <v>172</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>49</v>
@@ -3943,146 +3893,144 @@
         <v>23</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="J62" s="3">
-        <v>24</v>
+        <v>6</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>257</v>
+        <v>149</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>258</v>
+        <v>49</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F63" s="3"/>
       <c r="G63" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>182</v>
+        <v>147</v>
       </c>
       <c r="J63" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>53</v>
+        <v>259</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>153</v>
+        <v>261</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>49</v>
+        <v>118</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>268</v>
+        <v>147</v>
       </c>
       <c r="J64" s="3">
-        <v>42</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F65" s="3" t="s">
-        <v>189</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>151</v>
+        <v>190</v>
       </c>
       <c r="J65" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>257</v>
+        <v>149</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>258</v>
+        <v>49</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="J66" s="3">
-        <v>3</v>
+        <v>86</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>49</v>
@@ -4095,72 +4043,70 @@
         <v>23</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="I67" s="3" t="s">
         <v>151</v>
       </c>
       <c r="J67" s="3">
-        <v>1</v>
+        <v>86</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>280</v>
+        <v>176</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>145</v>
+        <v>118</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F68" s="3" t="s">
-        <v>281</v>
-      </c>
+      <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>228</v>
+        <v>275</v>
       </c>
       <c r="J68" s="3">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>284</v>
+        <v>260</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>153</v>
+        <v>261</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>49</v>
+        <v>118</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="J69" s="3">
         <v>3</v>
@@ -4168,43 +4114,45 @@
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>264</v>
+        <v>279</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>153</v>
+        <v>280</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>49</v>
+        <v>141</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F70" s="3"/>
+      <c r="F70" s="3" t="s">
+        <v>239</v>
+      </c>
       <c r="G70" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>77</v>
+        <v>233</v>
       </c>
       <c r="J70" s="3">
-        <v>71</v>
+        <v>27</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>53</v>
+        <v>282</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>49</v>
@@ -4217,24 +4165,24 @@
         <v>23</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>170</v>
+        <v>126</v>
       </c>
       <c r="J71" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>56</v>
+        <v>285</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>49</v>
@@ -4247,24 +4195,24 @@
         <v>23</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>84</v>
+        <v>155</v>
       </c>
       <c r="J72" s="3">
-        <v>84</v>
+        <v>26</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>292</v>
+        <v>53</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>49</v>
@@ -4277,151 +4225,149 @@
         <v>23</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>151</v>
+        <v>290</v>
       </c>
       <c r="J73" s="3">
-        <v>1</v>
+        <v>44</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>295</v>
+        <v>56</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>297</v>
+        <v>149</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F74" s="3" t="s">
-        <v>298</v>
-      </c>
+      <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>237</v>
+        <v>190</v>
       </c>
       <c r="J74" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>300</v>
+        <v>56</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="C75" s="3" t="s">
         <v>149</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F75" s="3"/>
       <c r="G75" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>182</v>
+        <v>151</v>
       </c>
       <c r="J75" s="3">
-        <v>0</v>
+        <v>86</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>149</v>
+        <v>60</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>43</v>
+        <v>88</v>
       </c>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>182</v>
+        <v>143</v>
       </c>
       <c r="J76" s="3">
-        <v>0</v>
+        <v>66</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>164</v>
+        <v>300</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>281</v>
+        <v>301</v>
       </c>
       <c r="G77" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="J77" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>43</v>
@@ -4431,24 +4377,24 @@
         <v>23</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="J78" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>313</v>
+        <v>264</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>49</v>
@@ -4461,117 +4407,117 @@
         <v>23</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>237</v>
+        <v>308</v>
       </c>
       <c r="J79" s="3">
-        <v>2</v>
+        <v>62</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>179</v>
+        <v>310</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>92</v>
+        <v>43</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>151</v>
+        <v>241</v>
       </c>
       <c r="J80" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>116</v>
+        <v>312</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>212</v>
+        <v>175</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>213</v>
+        <v>176</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>214</v>
+        <v>118</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>43</v>
+        <v>88</v>
       </c>
       <c r="F81" s="3"/>
       <c r="G81" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>318</v>
+        <v>147</v>
       </c>
       <c r="J81" s="3">
-        <v>63</v>
+        <v>3</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>320</v>
+        <v>187</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>122</v>
+        <v>181</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>151</v>
+        <v>190</v>
       </c>
       <c r="J82" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>214</v>
+        <v>181</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>43</v>
@@ -4581,27 +4527,27 @@
         <v>23</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="J83" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>320</v>
+        <v>260</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>214</v>
+        <v>181</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>43</v>
@@ -4611,27 +4557,27 @@
         <v>23</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="J84" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>43</v>
@@ -4641,24 +4587,24 @@
         <v>23</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="J85" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D86" s="3" t="s">
         <v>49</v>
@@ -4667,30 +4613,30 @@
         <v>43</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="G86" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>84</v>
+        <v>151</v>
       </c>
       <c r="J86" s="3">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D87" s="3" t="s">
         <v>49</v>
@@ -4699,76 +4645,76 @@
         <v>43</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="G87" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="J87" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>209</v>
+        <v>334</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F88" s="3"/>
       <c r="G88" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="J88" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>342</v>
+        <v>220</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>343</v>
+        <v>145</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F89" s="3"/>
       <c r="G89" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>237</v>
+        <v>178</v>
       </c>
       <c r="J89" s="3">
         <v>2</v>
@@ -4776,16 +4722,16 @@
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>43</v>
@@ -4795,27 +4741,27 @@
         <v>23</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="J90" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>320</v>
+        <v>343</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>321</v>
+        <v>344</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>43</v>
@@ -4825,109 +4771,17 @@
         <v>23</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>151</v>
+        <v>241</v>
       </c>
       <c r="J91" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="B92" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="C92" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="D92" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="E92" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F92" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="G92" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H92" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="I92" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="J92" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B93" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="C93" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="D93" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E93" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F93" s="3"/>
-      <c r="G93" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H93" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="I93" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="J93" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B94" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="C94" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="D94" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F94" s="3"/>
-      <c r="G94" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="J94" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J94"/>
+  <autoFilter ref="A1:J91"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5019,9 +4873,6 @@
     <hyperlink ref="H89" r:id="rId88"/>
     <hyperlink ref="H90" r:id="rId89"/>
     <hyperlink ref="H91" r:id="rId90"/>
-    <hyperlink ref="H92" r:id="rId91"/>
-    <hyperlink ref="H93" r:id="rId92"/>
-    <hyperlink ref="H94" r:id="rId93"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5029,8 +4880,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="42" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="1" max="1" width="56" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -5063,13 +4914,13 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>178</v>
+        <v>53</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -5077,18 +4928,18 @@
         <v>23</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>116</v>
+        <v>263</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>194</v>
+        <v>264</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -5096,18 +4947,18 @@
         <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>195</v>
+        <v>265</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>199</v>
+        <v>291</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -5115,18 +4966,18 @@
         <v>23</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>200</v>
+        <v>292</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>208</v>
+        <v>314</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>209</v>
+        <v>187</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>149</v>
+        <v>315</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5134,196 +4985,16 @@
         <v>23</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>340</v>
+        <v>316</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G14"/>
+  <autoFilter ref="A1:G5"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
     <hyperlink ref="G4" r:id="rId3"/>
     <hyperlink ref="G5" r:id="rId4"/>
-    <hyperlink ref="G6" r:id="rId5"/>
-    <hyperlink ref="G7" r:id="rId6"/>
-    <hyperlink ref="G8" r:id="rId7"/>
-    <hyperlink ref="G9" r:id="rId8"/>
-    <hyperlink ref="G10" r:id="rId9"/>
-    <hyperlink ref="G11" r:id="rId10"/>
-    <hyperlink ref="G12" r:id="rId11"/>
-    <hyperlink ref="G13" r:id="rId12"/>
-    <hyperlink ref="G14" r:id="rId13"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5337,23 +5008,23 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>358</v>
+        <v>346</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>359</v>
+        <v>347</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="B2" s="3">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>360</v>
+        <v>348</v>
       </c>
       <c r="B3" s="3">
         <v>15</v>
@@ -5361,7 +5032,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>361</v>
+        <v>349</v>
       </c>
       <c r="B4" s="3">
         <v>15</v>
@@ -5369,23 +5040,23 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>362</v>
+        <v>350</v>
       </c>
       <c r="B5" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>281</v>
+        <v>351</v>
       </c>
       <c r="B6" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>363</v>
+        <v>239</v>
       </c>
       <c r="B7" s="3">
         <v>11</v>
@@ -5393,7 +5064,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>364</v>
+        <v>352</v>
       </c>
       <c r="B8" s="3">
         <v>10</v>
@@ -5401,7 +5072,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>365</v>
+        <v>353</v>
       </c>
       <c r="B9" s="3">
         <v>9</v>
@@ -5409,7 +5080,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>366</v>
+        <v>354</v>
       </c>
       <c r="B10" s="3">
         <v>9</v>
@@ -5417,7 +5088,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>367</v>
+        <v>355</v>
       </c>
       <c r="B11" s="3">
         <v>8</v>
@@ -5425,23 +5096,23 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>368</v>
+        <v>356</v>
       </c>
       <c r="B12" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>369</v>
+        <v>357</v>
       </c>
       <c r="B13" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>370</v>
+        <v>358</v>
       </c>
       <c r="B14" s="3">
         <v>6</v>
@@ -5449,7 +5120,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>371</v>
+        <v>359</v>
       </c>
       <c r="B15" s="3">
         <v>5</v>
@@ -5457,7 +5128,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>372</v>
+        <v>360</v>
       </c>
       <c r="B16" s="3">
         <v>4</v>
@@ -5479,12 +5150,12 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>373</v>
+        <v>361</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="B2" s="3">
         <v>4</v>
@@ -5492,15 +5163,15 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>86</v>
+        <v>48</v>
       </c>
       <c r="B3" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="B4" s="3">
         <v>3</v>
@@ -5508,7 +5179,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -5516,7 +5187,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -5524,7 +5195,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>320</v>
+        <v>260</v>
       </c>
       <c r="B7" s="3">
         <v>3</v>
@@ -5540,7 +5211,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
@@ -5548,7 +5219,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -5556,7 +5227,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5564,7 +5235,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>209</v>
+        <v>172</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5572,7 +5243,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>212</v>
+        <v>179</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -5580,7 +5251,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>264</v>
+        <v>187</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -5588,18 +5259,18 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>59</v>
+        <v>220</v>
       </c>
       <c r="B15" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>65</v>
+        <v>264</v>
       </c>
       <c r="B16" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5617,16 +5288,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>374</v>
+        <v>362</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>375</v>
+        <v>363</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>373</v>
+        <v>361</v>
       </c>
     </row>
     <row r="2">
@@ -5634,7 +5305,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C2" s="3">
         <v>16.8</v>
@@ -5662,13 +5333,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>70</v>
+        <v>128</v>
       </c>
       <c r="C4" s="3">
-        <v>10.6</v>
+        <v>8.8</v>
       </c>
       <c r="D4" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -5676,10 +5347,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>132</v>
+        <v>70</v>
       </c>
       <c r="C5" s="3">
-        <v>8.8</v>
+        <v>7.2</v>
       </c>
       <c r="D5" s="3">
         <v>3</v>
@@ -5704,7 +5375,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C7" s="3">
         <v>5.3</v>
@@ -5718,7 +5389,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C8" s="3">
         <v>4.2</v>
@@ -5732,7 +5403,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>320</v>
+        <v>260</v>
       </c>
       <c r="C9" s="3">
         <v>3.6</v>
@@ -5746,7 +5417,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C10" s="3">
         <v>2.9</v>
@@ -5760,7 +5431,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C11" s="3">
         <v>2.8</v>
@@ -5774,7 +5445,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="C12" s="3">
         <v>2.8</v>
@@ -5788,13 +5459,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>127</v>
+        <v>264</v>
       </c>
       <c r="C13" s="3">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="D13" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -5802,13 +5473,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>163</v>
+        <v>123</v>
       </c>
       <c r="C14" s="3">
         <v>2.6</v>
       </c>
       <c r="D14" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -5816,10 +5487,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>212</v>
+        <v>160</v>
       </c>
       <c r="C15" s="3">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="D15" s="3">
         <v>2</v>
@@ -5830,10 +5501,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>264</v>
+        <v>169</v>
       </c>
       <c r="C16" s="3">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="D16" s="3">
         <v>2</v>
@@ -5856,18 +5527,18 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>377</v>
+        <v>365</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B2" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>12</v>
@@ -5878,10 +5549,10 @@
         <v>43</v>
       </c>
       <c r="B3" s="3">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>378</v>
+        <v>366</v>
       </c>
     </row>
     <row r="4">
@@ -5889,10 +5560,10 @@
         <v>38</v>
       </c>
       <c r="B4" s="3">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>379</v>
+        <v>367</v>
       </c>
     </row>
   </sheetData>
@@ -5911,7 +5582,7 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
     </row>
     <row r="2">
@@ -5924,31 +5595,31 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B3" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>214</v>
+        <v>181</v>
       </c>
       <c r="B4" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>258</v>
+        <v>37</v>
       </c>
       <c r="B5" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>37</v>
+        <v>141</v>
       </c>
       <c r="B6" s="3">
         <v>2</v>
@@ -5956,17 +5627,9 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>145</v>
+        <v>108</v>
       </c>
       <c r="B7" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="B8" s="3">
         <v>1</v>
       </c>
     </row>
@@ -5991,10 +5654,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>374</v>
+        <v>362</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>26</v>
@@ -6006,10 +5669,10 @@
         <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>381</v>
+        <v>369</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>21</v>
@@ -6026,31 +5689,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>383</v>
+        <v>295</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>384</v>
+        <v>296</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>60</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>385</v>
+        <v>371</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>386</v>
+        <v>372</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>387</v>
+        <v>297</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>388</v>
+        <v>373</v>
       </c>
     </row>
     <row r="3">
@@ -6058,31 +5721,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>389</v>
+        <v>374</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>390</v>
+        <v>375</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>60</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>391</v>
+        <v>376</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>392</v>
+        <v>377</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>393</v>
+        <v>378</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>394</v>
+        <v>379</v>
       </c>
     </row>
     <row r="4">
@@ -6090,31 +5753,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>351</v>
+        <v>380</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>352</v>
+        <v>381</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>353</v>
+        <v>382</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>391</v>
+        <v>376</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>395</v>
+        <v>383</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>354</v>
+        <v>384</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5">
@@ -6122,31 +5785,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>396</v>
+        <v>385</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>397</v>
+        <v>386</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>391</v>
+        <v>376</v>
       </c>
       <c r="F5" s="3">
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>398</v>
+        <v>387</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>399</v>
+        <v>388</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>400</v>
+        <v>389</v>
       </c>
     </row>
     <row r="6">
@@ -6154,31 +5817,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>401</v>
+        <v>390</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>402</v>
+        <v>391</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>391</v>
+        <v>376</v>
       </c>
       <c r="F6" s="3">
         <v>100</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>404</v>
+        <v>393</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7">
@@ -6186,31 +5849,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>405</v>
+        <v>394</v>
       </c>
       <c r="F7" s="3">
         <v>92</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8">
@@ -6218,31 +5881,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>407</v>
+        <v>396</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>408</v>
+        <v>397</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>409</v>
+        <v>398</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>405</v>
+        <v>394</v>
       </c>
       <c r="F8" s="3">
         <v>92</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>410</v>
+        <v>399</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>411</v>
+        <v>400</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="9">
@@ -6250,31 +5913,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>42</v>
+        <v>333</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>35</v>
+        <v>334</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>36</v>
+        <v>145</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>405</v>
+        <v>376</v>
       </c>
       <c r="F9" s="3">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>412</v>
+        <v>401</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>45</v>
+        <v>335</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>46</v>
+        <v>178</v>
       </c>
     </row>
     <row r="10">
@@ -6282,31 +5945,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>413</v>
+        <v>324</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>414</v>
+        <v>325</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>415</v>
+        <v>376</v>
       </c>
       <c r="F10" s="3">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>416</v>
+        <v>402</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>417</v>
+        <v>326</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>418</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11">
@@ -6314,31 +5977,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>419</v>
+        <v>42</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>420</v>
+        <v>35</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>153</v>
+        <v>36</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="F11" s="3">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>421</v>
+        <v>403</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>422</v>
+        <v>45</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>95</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12">
@@ -6346,31 +6009,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>423</v>
+        <v>404</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>424</v>
+        <v>405</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>60</v>
+        <v>149</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>391</v>
+        <v>376</v>
       </c>
       <c r="F12" s="3">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>425</v>
+        <v>406</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>426</v>
+        <v>407</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>427</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13">
@@ -6378,31 +6041,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>428</v>
+        <v>408</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>429</v>
+        <v>409</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>153</v>
+        <v>60</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>415</v>
+        <v>376</v>
       </c>
       <c r="F13" s="3">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>430</v>
+        <v>410</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>431</v>
+        <v>411</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>204</v>
+        <v>412</v>
       </c>
     </row>
     <row r="14">
@@ -6410,7 +6073,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>432</v>
+        <v>413</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>35</v>
@@ -6419,22 +6082,22 @@
         <v>36</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>391</v>
+        <v>376</v>
       </c>
       <c r="F14" s="3">
         <v>60</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>433</v>
+        <v>414</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>434</v>
+        <v>415</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="15">
@@ -6442,31 +6105,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>435</v>
+        <v>417</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>436</v>
+        <v>418</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>437</v>
+        <v>419</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>391</v>
+        <v>376</v>
       </c>
       <c r="F15" s="3">
         <v>56</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>438</v>
+        <v>420</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>439</v>
+        <v>421</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>440</v>
+        <v>422</v>
       </c>
     </row>
     <row r="16">
@@ -6474,31 +6137,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>441</v>
+        <v>423</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>249</v>
+        <v>187</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>250</v>
+        <v>188</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>391</v>
+        <v>376</v>
       </c>
       <c r="F16" s="3">
         <v>52</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>442</v>
+        <v>424</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>443</v>
+        <v>425</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
     </row>
     <row r="17">
@@ -6506,31 +6169,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>444</v>
+        <v>426</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>445</v>
+        <v>427</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>391</v>
+        <v>376</v>
       </c>
       <c r="F17" s="3">
         <v>52</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>446</v>
+        <v>428</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>447</v>
+        <v>429</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>448</v>
+        <v>430</v>
       </c>
     </row>
     <row r="18">
@@ -6538,31 +6201,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>449</v>
+        <v>432</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>450</v>
+        <v>433</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>415</v>
+        <v>434</v>
       </c>
       <c r="F18" s="3">
         <v>51</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>451</v>
+        <v>435</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>452</v>
+        <v>436</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>453</v>
+        <v>437</v>
       </c>
     </row>
     <row r="19">
@@ -6570,31 +6233,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>454</v>
+        <v>342</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>455</v>
+        <v>438</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>391</v>
+        <v>376</v>
       </c>
       <c r="F19" s="3">
         <v>48</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>456</v>
+        <v>439</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>457</v>
+        <v>440</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>130</v>
+        <v>441</v>
       </c>
     </row>
     <row r="20">
@@ -6602,31 +6265,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>341</v>
+        <v>58</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>458</v>
+        <v>59</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>160</v>
+        <v>60</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>391</v>
+        <v>376</v>
       </c>
       <c r="F20" s="3">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>459</v>
+        <v>442</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>460</v>
+        <v>62</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>461</v>
+        <v>63</v>
       </c>
     </row>
     <row r="21">
@@ -6634,31 +6297,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>58</v>
+        <v>443</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>59</v>
+        <v>444</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>60</v>
+        <v>176</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>391</v>
+        <v>434</v>
       </c>
       <c r="F21" s="3">
         <v>44</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>462</v>
+        <v>445</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>62</v>
+        <v>446</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>63</v>
+        <v>412</v>
       </c>
     </row>
   </sheetData>
